--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -6692,8 +6692,10 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L97" t="n">
-        <v>207</v>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -8558,8 +8560,10 @@
           <t>PARALISADO</t>
         </is>
       </c>
-      <c r="L126" t="n">
-        <v>130</v>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
       </c>
       <c r="M126" t="n">
         <v>5000</v>
@@ -9438,8 +9442,10 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L140" t="n">
-        <v>207</v>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
       </c>
       <c r="M140" t="n">
         <v>1</v>
@@ -9574,8 +9580,10 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L142" t="n">
-        <v>207</v>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
       </c>
       <c r="M142" t="n">
         <v>1</v>
@@ -9644,8 +9652,10 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L143" t="n">
-        <v>207</v>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
       </c>
       <c r="M143" t="n">
         <v>1</v>
@@ -9912,8 +9922,10 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L147" t="n">
-        <v>207</v>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
       </c>
       <c r="M147" t="n">
         <v>1</v>
@@ -9982,8 +9994,10 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L148" t="n">
-        <v>207</v>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
       </c>
       <c r="M148" t="n">
         <v>1</v>

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -560,7 +560,9 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
@@ -624,7 +626,9 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
@@ -688,7 +692,9 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
@@ -752,7 +758,9 @@
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
@@ -816,7 +824,9 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
@@ -880,7 +890,9 @@
       <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
@@ -944,7 +956,9 @@
       <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
@@ -1008,7 +1022,9 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
@@ -1072,7 +1088,9 @@
       <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
@@ -1136,7 +1154,9 @@
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
@@ -1200,7 +1220,9 @@
       <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
@@ -1264,7 +1286,9 @@
       <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
@@ -1328,7 +1352,9 @@
       <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
@@ -1392,7 +1418,9 @@
       <c r="G15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>14</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
@@ -1456,7 +1484,9 @@
       <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>15</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
@@ -1520,7 +1550,9 @@
       <c r="G17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>16</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
@@ -1584,7 +1616,9 @@
       <c r="G18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>17</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
@@ -1648,7 +1682,9 @@
       <c r="G19" t="n">
         <v>1</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>18</v>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
@@ -1712,7 +1748,9 @@
       <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>19</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
@@ -1776,7 +1814,9 @@
       <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
@@ -1840,7 +1880,9 @@
       <c r="G22" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>21</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
@@ -1904,7 +1946,9 @@
       <c r="G23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>22</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
@@ -1968,7 +2012,9 @@
       <c r="G24" t="n">
         <v>1</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>23</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
@@ -2032,7 +2078,9 @@
       <c r="G25" t="n">
         <v>1</v>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>24</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
@@ -2096,7 +2144,9 @@
       <c r="G26" t="n">
         <v>1</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>25</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
@@ -2160,7 +2210,9 @@
       <c r="G27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>26</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
@@ -2224,7 +2276,9 @@
       <c r="G28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>27</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
@@ -2288,7 +2342,9 @@
       <c r="G29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>28</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
@@ -2352,7 +2408,9 @@
       <c r="G30" t="n">
         <v>1</v>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>29</v>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
@@ -2416,7 +2474,9 @@
       <c r="G31" t="n">
         <v>1</v>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>30</v>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
@@ -2480,7 +2540,9 @@
       <c r="G32" t="n">
         <v>1</v>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>31</v>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
@@ -2544,7 +2606,9 @@
       <c r="G33" t="n">
         <v>1</v>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>32</v>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
@@ -2608,7 +2672,9 @@
       <c r="G34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>33</v>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
@@ -2672,7 +2738,9 @@
       <c r="G35" t="n">
         <v>1</v>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>34</v>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
@@ -2736,7 +2804,9 @@
       <c r="G36" t="n">
         <v>1</v>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>35</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
@@ -2800,7 +2870,9 @@
       <c r="G37" t="n">
         <v>1</v>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>36</v>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
@@ -2864,7 +2936,9 @@
       <c r="G38" t="n">
         <v>1</v>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>37</v>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
@@ -2928,7 +3002,9 @@
       <c r="G39" t="n">
         <v>1</v>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>38</v>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
@@ -2992,7 +3068,9 @@
       <c r="G40" t="n">
         <v>1</v>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>39</v>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
@@ -3056,7 +3134,9 @@
       <c r="G41" t="n">
         <v>1</v>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>40</v>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
@@ -3120,7 +3200,9 @@
       <c r="G42" t="n">
         <v>1</v>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>41</v>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
@@ -3184,7 +3266,9 @@
       <c r="G43" t="n">
         <v>1</v>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>42</v>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
@@ -3248,7 +3332,9 @@
       <c r="G44" t="n">
         <v>1</v>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>43</v>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
@@ -3312,7 +3398,9 @@
       <c r="G45" t="n">
         <v>1</v>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>44</v>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
@@ -3376,7 +3464,9 @@
       <c r="G46" t="n">
         <v>1</v>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="n">
+        <v>45</v>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
@@ -3440,7 +3530,9 @@
       <c r="G47" t="n">
         <v>1</v>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>46</v>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
@@ -3504,7 +3596,9 @@
       <c r="G48" t="n">
         <v>1</v>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>47</v>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
@@ -3568,7 +3662,9 @@
       <c r="G49" t="n">
         <v>1</v>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>48</v>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
@@ -3632,7 +3728,9 @@
       <c r="G50" t="n">
         <v>1</v>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>49</v>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
@@ -3696,7 +3794,9 @@
       <c r="G51" t="n">
         <v>1</v>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>50</v>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
@@ -3760,7 +3860,9 @@
       <c r="G52" t="n">
         <v>1</v>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>51</v>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
@@ -3824,7 +3926,9 @@
       <c r="G53" t="n">
         <v>1</v>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>52</v>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
@@ -3888,7 +3992,9 @@
       <c r="G54" t="n">
         <v>1</v>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>53</v>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
@@ -3952,7 +4058,9 @@
       <c r="G55" t="n">
         <v>1</v>
       </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>54</v>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
@@ -4016,7 +4124,9 @@
       <c r="G56" t="n">
         <v>1</v>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>55</v>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
@@ -4080,7 +4190,9 @@
       <c r="G57" t="n">
         <v>1</v>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>56</v>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
@@ -4144,7 +4256,9 @@
       <c r="G58" t="n">
         <v>1</v>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>57</v>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
@@ -4208,7 +4322,9 @@
       <c r="G59" t="n">
         <v>1</v>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>58</v>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
@@ -4272,7 +4388,9 @@
       <c r="G60" t="n">
         <v>1</v>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>59</v>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
@@ -4336,7 +4454,9 @@
       <c r="G61" t="n">
         <v>1</v>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>60</v>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
@@ -4400,7 +4520,9 @@
       <c r="G62" t="n">
         <v>1</v>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="n">
+        <v>61</v>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
@@ -4464,7 +4586,9 @@
       <c r="G63" t="n">
         <v>1</v>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="n">
+        <v>62</v>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
@@ -4528,7 +4652,9 @@
       <c r="G64" t="n">
         <v>1</v>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>63</v>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
@@ -4592,7 +4718,9 @@
       <c r="G65" t="n">
         <v>0</v>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="n">
+        <v>64</v>
+      </c>
       <c r="I65" t="n">
         <v>12404</v>
       </c>
@@ -4658,7 +4786,9 @@
       <c r="G66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>65</v>
+      </c>
       <c r="I66" t="n">
         <v>12780</v>
       </c>
@@ -4724,7 +4854,9 @@
       <c r="G67" t="n">
         <v>0</v>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>66</v>
+      </c>
       <c r="I67" t="n">
         <v>10397</v>
       </c>
@@ -4790,7 +4922,9 @@
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>67</v>
+      </c>
       <c r="I68" t="n">
         <v>12850</v>
       </c>
@@ -4856,7 +4990,9 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>68</v>
+      </c>
       <c r="I69" t="n">
         <v>12634</v>
       </c>
@@ -4922,7 +5058,9 @@
       <c r="G70" t="n">
         <v>0</v>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>69</v>
+      </c>
       <c r="I70" t="n">
         <v>12785</v>
       </c>
@@ -4988,7 +5126,9 @@
       <c r="G71" t="n">
         <v>0</v>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="n">
+        <v>70</v>
+      </c>
       <c r="I71" t="n">
         <v>12824</v>
       </c>
@@ -5054,7 +5194,9 @@
       <c r="G72" t="n">
         <v>0</v>
       </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>71</v>
+      </c>
       <c r="I72" t="n">
         <v>4716</v>
       </c>
@@ -5120,7 +5262,9 @@
       <c r="G73" t="n">
         <v>0</v>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>72</v>
+      </c>
       <c r="I73" t="n">
         <v>11140</v>
       </c>
@@ -5186,7 +5330,9 @@
       <c r="G74" t="n">
         <v>0</v>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>73</v>
+      </c>
       <c r="I74" t="n">
         <v>12510</v>
       </c>
@@ -5252,7 +5398,9 @@
       <c r="G75" t="n">
         <v>0</v>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="n">
+        <v>74</v>
+      </c>
       <c r="I75" t="n">
         <v>12453</v>
       </c>
@@ -5318,7 +5466,9 @@
       <c r="G76" t="n">
         <v>0</v>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="n">
+        <v>75</v>
+      </c>
       <c r="I76" t="n">
         <v>12454</v>
       </c>
@@ -5384,7 +5534,9 @@
       <c r="G77" t="n">
         <v>0</v>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>76</v>
+      </c>
       <c r="I77" t="n">
         <v>11521</v>
       </c>
@@ -5450,7 +5602,9 @@
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="n">
+        <v>77</v>
+      </c>
       <c r="I78" t="n">
         <v>11519</v>
       </c>
@@ -5516,7 +5670,9 @@
       <c r="G79" t="n">
         <v>0</v>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>78</v>
+      </c>
       <c r="I79" t="n">
         <v>11512</v>
       </c>
@@ -5582,7 +5738,9 @@
       <c r="G80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>79</v>
+      </c>
       <c r="I80" t="n">
         <v>11514</v>
       </c>
@@ -5648,7 +5806,9 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>80</v>
+      </c>
       <c r="I81" t="n">
         <v>11511</v>
       </c>
@@ -5714,7 +5874,9 @@
       <c r="G82" t="n">
         <v>0</v>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>81</v>
+      </c>
       <c r="I82" t="n">
         <v>11520</v>
       </c>
@@ -5780,7 +5942,9 @@
       <c r="G83" t="n">
         <v>0</v>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="n">
+        <v>82</v>
+      </c>
       <c r="I83" t="n">
         <v>11513</v>
       </c>
@@ -5846,7 +6010,9 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>83</v>
+      </c>
       <c r="I84" t="n">
         <v>11977</v>
       </c>
@@ -5912,7 +6078,9 @@
       <c r="G85" t="n">
         <v>1</v>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>84</v>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
@@ -5976,7 +6144,9 @@
       <c r="G86" t="n">
         <v>1</v>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="n">
+        <v>85</v>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
@@ -6040,7 +6210,9 @@
       <c r="G87" t="n">
         <v>1</v>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="n">
+        <v>86</v>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
@@ -6104,7 +6276,9 @@
       <c r="G88" t="n">
         <v>1</v>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>87</v>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
@@ -6168,7 +6342,9 @@
       <c r="G89" t="n">
         <v>1</v>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>88</v>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
@@ -6232,7 +6408,9 @@
       <c r="G90" t="n">
         <v>1</v>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>89</v>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
@@ -6296,7 +6474,9 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>90</v>
+      </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
@@ -6360,7 +6540,9 @@
       <c r="G92" t="n">
         <v>0</v>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="n">
+        <v>91</v>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
@@ -6424,7 +6606,9 @@
       <c r="G93" t="n">
         <v>0</v>
       </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>92</v>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
@@ -6488,7 +6672,9 @@
       <c r="G94" t="n">
         <v>0</v>
       </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="n">
+        <v>93</v>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
@@ -6552,7 +6738,9 @@
       <c r="G95" t="n">
         <v>0</v>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>94</v>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
@@ -6616,7 +6804,9 @@
       <c r="G96" t="n">
         <v>0</v>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="n">
+        <v>95</v>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
@@ -6680,7 +6870,9 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="n">
+        <v>96</v>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
@@ -6750,7 +6942,9 @@
       <c r="G98" t="n">
         <v>0</v>
       </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" t="n">
+        <v>97</v>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
@@ -6814,7 +7008,9 @@
       <c r="G99" t="n">
         <v>0</v>
       </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="H99" t="n">
+        <v>98</v>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
@@ -6878,7 +7074,9 @@
       <c r="G100" t="n">
         <v>0</v>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="n">
+        <v>99</v>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
@@ -6942,7 +7140,9 @@
       <c r="G101" t="n">
         <v>0</v>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>100</v>
+      </c>
       <c r="I101" t="n">
         <v>12871</v>
       </c>
@@ -7008,7 +7208,9 @@
       <c r="G102" t="n">
         <v>0</v>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>101</v>
+      </c>
       <c r="I102" t="n">
         <v>9999</v>
       </c>
@@ -7074,7 +7276,9 @@
       <c r="G103" t="n">
         <v>0</v>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="n">
+        <v>102</v>
+      </c>
       <c r="I103" t="n">
         <v>12690</v>
       </c>
@@ -7140,7 +7344,9 @@
       <c r="G104" t="n">
         <v>0</v>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>103</v>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
@@ -7204,7 +7410,9 @@
       <c r="G105" t="n">
         <v>0</v>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>104</v>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
@@ -7268,7 +7476,9 @@
       <c r="G106" t="n">
         <v>0</v>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="n">
+        <v>105</v>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
@@ -7332,7 +7542,9 @@
       <c r="G107" t="n">
         <v>0</v>
       </c>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>106</v>
+      </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
@@ -7396,7 +7608,9 @@
       <c r="G108" t="n">
         <v>0</v>
       </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="n">
+        <v>107</v>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
@@ -7460,7 +7674,9 @@
       <c r="G109" t="n">
         <v>0</v>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="n">
+        <v>108</v>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
@@ -7524,7 +7740,9 @@
       <c r="G110" t="n">
         <v>0</v>
       </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="n">
+        <v>109</v>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
@@ -7588,7 +7806,9 @@
       <c r="G111" t="n">
         <v>0</v>
       </c>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="n">
+        <v>110</v>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
@@ -7652,7 +7872,9 @@
       <c r="G112" t="n">
         <v>0</v>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="n">
+        <v>111</v>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
@@ -7716,7 +7938,9 @@
       <c r="G113" t="n">
         <v>0</v>
       </c>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="n">
+        <v>112</v>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
@@ -7780,7 +8004,9 @@
       <c r="G114" t="n">
         <v>0</v>
       </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="n">
+        <v>113</v>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
@@ -7844,7 +8070,9 @@
       <c r="G115" t="n">
         <v>0</v>
       </c>
-      <c r="H115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>114</v>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
@@ -7908,7 +8136,9 @@
       <c r="G116" t="n">
         <v>0</v>
       </c>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="n">
+        <v>115</v>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
@@ -7972,7 +8202,9 @@
       <c r="G117" t="n">
         <v>0</v>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="n">
+        <v>116</v>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
@@ -8036,7 +8268,9 @@
       <c r="G118" t="n">
         <v>0</v>
       </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="n">
+        <v>117</v>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
@@ -8100,7 +8334,9 @@
       <c r="G119" t="n">
         <v>0</v>
       </c>
-      <c r="H119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>118</v>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
@@ -8164,7 +8400,9 @@
       <c r="G120" t="n">
         <v>0</v>
       </c>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="n">
+        <v>119</v>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
@@ -8228,7 +8466,9 @@
       <c r="G121" t="n">
         <v>0</v>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>120</v>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
@@ -8292,7 +8532,9 @@
       <c r="G122" t="n">
         <v>0</v>
       </c>
-      <c r="H122" t="inlineStr"/>
+      <c r="H122" t="n">
+        <v>121</v>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
@@ -8356,7 +8598,9 @@
       <c r="G123" t="n">
         <v>0</v>
       </c>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>122</v>
+      </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
@@ -8420,7 +8664,9 @@
       <c r="G124" t="n">
         <v>0</v>
       </c>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="n">
+        <v>123</v>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
@@ -8484,7 +8730,9 @@
       <c r="G125" t="n">
         <v>0</v>
       </c>
-      <c r="H125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>124</v>
+      </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
@@ -8548,7 +8796,9 @@
       <c r="G126" t="n">
         <v>0</v>
       </c>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="n">
+        <v>125</v>
+      </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
@@ -8618,7 +8868,9 @@
       <c r="G127" t="n">
         <v>0</v>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H127" t="n">
+        <v>126</v>
+      </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
@@ -8682,7 +8934,9 @@
       <c r="G128" t="n">
         <v>0</v>
       </c>
-      <c r="H128" t="inlineStr"/>
+      <c r="H128" t="n">
+        <v>127</v>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
@@ -8746,7 +9000,9 @@
       <c r="G129" t="n">
         <v>0</v>
       </c>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>128</v>
+      </c>
       <c r="I129" t="n">
         <v>11877</v>
       </c>
@@ -8812,7 +9068,9 @@
       <c r="G130" t="n">
         <v>0</v>
       </c>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="n">
+        <v>129</v>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
@@ -8864,7 +9122,9 @@
       <c r="G131" t="n">
         <v>0</v>
       </c>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="n">
+        <v>130</v>
+      </c>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
@@ -8916,7 +9176,9 @@
       <c r="G132" t="n">
         <v>0</v>
       </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="n">
+        <v>131</v>
+      </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
@@ -8980,7 +9242,9 @@
       <c r="G133" t="n">
         <v>0</v>
       </c>
-      <c r="H133" t="inlineStr"/>
+      <c r="H133" t="n">
+        <v>132</v>
+      </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
@@ -9044,7 +9308,9 @@
       <c r="G134" t="n">
         <v>0</v>
       </c>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="n">
+        <v>133</v>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
@@ -9108,7 +9374,9 @@
       <c r="G135" t="n">
         <v>0</v>
       </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="n">
+        <v>134</v>
+      </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
@@ -9172,7 +9440,9 @@
       <c r="G136" t="n">
         <v>0</v>
       </c>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="n">
+        <v>135</v>
+      </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
@@ -9236,7 +9506,9 @@
       <c r="G137" t="n">
         <v>0</v>
       </c>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="n">
+        <v>136</v>
+      </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
@@ -9300,7 +9572,9 @@
       <c r="G138" t="n">
         <v>0</v>
       </c>
-      <c r="H138" t="inlineStr"/>
+      <c r="H138" t="n">
+        <v>137</v>
+      </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
@@ -9364,7 +9638,9 @@
       <c r="G139" t="n">
         <v>0</v>
       </c>
-      <c r="H139" t="inlineStr"/>
+      <c r="H139" t="n">
+        <v>138</v>
+      </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
@@ -9428,7 +9704,9 @@
       <c r="G140" t="n">
         <v>0</v>
       </c>
-      <c r="H140" t="inlineStr"/>
+      <c r="H140" t="n">
+        <v>139</v>
+      </c>
       <c r="I140" t="n">
         <v>12054</v>
       </c>
@@ -9500,7 +9778,9 @@
       <c r="G141" t="n">
         <v>0</v>
       </c>
-      <c r="H141" t="inlineStr"/>
+      <c r="H141" t="n">
+        <v>140</v>
+      </c>
       <c r="I141" t="n">
         <v>12702</v>
       </c>
@@ -9566,7 +9846,9 @@
       <c r="G142" t="n">
         <v>0</v>
       </c>
-      <c r="H142" t="inlineStr"/>
+      <c r="H142" t="n">
+        <v>141</v>
+      </c>
       <c r="I142" t="n">
         <v>12806</v>
       </c>
@@ -9638,7 +9920,9 @@
       <c r="G143" t="n">
         <v>0</v>
       </c>
-      <c r="H143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>142</v>
+      </c>
       <c r="I143" t="n">
         <v>12638</v>
       </c>
@@ -9710,7 +9994,9 @@
       <c r="G144" t="n">
         <v>0</v>
       </c>
-      <c r="H144" t="inlineStr"/>
+      <c r="H144" t="n">
+        <v>143</v>
+      </c>
       <c r="I144" t="n">
         <v>12568</v>
       </c>
@@ -9776,7 +10062,9 @@
       <c r="G145" t="n">
         <v>0</v>
       </c>
-      <c r="H145" t="inlineStr"/>
+      <c r="H145" t="n">
+        <v>144</v>
+      </c>
       <c r="I145" t="n">
         <v>12627</v>
       </c>
@@ -9842,7 +10130,9 @@
       <c r="G146" t="n">
         <v>0</v>
       </c>
-      <c r="H146" t="inlineStr"/>
+      <c r="H146" t="n">
+        <v>145</v>
+      </c>
       <c r="I146" t="n">
         <v>12146</v>
       </c>
@@ -9908,7 +10198,9 @@
       <c r="G147" t="n">
         <v>0</v>
       </c>
-      <c r="H147" t="inlineStr"/>
+      <c r="H147" t="n">
+        <v>146</v>
+      </c>
       <c r="I147" t="n">
         <v>12400</v>
       </c>
@@ -9980,7 +10272,9 @@
       <c r="G148" t="n">
         <v>0</v>
       </c>
-      <c r="H148" t="inlineStr"/>
+      <c r="H148" t="n">
+        <v>147</v>
+      </c>
       <c r="I148" t="n">
         <v>12288</v>
       </c>
@@ -10052,7 +10346,9 @@
       <c r="G149" t="n">
         <v>0</v>
       </c>
-      <c r="H149" t="inlineStr"/>
+      <c r="H149" t="n">
+        <v>148</v>
+      </c>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
@@ -10116,7 +10412,9 @@
       <c r="G150" t="n">
         <v>0</v>
       </c>
-      <c r="H150" t="inlineStr"/>
+      <c r="H150" t="n">
+        <v>149</v>
+      </c>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
@@ -10180,7 +10478,9 @@
       <c r="G151" t="n">
         <v>0</v>
       </c>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="n">
+        <v>150</v>
+      </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
@@ -10244,7 +10544,9 @@
       <c r="G152" t="n">
         <v>0</v>
       </c>
-      <c r="H152" t="inlineStr"/>
+      <c r="H152" t="n">
+        <v>151</v>
+      </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
@@ -10308,7 +10610,9 @@
       <c r="G153" t="n">
         <v>0</v>
       </c>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="n">
+        <v>152</v>
+      </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
@@ -10372,7 +10676,9 @@
       <c r="G154" t="n">
         <v>0</v>
       </c>
-      <c r="H154" t="inlineStr"/>
+      <c r="H154" t="n">
+        <v>153</v>
+      </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
@@ -10436,7 +10742,9 @@
       <c r="G155" t="n">
         <v>0</v>
       </c>
-      <c r="H155" t="inlineStr"/>
+      <c r="H155" t="n">
+        <v>154</v>
+      </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
@@ -10500,7 +10808,9 @@
       <c r="G156" t="n">
         <v>0</v>
       </c>
-      <c r="H156" t="inlineStr"/>
+      <c r="H156" t="n">
+        <v>155</v>
+      </c>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
@@ -10564,7 +10874,9 @@
       <c r="G157" t="n">
         <v>0</v>
       </c>
-      <c r="H157" t="inlineStr"/>
+      <c r="H157" t="n">
+        <v>156</v>
+      </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
@@ -10628,7 +10940,9 @@
       <c r="G158" t="n">
         <v>0</v>
       </c>
-      <c r="H158" t="inlineStr"/>
+      <c r="H158" t="n">
+        <v>157</v>
+      </c>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
@@ -10692,7 +11006,9 @@
       <c r="G159" t="n">
         <v>0</v>
       </c>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="n">
+        <v>158</v>
+      </c>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
@@ -10756,7 +11072,9 @@
       <c r="G160" t="n">
         <v>0</v>
       </c>
-      <c r="H160" t="inlineStr"/>
+      <c r="H160" t="n">
+        <v>159</v>
+      </c>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
@@ -10820,7 +11138,9 @@
       <c r="G161" t="n">
         <v>0</v>
       </c>
-      <c r="H161" t="inlineStr"/>
+      <c r="H161" t="n">
+        <v>160</v>
+      </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
@@ -10884,7 +11204,9 @@
       <c r="G162" t="n">
         <v>0</v>
       </c>
-      <c r="H162" t="inlineStr"/>
+      <c r="H162" t="n">
+        <v>161</v>
+      </c>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
@@ -10948,7 +11270,9 @@
       <c r="G163" t="n">
         <v>0</v>
       </c>
-      <c r="H163" t="inlineStr"/>
+      <c r="H163" t="n">
+        <v>162</v>
+      </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
@@ -11012,7 +11336,9 @@
       <c r="G164" t="n">
         <v>0</v>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="H164" t="n">
+        <v>163</v>
+      </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
@@ -11076,7 +11402,9 @@
       <c r="G165" t="n">
         <v>0</v>
       </c>
-      <c r="H165" t="inlineStr"/>
+      <c r="H165" t="n">
+        <v>164</v>
+      </c>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
@@ -11140,7 +11468,9 @@
       <c r="G166" t="n">
         <v>0</v>
       </c>
-      <c r="H166" t="inlineStr"/>
+      <c r="H166" t="n">
+        <v>165</v>
+      </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X166"/>
+  <dimension ref="A1:X167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4823,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5839492</v>
+        <v>4087644</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -5251,10 +5251,10 @@
         <v>451</v>
       </c>
       <c r="D73" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E73" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
@@ -5265,17 +5265,15 @@
       <c r="H73" t="n">
         <v>72</v>
       </c>
-      <c r="I73" t="n">
-        <v>11140</v>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
+          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5287,19 +5285,19 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>300000</v>
+        <v>11755000</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -5313,16 +5311,16 @@
         <v>1301</v>
       </c>
       <c r="B74" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C74" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D74" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E74" t="n">
-        <v>4290</v>
+        <v>1038</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
@@ -5334,11 +5332,11 @@
         <v>73</v>
       </c>
       <c r="I74" t="n">
-        <v>12510</v>
+        <v>11140</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
+          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5360,14 +5358,14 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>40000000</v>
+        <v>300000</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -5381,16 +5379,16 @@
         <v>1301</v>
       </c>
       <c r="B75" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C75" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D75" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E75" t="n">
-        <v>1036</v>
+        <v>4290</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
@@ -5402,11 +5400,11 @@
         <v>74</v>
       </c>
       <c r="I75" t="n">
-        <v>12453</v>
+        <v>12510</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
+          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5423,19 +5421,19 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>539924</v>
+        <v>40000000</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -5470,11 +5468,11 @@
         <v>75</v>
       </c>
       <c r="I76" t="n">
-        <v>12454</v>
+        <v>12453</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
+          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5496,14 +5494,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>15337533</v>
+        <v>539924</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -5538,11 +5536,11 @@
         <v>76</v>
       </c>
       <c r="I77" t="n">
-        <v>11521</v>
+        <v>12454</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5559,19 +5557,19 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>SABARÁ</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1440021</v>
+        <v>15337533</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -5606,11 +5604,11 @@
         <v>77</v>
       </c>
       <c r="I78" t="n">
-        <v>11519</v>
+        <v>11521</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5627,19 +5625,19 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>SABARÁ</t>
         </is>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>6942767</v>
+        <v>1440021</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -5674,16 +5672,16 @@
         <v>78</v>
       </c>
       <c r="I79" t="n">
-        <v>11512</v>
+        <v>11519</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
+          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -5700,14 +5698,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>14686005</v>
+        <v>6942767</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
@@ -5742,16 +5740,16 @@
         <v>79</v>
       </c>
       <c r="I80" t="n">
-        <v>11514</v>
+        <v>11512</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
+          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -5763,19 +5761,19 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>52160376</v>
+        <v>14686005</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
@@ -5810,11 +5808,11 @@
         <v>80</v>
       </c>
       <c r="I81" t="n">
-        <v>11511</v>
+        <v>11514</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
+          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5831,19 +5829,19 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>20521500</v>
+        <v>52160376</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
@@ -5878,11 +5876,11 @@
         <v>81</v>
       </c>
       <c r="I82" t="n">
-        <v>11520</v>
+        <v>11511</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5899,19 +5897,19 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>SANTA LUZIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>6952445</v>
+        <v>20521500</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
@@ -5946,11 +5944,11 @@
         <v>82</v>
       </c>
       <c r="I83" t="n">
-        <v>11513</v>
+        <v>11520</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
+          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5967,19 +5965,19 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SANTA LUZIA</t>
         </is>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>12959175</v>
+        <v>6952445</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
@@ -6014,11 +6012,11 @@
         <v>83</v>
       </c>
       <c r="I84" t="n">
-        <v>11977</v>
+        <v>11513</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6035,19 +6033,19 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>CATAGUASES</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>38244490</v>
+        <v>12959175</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
@@ -6058,38 +6056,40 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C85" t="n">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="D85" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E85" t="n">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>84</v>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>11977</v>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
+          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6101,19 +6101,19 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CATAGUASES</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>904245</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>62970566</v>
+        <v>38244490</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
@@ -6130,13 +6130,13 @@
         <v>6</v>
       </c>
       <c r="C86" t="n">
-        <v>243</v>
+        <v>421</v>
       </c>
       <c r="D86" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E86" t="n">
-        <v>4441</v>
+        <v>1048</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -6150,7 +6150,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6167,19 +6167,19 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>904245</v>
       </c>
       <c r="R86" t="n">
-        <v>6999284</v>
+        <v>62970566</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
@@ -6238,14 +6238,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>6999284</v>
       </c>
       <c r="R87" t="n">
-        <v>651694</v>
+        <v>0</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
@@ -6299,19 +6299,19 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>ALFENAS</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>651694</v>
       </c>
       <c r="R88" t="n">
-        <v>651694</v>
+        <v>0</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
@@ -6365,19 +6365,19 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ALFENAS</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>651694</v>
       </c>
       <c r="R89" t="n">
-        <v>1472757</v>
+        <v>0</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
@@ -6431,19 +6431,19 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>1472757</v>
       </c>
       <c r="R90" t="n">
-        <v>651694</v>
+        <v>0</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
@@ -6454,25 +6454,25 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C91" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D91" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E91" t="n">
-        <v>4476</v>
+        <v>4441</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>90</v>
@@ -6480,12 +6480,12 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -6497,16 +6497,16 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>270000</v>
+        <v>651694</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -6529,10 +6529,10 @@
         <v>122</v>
       </c>
       <c r="D92" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E92" t="n">
-        <v>4465</v>
+        <v>4476</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -6546,7 +6546,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>1100000</v>
+        <v>270000</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
+          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>624000</v>
+        <v>1100000</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
+          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>210000</v>
+        <v>624000</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -6744,7 +6744,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
+          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>150000</v>
+        <v>210000</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
@@ -6810,7 +6810,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
+          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>3918408</v>
+        <v>150000</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
@@ -6859,10 +6859,10 @@
         <v>122</v>
       </c>
       <c r="D97" t="n">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="E97" t="n">
-        <v>2500</v>
+        <v>4465</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
@@ -6876,7 +6876,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
+          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6884,17 +6884,11 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M97" t="n">
-        <v>1</v>
-      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -6908,7 +6902,7 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>282000</v>
+        <v>3918408</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
@@ -6922,19 +6916,19 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="B98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C98" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D98" t="n">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="E98" t="n">
-        <v>1006</v>
+        <v>2500</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
@@ -6948,7 +6942,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
+          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6956,28 +6950,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>1</v>
+      </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>282000</v>
       </c>
       <c r="R98" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
         <v>32</v>
       </c>
       <c r="E99" t="n">
-        <v>4063</v>
+        <v>1006</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -7014,7 +7014,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
+          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7031,19 +7031,19 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>20000000</v>
+        <v>1000000</v>
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
@@ -7054,19 +7054,19 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1541</v>
+        <v>1511</v>
       </c>
       <c r="B100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C100" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="D100" t="n">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="E100" t="n">
-        <v>2500</v>
+        <v>4063</v>
       </c>
       <c r="F100" t="n">
         <v>1</v>
@@ -7080,12 +7080,12 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
+          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -7102,14 +7102,14 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>1393050</v>
+        <v>150000</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
@@ -7120,19 +7120,19 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2011</v>
+        <v>1541</v>
       </c>
       <c r="B101" t="n">
         <v>10</v>
       </c>
       <c r="C101" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D101" t="n">
-        <v>88</v>
+        <v>705</v>
       </c>
       <c r="E101" t="n">
-        <v>4231</v>
+        <v>2500</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -7143,17 +7143,15 @@
       <c r="H101" t="n">
         <v>100</v>
       </c>
-      <c r="I101" t="n">
-        <v>12871</v>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
+          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -7174,10 +7172,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>2896100</v>
       </c>
       <c r="R101" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
@@ -7212,11 +7210,11 @@
         <v>101</v>
       </c>
       <c r="I102" t="n">
-        <v>9999</v>
+        <v>12871</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
+          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7245,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>1600000</v>
+        <v>2000000</v>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -7262,13 +7260,13 @@
         <v>10</v>
       </c>
       <c r="C103" t="n">
-        <v>122</v>
+        <v>302</v>
       </c>
       <c r="D103" t="n">
-        <v>705</v>
+        <v>88</v>
       </c>
       <c r="E103" t="n">
-        <v>2500</v>
+        <v>4231</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -7280,11 +7278,11 @@
         <v>102</v>
       </c>
       <c r="I103" t="n">
-        <v>12690</v>
+        <v>9999</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
+          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -7313,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2200000</v>
+        <v>1600000</v>
       </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
@@ -7324,19 +7322,19 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2151</v>
+        <v>2011</v>
       </c>
       <c r="B104" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C104" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="D104" t="n">
-        <v>75</v>
+        <v>705</v>
       </c>
       <c r="E104" t="n">
-        <v>1023</v>
+        <v>2500</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
@@ -7347,10 +7345,12 @@
       <c r="H104" t="n">
         <v>103</v>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="n">
+        <v>12690</v>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
+          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7372,14 +7372,14 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2200000</v>
       </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
@@ -7396,13 +7396,13 @@
         <v>12</v>
       </c>
       <c r="C105" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="D105" t="n">
-        <v>705</v>
+        <v>75</v>
       </c>
       <c r="E105" t="n">
-        <v>2500</v>
+        <v>1023</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
@@ -7416,7 +7416,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
@@ -7456,19 +7456,19 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2301</v>
+        <v>2151</v>
       </c>
       <c r="B106" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C106" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D106" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E106" t="n">
-        <v>4268</v>
+        <v>2500</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -7482,7 +7482,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Reabilitação da MG-010 (Conceição do Mato Dentro a Serro)</t>
+          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7499,19 +7499,19 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="R106" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
@@ -7548,7 +7548,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Reabilitação da MG-129 (Ouro Preto a Ouro Branco)</t>
+          <t>Reabilitação da MG-010 (Conceição do Mato Dentro a Serro)</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7614,7 +7614,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Restauração Rodovia MG-010, trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso) e recomposição de Talude Erodido</t>
+          <t>Reabilitação da MG-129 (Ouro Preto a Ouro Branco)</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
@@ -7666,7 +7666,7 @@
         <v>81</v>
       </c>
       <c r="E109" t="n">
-        <v>4275</v>
+        <v>4268</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
@@ -7680,7 +7680,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pavimentação MG-326 (Ponte Nova a Barra Longa) </t>
+          <t>Restauração Rodovia MG-010, trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso) e recomposição de Talude Erodido</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7709,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>82286724</v>
+        <v>10000000</v>
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
@@ -7746,7 +7746,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Pavimentação da MG-314 (Entr. MG-416 (Peçanha) a LMG-744 (Coroaci) Entr. Virgolândia)</t>
+          <t xml:space="preserve">Pavimentação MG-326 (Ponte Nova a Barra Longa) </t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7775,7 +7775,7 @@
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>22137718</v>
+        <v>82286724</v>
       </c>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
@@ -7812,7 +7812,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Pavimentação da Rodovia Municipal (Santa Rita do Itueto a Entr. BR-259 (Resplendor))</t>
+          <t>Pavimentação da MG-314 (Entr. MG-416 (Peçanha) a LMG-744 (Coroaci) Entr. Virgolândia)</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7841,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>21757581</v>
+        <v>22137718</v>
       </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
@@ -7878,7 +7878,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Rodovia MG-010, trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso), com extensão de 21,80 Km</t>
+          <t>Pavimentação da Rodovia Municipal (Santa Rita do Itueto a Entr. BR-259 (Resplendor))</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7907,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>8036364</v>
+        <v>21757581</v>
       </c>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
@@ -7944,7 +7944,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros (Distrito) - Entrº MG-181 (Estaca 1250 a 2000)</t>
+          <t>Rodovia MG-010, trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso), com extensão de 21,80 Km</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>14063636</v>
+        <v>8036364</v>
       </c>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
@@ -8010,7 +8010,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Rodovia MG-10 - Trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso), com extensão de 22,50 km</t>
+          <t>Trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros (Distrito) - Entrº MG-181 (Estaca 1250 a 2000)</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -8039,7 +8039,7 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>8100000</v>
+        <v>14063636</v>
       </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
@@ -8076,7 +8076,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Contorno de Andradas</t>
+          <t>Rodovia MG-10 - Trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso), com extensão de 22,50 km</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>4804860</v>
+        <v>8100000</v>
       </c>
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
@@ -8142,7 +8142,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Empreendimento em definição junto ao Banco do Brasil - Contrato de Financiamento nº 20/00020-0 (PDMG)</t>
+          <t>Melhoramento e pavimentação do Contorno de Andradas</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>6000001</v>
+        <v>4804860</v>
       </c>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
@@ -8194,7 +8194,7 @@
         <v>81</v>
       </c>
       <c r="E117" t="n">
-        <v>4287</v>
+        <v>4275</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -8208,7 +8208,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t>Empreendimento em definição junto ao Banco do Brasil - Contrato de Financiamento nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8234,10 +8234,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>6000001</v>
       </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
@@ -8260,7 +8260,7 @@
         <v>81</v>
       </c>
       <c r="E118" t="n">
-        <v>4289</v>
+        <v>4287</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -8274,7 +8274,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8326,7 +8326,7 @@
         <v>81</v>
       </c>
       <c r="E119" t="n">
-        <v>4293</v>
+        <v>4289</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -8340,7 +8340,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>04ª URG Barbacena</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R119" t="n">
-        <v>13000000</v>
+        <v>0</v>
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
@@ -8406,7 +8406,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>20ª URG Formiga</t>
+          <t>04ª URG Barbacena</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>13000000</v>
+        <v>12870000</v>
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
@@ -8472,7 +8472,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>28ª URG Teófilo Otoni</t>
+          <t>20ª URG Formiga</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8501,7 +8501,7 @@
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>9671783</v>
+        <v>12870000</v>
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>30ª URG Juiz de Fora</t>
+          <t>28ª URG Teófilo Otoni</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8567,7 +8567,7 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>12500000</v>
+        <v>9575065</v>
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
@@ -8604,7 +8604,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>01ª URG Belo Horizonte - Sul</t>
+          <t>30ª URG Juiz de Fora</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>15000000</v>
+        <v>12375000</v>
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
@@ -8670,7 +8670,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>01ª URG Belo Horizonte - Norte</t>
+          <t>01ª URG Belo Horizonte - Sul</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8699,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>15000000</v>
+        <v>14850000</v>
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
@@ -8736,7 +8736,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>31ª URG Ituiutaba</t>
+          <t>01ª URG Belo Horizonte - Norte</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8765,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>10000000</v>
+        <v>14850000</v>
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
@@ -8776,19 +8776,19 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="B126" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C126" t="n">
-        <v>363</v>
+        <v>782</v>
       </c>
       <c r="D126" t="n">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="E126" t="n">
-        <v>4006</v>
+        <v>4293</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -8802,42 +8802,36 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t>31ª URG Ituiutaba</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>METRO QUADRADO</t>
-        </is>
-      </c>
-      <c r="M126" t="n">
-        <v>5000</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>9900000</v>
       </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
@@ -8848,19 +8842,19 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2321</v>
+        <v>2311</v>
       </c>
       <c r="B127" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="D127" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="E127" t="n">
-        <v>4222</v>
+        <v>4006</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
@@ -8874,33 +8868,39 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>5000</v>
+      </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>800291</v>
+        <v>5000000</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -8962,11 +8962,11 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>174673</v>
+        <v>800291</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
@@ -9003,17 +9003,15 @@
       <c r="H129" t="n">
         <v>128</v>
       </c>
-      <c r="I129" t="n">
-        <v>11877</v>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -9025,16 +9023,16 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>1088908</v>
+        <v>174673</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -9048,19 +9046,19 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2361</v>
+        <v>2321</v>
       </c>
       <c r="B130" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C130" t="n">
-        <v>846</v>
+        <v>302</v>
       </c>
       <c r="D130" t="n">
-        <v>705</v>
+        <v>87</v>
       </c>
       <c r="E130" t="n">
-        <v>7004</v>
+        <v>4222</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -9071,10 +9069,12 @@
       <c r="H130" t="n">
         <v>129</v>
       </c>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="n">
+        <v>11877</v>
+      </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -9089,10 +9089,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Barbacena</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>SÃO JOÃO DEL REI</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>1088908</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
@@ -9105,16 +9117,16 @@
         <v>2361</v>
       </c>
       <c r="B131" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C131" t="n">
-        <v>274</v>
+        <v>846</v>
       </c>
       <c r="D131" t="n">
-        <v>766</v>
+        <v>705</v>
       </c>
       <c r="E131" t="n">
-        <v>2113</v>
+        <v>7004</v>
       </c>
       <c r="F131" t="n">
         <v>1</v>
@@ -9165,10 +9177,10 @@
         <v>274</v>
       </c>
       <c r="D132" t="n">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E132" t="n">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -9182,7 +9194,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -9197,22 +9209,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>2754406</v>
-      </c>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
@@ -9222,19 +9222,19 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2371</v>
+        <v>2361</v>
       </c>
       <c r="B133" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C133" t="n">
-        <v>609</v>
+        <v>274</v>
       </c>
       <c r="D133" t="n">
-        <v>78</v>
+        <v>767</v>
       </c>
       <c r="E133" t="n">
-        <v>4238</v>
+        <v>2114</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
@@ -9248,7 +9248,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9274,10 +9274,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>8311374</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>2754406</v>
       </c>
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
@@ -9288,19 +9288,19 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2421</v>
+        <v>2371</v>
       </c>
       <c r="B134" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C134" t="n">
-        <v>544</v>
+        <v>609</v>
       </c>
       <c r="D134" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="E134" t="n">
-        <v>1016</v>
+        <v>4238</v>
       </c>
       <c r="F134" t="n">
         <v>1</v>
@@ -9314,7 +9314,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Implantação de Sistemas de Abastecimento de Água e instalação de kits fotovoltaicos em poços artesianos conforme demanda da sociedade</t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -9331,16 +9331,16 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>477508</v>
+        <v>8311374</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -9354,19 +9354,19 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>3051</v>
+        <v>2421</v>
       </c>
       <c r="B135" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C135" t="n">
-        <v>364</v>
+        <v>544</v>
       </c>
       <c r="D135" t="n">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="E135" t="n">
-        <v>4016</v>
+        <v>1016</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
@@ -9380,7 +9380,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t>Implantação de Sistemas de Abastecimento de Água e instalação de kits fotovoltaicos em poços artesianos conforme demanda da sociedade</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>4825656</v>
+        <v>477508</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>12649000</v>
+        <v>4825656</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
@@ -9512,7 +9512,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>3715000</v>
+        <v>12649000</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
@@ -9555,16 +9555,16 @@
         <v>3051</v>
       </c>
       <c r="B138" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C138" t="n">
-        <v>571</v>
+        <v>364</v>
       </c>
       <c r="D138" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E138" t="n">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="F138" t="n">
         <v>1</v>
@@ -9578,7 +9578,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Melhoria da infraestrutura da pesquisa.</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3715000</v>
       </c>
       <c r="R138" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
@@ -9644,7 +9644,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t>Melhoria da infraestrutura da pesquisa.</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9684,19 +9684,19 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B140" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C140" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D140" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E140" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -9707,30 +9707,22 @@
       <c r="H140" t="n">
         <v>139</v>
       </c>
-      <c r="I140" t="n">
-        <v>12054</v>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M140" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -9747,7 +9739,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>10431496</v>
+        <v>250000</v>
       </c>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
@@ -9782,11 +9774,11 @@
         <v>140</v>
       </c>
       <c r="I141" t="n">
-        <v>12702</v>
+        <v>12054</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>CINCÃO - Fornecimento e montagem de estante tipo porta-paletes e de planos metálicos para os armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente do TRIBUNAL</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9794,28 +9786,34 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M141" t="n">
+        <v>1</v>
+      </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>102247</v>
+        <v>10431496</v>
       </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
@@ -9850,11 +9848,11 @@
         <v>141</v>
       </c>
       <c r="I142" t="n">
-        <v>12806</v>
+        <v>12702</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t>CINCÃO - Fornecimento e montagem de estante tipo porta-paletes e de planos metálicos para os armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente do TRIBUNAL</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9862,34 +9860,28 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M142" t="n">
-        <v>1</v>
-      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>19560087</v>
+        <v>102247</v>
       </c>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
@@ -9924,11 +9916,11 @@
         <v>142</v>
       </c>
       <c r="I143" t="n">
-        <v>12638</v>
+        <v>12806</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9998,11 +9990,11 @@
         <v>143</v>
       </c>
       <c r="I144" t="n">
-        <v>12568</v>
+        <v>12638</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Itabirito/MG.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -10010,11 +10002,17 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M144" t="n">
+        <v>1</v>
+      </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -10031,7 +10029,7 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>5550000</v>
+        <v>19560087</v>
       </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
@@ -10066,11 +10064,11 @@
         <v>144</v>
       </c>
       <c r="I145" t="n">
-        <v>12627</v>
+        <v>12568</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Itabirito/MG.</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10087,19 +10085,19 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>4000000</v>
+        <v>5550000</v>
       </c>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
@@ -10134,11 +10132,11 @@
         <v>145</v>
       </c>
       <c r="I146" t="n">
-        <v>12146</v>
+        <v>12627</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -10167,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>13121711</v>
+        <v>4000000</v>
       </c>
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="inlineStr"/>
@@ -10202,11 +10200,11 @@
         <v>146</v>
       </c>
       <c r="I147" t="n">
-        <v>12400</v>
+        <v>12146</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -10214,34 +10212,28 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M147" t="n">
-        <v>1</v>
-      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>18431199</v>
+        <v>13121711</v>
       </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
@@ -10276,11 +10268,11 @@
         <v>147</v>
       </c>
       <c r="I148" t="n">
-        <v>12288</v>
+        <v>12400</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10315,7 +10307,7 @@
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>1950000</v>
+        <v>18431199</v>
       </c>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
@@ -10326,19 +10318,19 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>5011</v>
+        <v>4031</v>
       </c>
       <c r="B149" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C149" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="D149" t="n">
-        <v>133</v>
+        <v>706</v>
       </c>
       <c r="E149" t="n">
-        <v>3017</v>
+        <v>2091</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
@@ -10349,22 +10341,30 @@
       <c r="H149" t="n">
         <v>148</v>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="n">
+        <v>12288</v>
+      </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M149" t="n">
+        <v>1</v>
+      </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -10381,7 +10381,7 @@
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>800000</v>
+        <v>1950000</v>
       </c>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
@@ -10392,19 +10392,19 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>5031</v>
+        <v>5011</v>
       </c>
       <c r="B150" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C150" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="D150" t="n">
         <v>133</v>
       </c>
       <c r="E150" t="n">
-        <v>3015</v>
+        <v>3017</v>
       </c>
       <c r="F150" t="n">
         <v>1</v>
@@ -10418,7 +10418,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10447,7 +10447,7 @@
         <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>4782988</v>
+        <v>800000</v>
       </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
@@ -10458,19 +10458,19 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>5141</v>
+        <v>5031</v>
       </c>
       <c r="B151" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C151" t="n">
-        <v>126</v>
+        <v>572</v>
       </c>
       <c r="D151" t="n">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="E151" t="n">
-        <v>6006</v>
+        <v>3015</v>
       </c>
       <c r="F151" t="n">
         <v>1</v>
@@ -10484,7 +10484,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10513,7 +10513,7 @@
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>16317109</v>
+        <v>4782988</v>
       </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
@@ -10524,19 +10524,19 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>5391</v>
+        <v>5141</v>
       </c>
       <c r="B152" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C152" t="n">
-        <v>752</v>
+        <v>126</v>
       </c>
       <c r="D152" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="E152" t="n">
-        <v>3004</v>
+        <v>6006</v>
       </c>
       <c r="F152" t="n">
         <v>1</v>
@@ -10550,7 +10550,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10567,19 +10567,19 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>92004926</v>
+        <v>16317109</v>
       </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
@@ -10633,19 +10633,19 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>10705994</v>
+        <v>92004926</v>
       </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
@@ -10699,19 +10699,19 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>10464844</v>
+        <v>10705994</v>
       </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
@@ -10765,19 +10765,19 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>2098278</v>
+        <v>10464844</v>
       </c>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
@@ -10831,19 +10831,19 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>96721858</v>
+        <v>2098278</v>
       </c>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
@@ -10897,19 +10897,19 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>16415074</v>
+        <v>96721858</v>
       </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
@@ -10963,19 +10963,19 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>1</v>
+        <v>16415074</v>
       </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
@@ -10998,7 +10998,7 @@
         <v>92</v>
       </c>
       <c r="E159" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F159" t="n">
         <v>1</v>
@@ -11012,7 +11012,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -11029,19 +11029,19 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>126817302</v>
+        <v>1</v>
       </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
@@ -11095,19 +11095,19 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>16058991</v>
+        <v>126817302</v>
       </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
@@ -11161,19 +11161,19 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>65795530</v>
+        <v>16058991</v>
       </c>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
@@ -11227,19 +11227,19 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>44156794</v>
+        <v>65795530</v>
       </c>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
@@ -11293,19 +11293,19 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>140716908</v>
+        <v>44156794</v>
       </c>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
@@ -11359,19 +11359,19 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>8715687</v>
+        <v>140716908</v>
       </c>
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
@@ -11425,19 +11425,19 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>24622611</v>
+        <v>8715687</v>
       </c>
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
@@ -11457,10 +11457,10 @@
         <v>752</v>
       </c>
       <c r="D166" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E166" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
@@ -11474,7 +11474,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Expansão do Sistema de Geração</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11491,19 +11491,19 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>1</v>
+        <v>24622611</v>
       </c>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
@@ -11512,6 +11512,72 @@
       <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr"/>
     </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B167" t="n">
+        <v>25</v>
+      </c>
+      <c r="C167" t="n">
+        <v>752</v>
+      </c>
+      <c r="D167" t="n">
+        <v>94</v>
+      </c>
+      <c r="E167" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>166</v>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Expansão do Sistema de Geração</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>1</v>
+      </c>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
+      <c r="W167" t="inlineStr"/>
+      <c r="X167" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X167"/>
+  <dimension ref="A1:X174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,33 +738,35 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="D5" t="n">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="E5" t="n">
-        <v>4519</v>
+        <v>2060</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>12876</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORÇO ESTRUTURAL, REFORMA E AMPLIAÇÃO - EE ABRE CAMPO</t>
+          <t>Adequação da estrutura física do NAIS/9ª RPM, visando ao atendimento dos requisitos necessários à regularização junto aos órgãos de controle, especialmente à Vigilância Sanitária e à Secretaria de Saúde</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -772,25 +774,31 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ABRE CAMPO</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380000</v>
+        <v>201022</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -804,33 +812,35 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="D6" t="n">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>4519</v>
+        <v>2060</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>12882</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>OBRA DE COMBATE A INCÊNDIO DE TODO O COMPLEXO E ACESSIBILIDADE NO CAMPUS GAMELEIRA - PRÉDIOS A,B,C,D (INCLUNDO MUSEU ESCOLA ANA MARIA CASASANTA PEIXOTO E MUSEU LEOPOLDO CATHOUD) E EE LEON RENAULT</t>
+          <t xml:space="preserve"> Projeto elétrico, hidráulico, esgoto, rede, serralheria (prateleiras) e arquitetônico para reforma do CAO/CODONT; Valor estimado: R$ 197.856,73.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -838,11 +848,17 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -856,7 +872,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>653600</v>
+        <v>197857</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -870,33 +886,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="D7" t="n">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="E7" t="n">
-        <v>4519</v>
+        <v>2060</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>12880</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE GETÚLIO VARGAS</t>
+          <t xml:space="preserve"> Projeto de reestruturação dos consultórios de roseta para linha;</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -904,11 +922,17 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -922,7 +946,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>332120</v>
+        <v>1929103</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -936,33 +960,35 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="E8" t="n">
-        <v>4519</v>
+        <v>2060</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>12881</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE JOSÉ BONIFÁCIO</t>
+          <t>Execução das obras de reestruturação dos consultórios de roseta para linha;</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -970,11 +996,17 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -988,7 +1020,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>1033600</v>
+        <v>1929103</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1028,7 +1060,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PROJETOS EXECUTIVOS PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
+          <t>OBRA PARA REFORÇO ESTRUTURAL, REFORMA E AMPLIAÇÃO - EE ABRE CAMPO</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1045,16 +1077,16 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ABRE CAMPO</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>59660</v>
+        <v>380000</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1094,7 +1126,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
+          <t>OBRA DE COMBATE A INCÊNDIO DE TODO O COMPLEXO E ACESSIBILIDADE NO CAMPUS GAMELEIRA - PRÉDIOS A,B,C,D (INCLUNDO MUSEU ESCOLA ANA MARIA CASASANTA PEIXOTO E MUSEU LEOPOLDO CATHOUD) E EE LEON RENAULT</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1120,7 +1152,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>83600</v>
+        <v>653600</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1160,7 +1192,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>OBRAS DE REFORMA GERAL EE PROF CAETANO AZEREDO</t>
+          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE GETÚLIO VARGAS</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1186,7 +1218,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>805600</v>
+        <v>332120</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1226,7 +1258,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>OBRA PARA REGULARIZAÇÃO DO PROCESSO DE SEGURANÇA CONTRA INCÊNDIO E PÂNICO (PSCIP), ADEQUAÇÃO À ACESSIBILIDADE EE PEDRO II</t>
+          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE JOSÉ BONIFÁCIO</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1252,7 +1284,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387600</v>
+        <v>1033600</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1292,7 +1324,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO (SOLUÇÃO DE PROBLEMAS ESTRUTURAIS) EE SANDOVAL AZEVEDO</t>
+          <t>PROJETOS EXECUTIVOS PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1318,7 +1350,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>251560</v>
+        <v>59660</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1358,7 +1390,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA GERAL/RESTAURAÇÃO (MENOS TELHADO DA CASA MODELO, MURO DE ARRIMO) EE SÃO RAFAEL</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1384,7 +1416,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>2121920</v>
+        <v>83600</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1424,7 +1456,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA - ESTRUTURA ESCOLA GUIGNARD UEMG</t>
+          <t>OBRAS DE REFORMA GERAL EE PROF CAETANO AZEREDO</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1450,7 +1482,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>1929640</v>
+        <v>805600</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1490,12 +1522,12 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>OBRAS DE REFORMA E RESTAURAÇÃO DOS PRÉDIOS INSTITUTO DE EDUCAÇÃO DE MINAS GERAIS - IEMG</t>
+          <t>OBRA PARA REGULARIZAÇÃO DO PROCESSO DE SEGURANÇA CONTRA INCÊNDIO E PÂNICO (PSCIP), ADEQUAÇÃO À ACESSIBILIDADE EE PEDRO II</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1516,7 +1548,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>3040000</v>
+        <v>387600</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1556,7 +1588,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA, DO PRÉDIO DO ANTIGO AUDITÓRIO DO CAMPUS DA SEE-  GAMELEIRA, PARA ABRIGAR A NOVA SEDE DA SRE MET B - SEDE DA SRE MET B - AUDITÓRIO GAMELEIRA</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO (SOLUÇÃO DE PROBLEMAS ESTRUTURAIS) EE SANDOVAL AZEVEDO</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1582,7 +1614,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>3025160</v>
+        <v>251560</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1622,7 +1654,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>OBRA  PARA REFORMA/RESTAURAÇÃO EE SÃO JOAQUIM</t>
+          <t>OBRA DE REFORMA GERAL/RESTAURAÇÃO (MENOS TELHADO DA CASA MODELO, MURO DE ARRIMO) EE SÃO RAFAEL</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1644,11 +1676,11 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONCEIÇÃO DO MATO DENTRO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>2105200</v>
+        <v>2121920</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1688,12 +1720,12 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>OBRA DE ESTRUTURA E OUTRAS, EM PRÉDIO TOMBADO</t>
+          <t>OBRA DE REFORMA - ESTRUTURA ESCOLA GUIGNARD UEMG</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1710,11 +1742,11 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CORDISBURGO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>260300</v>
+        <v>1929640</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -1754,12 +1786,12 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E SOLUÇÃO DE PROBLEMAS ESTRUTURAIS EE ODILON BEHRENS</t>
+          <t>OBRAS DE REFORMA E RESTAURAÇÃO DOS PRÉDIOS INSTITUTO DE EDUCAÇÃO DE MINAS GERAIS - IEMG</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1771,16 +1803,16 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>GUANHÃES</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>1705060</v>
+        <v>3040000</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -1820,7 +1852,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OBRA PARA SOLUÇÃO DE DESLIZAMENTO DE TERRA DE PARTE DO TALUDE E A RUPTURA DE PARTE DO MURO DIVISÓRIO INTERNO EE SELIM JOSÉ DE SALES</t>
+          <t>OBRA PARA REFORMA, DO PRÉDIO DO ANTIGO AUDITÓRIO DO CAMPUS DA SEE-  GAMELEIRA, PARA ABRIGAR A NOVA SEDE DA SRE MET B - SEDE DA SRE MET B - AUDITÓRIO GAMELEIRA</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1837,16 +1869,16 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>190000</v>
+        <v>3025160</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -1886,7 +1918,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>OBRAS PARA RESTAURAÇÃO DO PRÉDIO EE WENCESLAU BRAZ</t>
+          <t>OBRA  PARA REFORMA/RESTAURAÇÃO EE SÃO JOAQUIM</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1903,16 +1935,16 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ITAJUBÁ</t>
+          <t>CONCEIÇÃO DO MATO DENTRO</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>2420600</v>
+        <v>2105200</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -1952,12 +1984,12 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E CONTENÇÃO E ESTABILIDADE DE TALUDE E DO PRÉDIO EE SÃO JOSÉ</t>
+          <t>OBRA DE ESTRUTURA E OUTRAS, EM PRÉDIO TOMBADO</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1969,16 +2001,16 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>CORDISBURGO</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691600</v>
+        <v>260300</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2018,7 +2050,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE RAUL SOARES</t>
+          <t>OBRA PARA REFORMA E SOLUÇÃO DE PROBLEMAS ESTRUTURAIS EE ODILON BEHRENS</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2035,16 +2067,16 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>ARAGUARI</t>
+          <t>GUANHÃES</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>380000</v>
+        <v>1705060</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2084,12 +2116,12 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA GERAL E RESTAURAÇÃO EE AFONSO PENA</t>
+          <t xml:space="preserve"> OBRA PARA SOLUÇÃO DE DESLIZAMENTO DE TERRA DE PARTE DO TALUDE E A RUPTURA DE PARTE DO MURO DIVISÓRIO INTERNO EE SELIM JOSÉ DE SALES</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2101,16 +2133,16 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>1194340</v>
+        <v>190000</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2150,7 +2182,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE FRANCISCO SALES</t>
+          <t>OBRAS PARA RESTAURAÇÃO DO PRÉDIO EE WENCESLAU BRAZ</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2167,16 +2199,16 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407740</v>
+        <v>2420600</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2216,7 +2248,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO COMPLEMENTARES - UNIDADE I EE GOV MILTON CAMPOS</t>
+          <t>OBRA PARA REFORMA E CONTENÇÃO E ESTABILIDADE DE TALUDE E DO PRÉDIO EE SÃO JOSÉ</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2233,16 +2265,16 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>1102000</v>
+        <v>691600</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2282,7 +2314,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>OBRA PARA TALUDE E MURO EE PROFA MARIA AMÉLIA GUIMARÃES</t>
+          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE RAUL SOARES</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2299,16 +2331,16 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ARAGUARI</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>190000</v>
+        <v>380000</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2348,12 +2380,12 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO, CONSERVAÇÃO E PRESERVAÇÃO ANTIGA ESCOLA DE APRENDIZES MARINHEIROS E CASA DO COMANDANTE - FUCAM (EE PROFESSORA MARIETA AMORIM VIEIRA)</t>
+          <t>OBRA PARA REFORMA GERAL E RESTAURAÇÃO EE AFONSO PENA</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2365,16 +2397,16 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BURITIZEIRO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>235600</v>
+        <v>1194340</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2414,7 +2446,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ATENDIMENTOS ESCOLAS ESTADUAIS - CAIXAS ESCOLARES E CONVÊNIOS</t>
+          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE FRANCISCO SALES</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2431,16 +2463,16 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>250000000</v>
+        <v>407740</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2480,7 +2512,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO COMPLEMENTARES - UNIDADE I EE GOV MILTON CAMPOS</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2497,16 +2529,16 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>GUAPÉ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387600</v>
+        <v>1102000</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2546,7 +2578,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
+          <t>OBRA PARA TALUDE E MURO EE PROFA MARIA AMÉLIA GUIMARÃES</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2568,11 +2600,11 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>361760</v>
+        <v>190000</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2612,7 +2644,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
+          <t>RESTAURAÇÃO, CONSERVAÇÃO E PRESERVAÇÃO ANTIGA ESCOLA DE APRENDIZES MARINHEIROS E CASA DO COMANDANTE - FUCAM (EE PROFESSORA MARIETA AMORIM VIEIRA)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2629,16 +2661,16 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>BURITIZEIRO</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>218500</v>
+        <v>235600</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -2678,7 +2710,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
+          <t>ATENDIMENTOS ESCOLAS ESTADUAIS - CAIXAS ESCOLARES E CONVÊNIOS</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2695,16 +2727,16 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>1976000</v>
+        <v>250000000</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -2744,7 +2776,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
+          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2761,16 +2793,16 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>GUAPÉ</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>805600</v>
+        <v>387600</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -2810,7 +2842,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
+          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2832,11 +2864,11 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>760000</v>
+        <v>361760</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -2876,7 +2908,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
+          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2893,16 +2925,16 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>653600</v>
+        <v>218500</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -2942,12 +2974,12 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2959,16 +2991,16 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>1204600</v>
+        <v>1976000</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3008,7 +3040,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
+          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3025,16 +3057,16 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PATOS DE MINAS</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>1927740</v>
+        <v>805600</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3074,7 +3106,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
+          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3091,16 +3123,16 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>653600</v>
+        <v>760000</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3140,7 +3172,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3157,16 +3189,16 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>19000</v>
+        <v>653600</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3206,12 +3238,12 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
+          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3223,16 +3255,16 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>19000</v>
+        <v>1204600</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3272,7 +3304,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
+          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3294,11 +3326,11 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>MATUTINA</t>
+          <t>PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>1318600</v>
+        <v>1927740</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3338,12 +3370,12 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
+          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3360,7 +3392,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q44" t="n">
@@ -3404,7 +3436,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3426,7 +3458,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q45" t="n">
@@ -3470,7 +3502,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3487,12 +3519,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -3536,7 +3568,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
+          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3553,16 +3585,16 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>MATUTINA</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>760000</v>
+        <v>1318600</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -3602,12 +3634,12 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
+          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3619,16 +3651,16 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PARAOPEBA</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>19000</v>
+        <v>653600</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -3668,7 +3700,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
+          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3685,12 +3717,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PATROCÍNIO</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -3734,7 +3766,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
+          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3751,12 +3783,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PATROCÍNIO</t>
+          <t>NOVA ERA</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -3800,7 +3832,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
+          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3822,11 +3854,11 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PITANGUI</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434720</v>
+        <v>760000</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -3866,7 +3898,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
+          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3883,16 +3915,16 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO</t>
+          <t>PARAOPEBA</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>221160</v>
+        <v>19000</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -3932,7 +3964,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
+          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3949,16 +3981,16 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>PATROCÍNIO</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>1748000</v>
+        <v>19000</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -3998,7 +4030,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
+          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4015,16 +4047,16 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>PATROCÍNIO</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479560</v>
+        <v>19000</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -4064,7 +4096,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4081,16 +4113,16 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>UBÁ</t>
+          <t>PITANGUI</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>228000</v>
+        <v>434720</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -4130,12 +4162,12 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
+          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -4147,16 +4179,16 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>2552080</v>
+        <v>221160</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -4196,7 +4228,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
+          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4213,16 +4245,16 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>1386240</v>
+        <v>1748000</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -4262,7 +4294,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4279,16 +4311,16 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>1900000</v>
+        <v>479560</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -4328,7 +4360,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
+          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4345,16 +4377,16 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>UBÁ</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>1008140</v>
+        <v>228000</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -4394,12 +4426,12 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
+          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -4411,16 +4443,16 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>SERRO</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>380000</v>
+        <v>2552080</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -4460,7 +4492,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
+          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4477,16 +4509,16 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>228000</v>
+        <v>1386240</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -4526,7 +4558,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4543,16 +4575,16 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539600</v>
+        <v>1900000</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -4592,7 +4624,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
+          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4609,16 +4641,16 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>19000</v>
+        <v>1008140</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -4658,12 +4690,12 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
+          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4675,16 +4707,16 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>SERRO</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>2074800</v>
+        <v>380000</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -4698,40 +4730,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1301</v>
+        <v>1261</v>
       </c>
       <c r="B65" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C65" t="n">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="D65" t="n">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="E65" t="n">
-        <v>1037</v>
+        <v>4519</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>64</v>
       </c>
-      <c r="I65" t="n">
-        <v>12404</v>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4743,19 +4773,19 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>228000</v>
       </c>
       <c r="R65" t="n">
-        <v>519640</v>
+        <v>0</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -4766,40 +4796,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1301</v>
+        <v>1261</v>
       </c>
       <c r="B66" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C66" t="n">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="D66" t="n">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="E66" t="n">
-        <v>1037</v>
+        <v>4519</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>65</v>
       </c>
-      <c r="I66" t="n">
-        <v>12780</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4811,19 +4839,19 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>539600</v>
       </c>
       <c r="R66" t="n">
-        <v>4087644</v>
+        <v>0</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -4834,40 +4862,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1301</v>
+        <v>1261</v>
       </c>
       <c r="B67" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="D67" t="n">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="E67" t="n">
-        <v>1037</v>
+        <v>4519</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>66</v>
       </c>
-      <c r="I67" t="n">
-        <v>10397</v>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
+          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4879,19 +4905,19 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>IBERTIOGA</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="R67" t="n">
-        <v>19153735</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
@@ -4902,35 +4928,33 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1301</v>
+        <v>1261</v>
       </c>
       <c r="B68" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C68" t="n">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="D68" t="n">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="E68" t="n">
-        <v>1037</v>
+        <v>4519</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
         <v>67</v>
       </c>
-      <c r="I68" t="n">
-        <v>12850</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
+          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4947,19 +4971,19 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2074800</v>
       </c>
       <c r="R68" t="n">
-        <v>23943007</v>
+        <v>0</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
@@ -4994,11 +5018,11 @@
         <v>68</v>
       </c>
       <c r="I69" t="n">
-        <v>12634</v>
+        <v>12404</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
+          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5015,19 +5039,19 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>ITAPAGIPE</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>26593690</v>
+        <v>519640</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -5062,11 +5086,11 @@
         <v>69</v>
       </c>
       <c r="I70" t="n">
-        <v>12785</v>
+        <v>12780</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
+          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5083,19 +5107,19 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>ITURAMA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2870210</v>
+        <v>4087644</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -5130,11 +5154,11 @@
         <v>70</v>
       </c>
       <c r="I71" t="n">
-        <v>12824</v>
+        <v>10397</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
+          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5151,19 +5175,19 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>PARACATU</t>
+          <t>IBERTIOGA</t>
         </is>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>23280000</v>
+        <v>19153735</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -5198,11 +5222,11 @@
         <v>71</v>
       </c>
       <c r="I72" t="n">
-        <v>4716</v>
+        <v>12850</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
+          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5219,19 +5243,19 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>MONTE CARMELO</t>
+          <t>JABOTICATUBAS</t>
         </is>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>19100000</v>
+        <v>23943007</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -5265,15 +5289,17 @@
       <c r="H73" t="n">
         <v>72</v>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>12634</v>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
+          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5285,19 +5311,19 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>ITAPAGIPE</t>
         </is>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>11755000</v>
+        <v>26593690</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -5317,10 +5343,10 @@
         <v>451</v>
       </c>
       <c r="D74" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E74" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
@@ -5332,11 +5358,11 @@
         <v>73</v>
       </c>
       <c r="I74" t="n">
-        <v>11140</v>
+        <v>12785</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
+          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5353,19 +5379,19 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ITURAMA</t>
         </is>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>300000</v>
+        <v>2870210</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -5379,16 +5405,16 @@
         <v>1301</v>
       </c>
       <c r="B75" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C75" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D75" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="E75" t="n">
-        <v>4290</v>
+        <v>1037</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
@@ -5400,11 +5426,11 @@
         <v>74</v>
       </c>
       <c r="I75" t="n">
-        <v>12510</v>
+        <v>12824</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
+          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5421,19 +5447,19 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>PARACATU</t>
         </is>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>40000000</v>
+        <v>23280000</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -5453,10 +5479,10 @@
         <v>451</v>
       </c>
       <c r="D76" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E76" t="n">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
@@ -5468,11 +5494,11 @@
         <v>75</v>
       </c>
       <c r="I76" t="n">
-        <v>12453</v>
+        <v>4716</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
+          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5489,19 +5515,19 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>MONTE CARMELO</t>
         </is>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>539924</v>
+        <v>19100000</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -5521,10 +5547,10 @@
         <v>451</v>
       </c>
       <c r="D77" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E77" t="n">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
@@ -5535,17 +5561,15 @@
       <c r="H77" t="n">
         <v>76</v>
       </c>
-      <c r="I77" t="n">
-        <v>12454</v>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
+          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -5557,19 +5581,19 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>15337533</v>
+        <v>11755000</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -5589,10 +5613,10 @@
         <v>451</v>
       </c>
       <c r="D78" t="n">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="E78" t="n">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -5604,11 +5628,11 @@
         <v>77</v>
       </c>
       <c r="I78" t="n">
-        <v>11521</v>
+        <v>11140</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5630,14 +5654,14 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>SABARÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>1440021</v>
+        <v>300000</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -5651,16 +5675,16 @@
         <v>1301</v>
       </c>
       <c r="B79" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C79" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D79" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E79" t="n">
-        <v>1036</v>
+        <v>4290</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
@@ -5672,11 +5696,11 @@
         <v>78</v>
       </c>
       <c r="I79" t="n">
-        <v>11519</v>
+        <v>12510</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5693,19 +5717,19 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>6942767</v>
+        <v>40000000</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
@@ -5740,16 +5764,16 @@
         <v>79</v>
       </c>
       <c r="I80" t="n">
-        <v>11512</v>
+        <v>12453</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
+          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -5761,19 +5785,19 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>14686005</v>
+        <v>539924</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
@@ -5808,11 +5832,11 @@
         <v>80</v>
       </c>
       <c r="I81" t="n">
-        <v>11514</v>
+        <v>12454</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
+          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5829,19 +5853,19 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>52160376</v>
+        <v>15337533</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
@@ -5876,11 +5900,11 @@
         <v>81</v>
       </c>
       <c r="I82" t="n">
-        <v>11511</v>
+        <v>11521</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
+          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5897,19 +5921,19 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SABARÁ</t>
         </is>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>20521500</v>
+        <v>1440021</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
@@ -5944,11 +5968,11 @@
         <v>82</v>
       </c>
       <c r="I83" t="n">
-        <v>11520</v>
+        <v>11519</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5965,19 +5989,19 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>SANTA LUZIA</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>6952445</v>
+        <v>6942767</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
@@ -6012,16 +6036,16 @@
         <v>83</v>
       </c>
       <c r="I84" t="n">
-        <v>11513</v>
+        <v>11512</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
+          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6033,19 +6057,19 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>12959175</v>
+        <v>14686005</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
@@ -6080,11 +6104,11 @@
         <v>84</v>
       </c>
       <c r="I85" t="n">
-        <v>11977</v>
+        <v>11514</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6101,19 +6125,19 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>CATAGUASES</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>38244490</v>
+        <v>52160376</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
@@ -6124,38 +6148,40 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B86" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C86" t="n">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="D86" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E86" t="n">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>85</v>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>11511</v>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
+          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6176,10 +6202,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>904245</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>62970566</v>
+        <v>20521500</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
@@ -6190,38 +6216,40 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C87" t="n">
-        <v>243</v>
+        <v>451</v>
       </c>
       <c r="D87" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E87" t="n">
-        <v>4441</v>
+        <v>1036</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>86</v>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>11520</v>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6238,14 +6266,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>SANTA LUZIA</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>6999284</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>6952445</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
@@ -6256,38 +6284,40 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B88" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C88" t="n">
-        <v>243</v>
+        <v>451</v>
       </c>
       <c r="D88" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E88" t="n">
-        <v>4441</v>
+        <v>1036</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>87</v>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>11513</v>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -6299,19 +6329,19 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>651694</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>12959175</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
@@ -6322,38 +6352,40 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B89" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C89" t="n">
-        <v>243</v>
+        <v>451</v>
       </c>
       <c r="D89" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E89" t="n">
-        <v>4441</v>
+        <v>1036</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>88</v>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>11977</v>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -6365,19 +6397,19 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>ALFENAS</t>
+          <t>CATAGUASES</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>651694</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>38244490</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
@@ -6388,25 +6420,25 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1451</v>
+        <v>1371</v>
       </c>
       <c r="B90" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C90" t="n">
-        <v>243</v>
+        <v>511</v>
       </c>
       <c r="D90" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="E90" t="n">
-        <v>4441</v>
+        <v>4118</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>89</v>
@@ -6414,12 +6446,12 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Programa Água Doce - RIMC</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -6431,19 +6463,19 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>1472757</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>4547000</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
@@ -6454,25 +6486,25 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1451</v>
+        <v>1371</v>
       </c>
       <c r="B91" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C91" t="n">
-        <v>243</v>
+        <v>511</v>
       </c>
       <c r="D91" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="E91" t="n">
-        <v>4441</v>
+        <v>4118</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>90</v>
@@ -6480,12 +6512,12 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Programa Água Doce - RITO</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -6497,19 +6529,19 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651694</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4547000</v>
       </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
@@ -6520,25 +6552,25 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C92" t="n">
-        <v>122</v>
+        <v>421</v>
       </c>
       <c r="D92" t="n">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="E92" t="n">
-        <v>4476</v>
+        <v>1048</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
         <v>91</v>
@@ -6546,12 +6578,12 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -6563,19 +6595,19 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>270000</v>
+        <v>904245</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>44308050</v>
       </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
@@ -6586,25 +6618,25 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B93" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C93" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D93" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E93" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
         <v>92</v>
@@ -6612,12 +6644,12 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -6638,7 +6670,7 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>1100000</v>
+        <v>6999284</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
@@ -6652,25 +6684,25 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C94" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D94" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E94" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
         <v>93</v>
@@ -6678,12 +6710,12 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -6700,11 +6732,11 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>624000</v>
+        <v>651694</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -6718,25 +6750,25 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C95" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D95" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E95" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
         <v>94</v>
@@ -6744,12 +6776,12 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -6761,16 +6793,16 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ALFENAS</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>210000</v>
+        <v>651694</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
@@ -6784,25 +6816,25 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B96" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C96" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D96" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E96" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
         <v>95</v>
@@ -6810,12 +6842,12 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -6832,11 +6864,11 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>150000</v>
+        <v>1472757</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
@@ -6850,25 +6882,25 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C97" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D97" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E97" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
         <v>96</v>
@@ -6876,12 +6908,12 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -6893,16 +6925,16 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>3918408</v>
+        <v>651694</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
@@ -6916,25 +6948,25 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C98" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D98" t="n">
-        <v>705</v>
+        <v>146</v>
       </c>
       <c r="E98" t="n">
-        <v>2500</v>
+        <v>4441</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
         <v>97</v>
@@ -6942,39 +6974,33 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M98" t="n">
-        <v>1</v>
-      </c>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>282000</v>
+        <v>18572878</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
@@ -6988,19 +7014,19 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="B99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C99" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D99" t="n">
-        <v>32</v>
+        <v>147</v>
       </c>
       <c r="E99" t="n">
-        <v>1006</v>
+        <v>4476</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -7014,7 +7040,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7031,19 +7057,19 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="R99" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
@@ -7054,19 +7080,19 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="B100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C100" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D100" t="n">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="E100" t="n">
-        <v>4063</v>
+        <v>4465</v>
       </c>
       <c r="F100" t="n">
         <v>1</v>
@@ -7080,7 +7106,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
+          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7102,14 +7128,14 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>150000</v>
+        <v>1100000</v>
       </c>
       <c r="R100" t="n">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
@@ -7120,19 +7146,19 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1541</v>
+        <v>1501</v>
       </c>
       <c r="B101" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C101" t="n">
         <v>122</v>
       </c>
       <c r="D101" t="n">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="E101" t="n">
-        <v>2500</v>
+        <v>4465</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -7146,12 +7172,12 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
+          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -7172,7 +7198,7 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>2896100</v>
+        <v>624000</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -7186,19 +7212,19 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2011</v>
+        <v>1501</v>
       </c>
       <c r="B102" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C102" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D102" t="n">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="E102" t="n">
-        <v>4231</v>
+        <v>4465</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
@@ -7209,12 +7235,10 @@
       <c r="H102" t="n">
         <v>101</v>
       </c>
-      <c r="I102" t="n">
-        <v>12871</v>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
+          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7240,10 +7264,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="R102" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -7254,19 +7278,19 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2011</v>
+        <v>1501</v>
       </c>
       <c r="B103" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D103" t="n">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="E103" t="n">
-        <v>4231</v>
+        <v>4465</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -7277,12 +7301,10 @@
       <c r="H103" t="n">
         <v>102</v>
       </c>
-      <c r="I103" t="n">
-        <v>9999</v>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
+          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -7308,10 +7330,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="R103" t="n">
-        <v>1600000</v>
+        <v>0</v>
       </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
@@ -7322,19 +7344,19 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2011</v>
+        <v>1501</v>
       </c>
       <c r="B104" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C104" t="n">
         <v>122</v>
       </c>
       <c r="D104" t="n">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="E104" t="n">
-        <v>2500</v>
+        <v>4465</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
@@ -7345,12 +7367,10 @@
       <c r="H104" t="n">
         <v>103</v>
       </c>
-      <c r="I104" t="n">
-        <v>12690</v>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
+          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7376,10 +7396,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3918408</v>
       </c>
       <c r="R104" t="n">
-        <v>2200000</v>
+        <v>0</v>
       </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
@@ -7390,19 +7410,19 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2151</v>
+        <v>1501</v>
       </c>
       <c r="B105" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="D105" t="n">
-        <v>75</v>
+        <v>705</v>
       </c>
       <c r="E105" t="n">
-        <v>1023</v>
+        <v>2500</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
@@ -7416,7 +7436,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
+          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -7424,11 +7444,17 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>1</v>
+      </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7438,11 +7464,11 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>200000</v>
+        <v>282000</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
@@ -7456,19 +7482,19 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2151</v>
+        <v>1511</v>
       </c>
       <c r="B106" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C106" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="D106" t="n">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="E106" t="n">
-        <v>2500</v>
+        <v>1006</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -7482,7 +7508,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
+          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7499,19 +7525,19 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
@@ -7522,19 +7548,19 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2301</v>
+        <v>1511</v>
       </c>
       <c r="B107" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C107" t="n">
-        <v>782</v>
+        <v>181</v>
       </c>
       <c r="D107" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="E107" t="n">
-        <v>4268</v>
+        <v>4063</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
@@ -7548,7 +7574,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Reabilitação da MG-010 (Conceição do Mato Dentro a Serro)</t>
+          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7565,19 +7591,19 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="R107" t="n">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
@@ -7588,19 +7614,19 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2301</v>
+        <v>1541</v>
       </c>
       <c r="B108" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C108" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D108" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E108" t="n">
-        <v>4268</v>
+        <v>2500</v>
       </c>
       <c r="F108" t="n">
         <v>1</v>
@@ -7614,12 +7640,12 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Reabilitação da MG-129 (Ouro Preto a Ouro Branco)</t>
+          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -7631,19 +7657,19 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2896100</v>
       </c>
       <c r="R108" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
@@ -7654,19 +7680,19 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2301</v>
+        <v>2011</v>
       </c>
       <c r="B109" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C109" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D109" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E109" t="n">
-        <v>4268</v>
+        <v>4231</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
@@ -7677,10 +7703,12 @@
       <c r="H109" t="n">
         <v>108</v>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="n">
+        <v>12871</v>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Restauração Rodovia MG-010, trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso) e recomposição de Talude Erodido</t>
+          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7697,19 +7725,19 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>10000000</v>
+        <v>2000000</v>
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
@@ -7720,19 +7748,19 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2301</v>
+        <v>2011</v>
       </c>
       <c r="B110" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C110" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D110" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E110" t="n">
-        <v>4275</v>
+        <v>4231</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
@@ -7743,10 +7771,12 @@
       <c r="H110" t="n">
         <v>109</v>
       </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>9999</v>
+      </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pavimentação MG-326 (Ponte Nova a Barra Longa) </t>
+          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7763,19 +7793,19 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>82286724</v>
+        <v>1600000</v>
       </c>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
@@ -7786,19 +7816,19 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2301</v>
+        <v>2011</v>
       </c>
       <c r="B111" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C111" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D111" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E111" t="n">
-        <v>4275</v>
+        <v>2500</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
@@ -7809,10 +7839,12 @@
       <c r="H111" t="n">
         <v>110</v>
       </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="n">
+        <v>12690</v>
+      </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Pavimentação da MG-314 (Entr. MG-416 (Peçanha) a LMG-744 (Coroaci) Entr. Virgolândia)</t>
+          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7829,19 +7861,19 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>22137718</v>
+        <v>2200000</v>
       </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
@@ -7852,19 +7884,19 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2301</v>
+        <v>2151</v>
       </c>
       <c r="B112" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C112" t="n">
-        <v>782</v>
+        <v>572</v>
       </c>
       <c r="D112" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E112" t="n">
-        <v>4275</v>
+        <v>1023</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -7878,7 +7910,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Pavimentação da Rodovia Municipal (Santa Rita do Itueto a Entr. BR-259 (Resplendor))</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7895,19 +7927,19 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="R112" t="n">
-        <v>21757581</v>
+        <v>0</v>
       </c>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
@@ -7918,19 +7950,19 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2301</v>
+        <v>2151</v>
       </c>
       <c r="B113" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C113" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D113" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E113" t="n">
-        <v>4275</v>
+        <v>2500</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -7944,7 +7976,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Rodovia MG-010, trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso), com extensão de 21,80 Km</t>
+          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7961,19 +7993,19 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="R113" t="n">
-        <v>8036364</v>
+        <v>0</v>
       </c>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
@@ -7996,7 +8028,7 @@
         <v>81</v>
       </c>
       <c r="E114" t="n">
-        <v>4275</v>
+        <v>4268</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
@@ -8010,7 +8042,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros (Distrito) - Entrº MG-181 (Estaca 1250 a 2000)</t>
+          <t>Reabilitação da MG-010 (Conceição do Mato Dentro a Serro)</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -8039,7 +8071,7 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>14063636</v>
+        <v>5000000</v>
       </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
@@ -8062,7 +8094,7 @@
         <v>81</v>
       </c>
       <c r="E115" t="n">
-        <v>4275</v>
+        <v>4268</v>
       </c>
       <c r="F115" t="n">
         <v>1</v>
@@ -8076,7 +8108,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Rodovia MG-10 - Trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso), com extensão de 22,50 km</t>
+          <t>Reabilitação da MG-129 (Ouro Preto a Ouro Branco)</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8105,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>8100000</v>
+        <v>5000000</v>
       </c>
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
@@ -8128,7 +8160,7 @@
         <v>81</v>
       </c>
       <c r="E116" t="n">
-        <v>4275</v>
+        <v>4268</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
@@ -8142,7 +8174,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Contorno de Andradas</t>
+          <t>Restauração Rodovia MG-010, trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso) e recomposição de Talude Erodido</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8171,7 +8203,7 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>4804860</v>
+        <v>10000000</v>
       </c>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
@@ -8208,7 +8240,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Empreendimento em definição junto ao Banco do Brasil - Contrato de Financiamento nº 20/00020-0 (PDMG)</t>
+          <t xml:space="preserve">Pavimentação MG-326 (Ponte Nova a Barra Longa) </t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8237,7 +8269,7 @@
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>6000001</v>
+        <v>82286724</v>
       </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
@@ -8260,7 +8292,7 @@
         <v>81</v>
       </c>
       <c r="E118" t="n">
-        <v>4287</v>
+        <v>4275</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -8274,7 +8306,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t>Pavimentação da MG-314 (Entr. MG-416 (Peçanha) a LMG-744 (Coroaci) Entr. Virgolândia)</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8300,10 +8332,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>22137718</v>
       </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
@@ -8326,7 +8358,7 @@
         <v>81</v>
       </c>
       <c r="E119" t="n">
-        <v>4289</v>
+        <v>4275</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -8340,7 +8372,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>Pavimentação da Rodovia Municipal (Santa Rita do Itueto a Entr. BR-259 (Resplendor))</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8366,10 +8398,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>21757581</v>
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
@@ -8392,7 +8424,7 @@
         <v>81</v>
       </c>
       <c r="E120" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -8406,7 +8438,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>04ª URG Barbacena</t>
+          <t>Rodovia MG-010, trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso), com extensão de 21,80 Km</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8435,7 +8467,7 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>12870000</v>
+        <v>8036364</v>
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
@@ -8458,7 +8490,7 @@
         <v>81</v>
       </c>
       <c r="E121" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -8472,7 +8504,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>20ª URG Formiga</t>
+          <t>Trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros (Distrito) - Entrº MG-181 (Estaca 1250 a 2000)</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8501,7 +8533,7 @@
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>12870000</v>
+        <v>14063636</v>
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
@@ -8524,7 +8556,7 @@
         <v>81</v>
       </c>
       <c r="E122" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -8538,7 +8570,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>28ª URG Teófilo Otoni</t>
+          <t>Rodovia MG-10 - Trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso), com extensão de 22,50 km</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8567,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>9575065</v>
+        <v>8100000</v>
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
@@ -8590,7 +8622,7 @@
         <v>81</v>
       </c>
       <c r="E123" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -8604,7 +8636,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30ª URG Juiz de Fora</t>
+          <t>Melhoramento e pavimentação do Contorno de Andradas</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8633,7 +8665,7 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>12375000</v>
+        <v>4804860</v>
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
@@ -8656,7 +8688,7 @@
         <v>81</v>
       </c>
       <c r="E124" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -8670,7 +8702,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>01ª URG Belo Horizonte - Sul</t>
+          <t>Empreendimento em definição junto ao Banco do Brasil - Contrato de Financiamento nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8699,7 +8731,7 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>14850000</v>
+        <v>6000001</v>
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
@@ -8722,7 +8754,7 @@
         <v>81</v>
       </c>
       <c r="E125" t="n">
-        <v>4293</v>
+        <v>4287</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -8736,7 +8768,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>01ª URG Belo Horizonte - Norte</t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8762,10 +8794,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R125" t="n">
-        <v>14850000</v>
+        <v>0</v>
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
@@ -8788,7 +8820,7 @@
         <v>81</v>
       </c>
       <c r="E126" t="n">
-        <v>4293</v>
+        <v>4289</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -8802,7 +8834,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>31ª URG Ituiutaba</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8828,10 +8860,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R126" t="n">
-        <v>9900000</v>
+        <v>0</v>
       </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
@@ -8842,19 +8874,19 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="B127" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C127" t="n">
-        <v>363</v>
+        <v>782</v>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="E127" t="n">
-        <v>4006</v>
+        <v>4293</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
@@ -8868,42 +8900,36 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t>04ª URG Barbacena</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>METRO QUADRADO</t>
-        </is>
-      </c>
-      <c r="M127" t="n">
-        <v>5000</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>12870000</v>
       </c>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
@@ -8914,19 +8940,19 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2321</v>
+        <v>2301</v>
       </c>
       <c r="B128" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C128" t="n">
-        <v>302</v>
+        <v>782</v>
       </c>
       <c r="D128" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E128" t="n">
-        <v>4222</v>
+        <v>4293</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
@@ -8940,12 +8966,12 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>20ª URG Formiga</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -8957,19 +8983,19 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>800291</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>12870000</v>
       </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
@@ -8980,19 +9006,19 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2321</v>
+        <v>2301</v>
       </c>
       <c r="B129" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C129" t="n">
-        <v>302</v>
+        <v>782</v>
       </c>
       <c r="D129" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E129" t="n">
-        <v>4222</v>
+        <v>4293</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
@@ -9006,12 +9032,12 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>28ª URG Teófilo Otoni</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -9023,19 +9049,19 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>174673</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>9575065</v>
       </c>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
@@ -9046,19 +9072,19 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2321</v>
+        <v>2301</v>
       </c>
       <c r="B130" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C130" t="n">
-        <v>302</v>
+        <v>782</v>
       </c>
       <c r="D130" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E130" t="n">
-        <v>4222</v>
+        <v>4293</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -9069,12 +9095,10 @@
       <c r="H130" t="n">
         <v>129</v>
       </c>
-      <c r="I130" t="n">
-        <v>11877</v>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>30ª URG Juiz de Fora</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -9091,19 +9115,19 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>1088908</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>12375000</v>
       </c>
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
@@ -9114,19 +9138,19 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2361</v>
+        <v>2301</v>
       </c>
       <c r="B131" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C131" t="n">
-        <v>846</v>
+        <v>782</v>
       </c>
       <c r="D131" t="n">
-        <v>705</v>
+        <v>81</v>
       </c>
       <c r="E131" t="n">
-        <v>7004</v>
+        <v>4293</v>
       </c>
       <c r="F131" t="n">
         <v>1</v>
@@ -9140,7 +9164,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>01ª URG Belo Horizonte - Sul</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -9155,10 +9179,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>14850000</v>
+      </c>
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
@@ -9168,19 +9204,19 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2361</v>
+        <v>2301</v>
       </c>
       <c r="B132" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C132" t="n">
-        <v>274</v>
+        <v>782</v>
       </c>
       <c r="D132" t="n">
-        <v>766</v>
+        <v>81</v>
       </c>
       <c r="E132" t="n">
-        <v>2113</v>
+        <v>4293</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -9194,7 +9230,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>01ª URG Belo Horizonte - Norte</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -9209,10 +9245,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>14850000</v>
+      </c>
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
@@ -9222,19 +9270,19 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2361</v>
+        <v>2301</v>
       </c>
       <c r="B133" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C133" t="n">
-        <v>274</v>
+        <v>782</v>
       </c>
       <c r="D133" t="n">
-        <v>767</v>
+        <v>81</v>
       </c>
       <c r="E133" t="n">
-        <v>2114</v>
+        <v>4293</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
@@ -9248,7 +9296,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t>31ª URG Ituiutaba</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9265,19 +9313,19 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>2754406</v>
+        <v>9900000</v>
       </c>
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
@@ -9288,19 +9336,19 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2371</v>
+        <v>2311</v>
       </c>
       <c r="B134" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C134" t="n">
-        <v>609</v>
+        <v>363</v>
       </c>
       <c r="D134" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="E134" t="n">
-        <v>4238</v>
+        <v>4006</v>
       </c>
       <c r="F134" t="n">
         <v>1</v>
@@ -9314,33 +9362,39 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M134" t="n">
+        <v>5000</v>
+      </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>8311374</v>
+        <v>5000000</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -9354,19 +9408,19 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2421</v>
+        <v>2321</v>
       </c>
       <c r="B135" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C135" t="n">
-        <v>544</v>
+        <v>302</v>
       </c>
       <c r="D135" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E135" t="n">
-        <v>1016</v>
+        <v>4222</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
@@ -9380,12 +9434,12 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Implantação de Sistemas de Abastecimento de Água e instalação de kits fotovoltaicos em poços artesianos conforme demanda da sociedade</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -9397,16 +9451,16 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>477508</v>
+        <v>800291</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
@@ -9420,19 +9474,19 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>3051</v>
+        <v>2321</v>
       </c>
       <c r="B136" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C136" t="n">
-        <v>364</v>
+        <v>302</v>
       </c>
       <c r="D136" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="E136" t="n">
-        <v>4016</v>
+        <v>4222</v>
       </c>
       <c r="F136" t="n">
         <v>1</v>
@@ -9446,12 +9500,12 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -9463,16 +9517,16 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>4825656</v>
+        <v>174673</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
@@ -9486,19 +9540,19 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>3051</v>
+        <v>2321</v>
       </c>
       <c r="B137" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C137" t="n">
-        <v>364</v>
+        <v>302</v>
       </c>
       <c r="D137" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="E137" t="n">
-        <v>4016</v>
+        <v>4222</v>
       </c>
       <c r="F137" t="n">
         <v>1</v>
@@ -9509,10 +9563,12 @@
       <c r="H137" t="n">
         <v>136</v>
       </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="n">
+        <v>11877</v>
+      </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9529,16 +9585,16 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>12649000</v>
+        <v>1088908</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
@@ -9552,19 +9608,19 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>3051</v>
+        <v>2361</v>
       </c>
       <c r="B138" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C138" t="n">
-        <v>364</v>
+        <v>846</v>
       </c>
       <c r="D138" t="n">
-        <v>15</v>
+        <v>705</v>
       </c>
       <c r="E138" t="n">
-        <v>4016</v>
+        <v>7004</v>
       </c>
       <c r="F138" t="n">
         <v>1</v>
@@ -9578,7 +9634,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9593,22 +9649,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q138" t="n">
-        <v>3715000</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
@@ -9618,19 +9662,19 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>3051</v>
+        <v>2361</v>
       </c>
       <c r="B139" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C139" t="n">
-        <v>571</v>
+        <v>274</v>
       </c>
       <c r="D139" t="n">
-        <v>16</v>
+        <v>766</v>
       </c>
       <c r="E139" t="n">
-        <v>4018</v>
+        <v>2113</v>
       </c>
       <c r="F139" t="n">
         <v>1</v>
@@ -9644,7 +9688,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Melhoria da infraestrutura da pesquisa.</t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9659,22 +9703,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>250000</v>
-      </c>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
@@ -9684,19 +9716,19 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>3051</v>
+        <v>2361</v>
       </c>
       <c r="B140" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C140" t="n">
-        <v>571</v>
+        <v>274</v>
       </c>
       <c r="D140" t="n">
-        <v>16</v>
+        <v>767</v>
       </c>
       <c r="E140" t="n">
-        <v>4018</v>
+        <v>2114</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -9710,7 +9742,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9727,19 +9759,19 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>250000</v>
+        <v>2754406</v>
       </c>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
@@ -9750,19 +9782,19 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>4031</v>
+        <v>2371</v>
       </c>
       <c r="B141" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C141" t="n">
-        <v>61</v>
+        <v>609</v>
       </c>
       <c r="D141" t="n">
-        <v>706</v>
+        <v>78</v>
       </c>
       <c r="E141" t="n">
-        <v>2091</v>
+        <v>4238</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
@@ -9773,47 +9805,39 @@
       <c r="H141" t="n">
         <v>140</v>
       </c>
-      <c r="I141" t="n">
-        <v>12054</v>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M141" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>8311374</v>
       </c>
       <c r="R141" t="n">
-        <v>10431496</v>
+        <v>0</v>
       </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
@@ -9824,19 +9848,19 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>4031</v>
+        <v>2421</v>
       </c>
       <c r="B142" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C142" t="n">
-        <v>61</v>
+        <v>544</v>
       </c>
       <c r="D142" t="n">
-        <v>706</v>
+        <v>101</v>
       </c>
       <c r="E142" t="n">
-        <v>2091</v>
+        <v>1016</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -9847,17 +9871,15 @@
       <c r="H142" t="n">
         <v>141</v>
       </c>
-      <c r="I142" t="n">
-        <v>12702</v>
-      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>CINCÃO - Fornecimento e montagem de estante tipo porta-paletes e de planos metálicos para os armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente do TRIBUNAL</t>
+          <t>Implantação de Sistemas de Abastecimento de Água e instalação de kits fotovoltaicos em poços artesianos conforme demanda da sociedade</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -9869,19 +9891,19 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>477508</v>
       </c>
       <c r="R142" t="n">
-        <v>102247</v>
+        <v>0</v>
       </c>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
@@ -9892,19 +9914,19 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B143" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C143" t="n">
-        <v>61</v>
+        <v>364</v>
       </c>
       <c r="D143" t="n">
-        <v>706</v>
+        <v>15</v>
       </c>
       <c r="E143" t="n">
-        <v>2091</v>
+        <v>4016</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
@@ -9915,30 +9937,22 @@
       <c r="H143" t="n">
         <v>142</v>
       </c>
-      <c r="I143" t="n">
-        <v>12806</v>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M143" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -9952,10 +9966,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>4825656</v>
       </c>
       <c r="R143" t="n">
-        <v>19560087</v>
+        <v>0</v>
       </c>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
@@ -9966,19 +9980,19 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B144" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C144" t="n">
-        <v>61</v>
+        <v>364</v>
       </c>
       <c r="D144" t="n">
-        <v>706</v>
+        <v>15</v>
       </c>
       <c r="E144" t="n">
-        <v>2091</v>
+        <v>4016</v>
       </c>
       <c r="F144" t="n">
         <v>1</v>
@@ -9989,30 +10003,22 @@
       <c r="H144" t="n">
         <v>143</v>
       </c>
-      <c r="I144" t="n">
-        <v>12638</v>
-      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M144" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -10026,10 +10032,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>12649000</v>
       </c>
       <c r="R144" t="n">
-        <v>19560087</v>
+        <v>0</v>
       </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
@@ -10040,19 +10046,19 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B145" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C145" t="n">
-        <v>61</v>
+        <v>364</v>
       </c>
       <c r="D145" t="n">
-        <v>706</v>
+        <v>15</v>
       </c>
       <c r="E145" t="n">
-        <v>2091</v>
+        <v>4016</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -10063,17 +10069,15 @@
       <c r="H145" t="n">
         <v>144</v>
       </c>
-      <c r="I145" t="n">
-        <v>12568</v>
-      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Itabirito/MG.</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -10094,10 +10098,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3715000</v>
       </c>
       <c r="R145" t="n">
-        <v>5550000</v>
+        <v>0</v>
       </c>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
@@ -10108,19 +10112,19 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B146" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C146" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D146" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E146" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F146" t="n">
         <v>1</v>
@@ -10131,17 +10135,15 @@
       <c r="H146" t="n">
         <v>145</v>
       </c>
-      <c r="I146" t="n">
-        <v>12627</v>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
+          <t>Melhoria da infraestrutura da pesquisa.</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -10153,19 +10155,19 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>4000000</v>
+        <v>250000</v>
       </c>
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="inlineStr"/>
@@ -10176,19 +10178,19 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B147" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C147" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D147" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E147" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F147" t="n">
         <v>1</v>
@@ -10199,17 +10201,15 @@
       <c r="H147" t="n">
         <v>146</v>
       </c>
-      <c r="I147" t="n">
-        <v>12146</v>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -10221,19 +10221,19 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>13121711</v>
+        <v>250000</v>
       </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
@@ -10268,11 +10268,11 @@
         <v>147</v>
       </c>
       <c r="I148" t="n">
-        <v>12400</v>
+        <v>12054</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10307,7 +10307,7 @@
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>18431199</v>
+        <v>10431496</v>
       </c>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
@@ -10342,11 +10342,11 @@
         <v>148</v>
       </c>
       <c r="I149" t="n">
-        <v>12288</v>
+        <v>12702</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t>CINCÃO - Fornecimento e montagem de estante tipo porta-paletes e de planos metálicos para os armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente do TRIBUNAL</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10354,34 +10354,28 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M149" t="n">
-        <v>1</v>
-      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>1950000</v>
+        <v>102247</v>
       </c>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
@@ -10392,19 +10386,19 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>5011</v>
+        <v>4031</v>
       </c>
       <c r="B150" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C150" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="D150" t="n">
-        <v>133</v>
+        <v>706</v>
       </c>
       <c r="E150" t="n">
-        <v>3017</v>
+        <v>2091</v>
       </c>
       <c r="F150" t="n">
         <v>1</v>
@@ -10415,22 +10409,30 @@
       <c r="H150" t="n">
         <v>149</v>
       </c>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="n">
+        <v>12806</v>
+      </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
+        <v>1</v>
+      </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -10447,7 +10449,7 @@
         <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>800000</v>
+        <v>19560087</v>
       </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
@@ -10458,19 +10460,19 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>5031</v>
+        <v>4031</v>
       </c>
       <c r="B151" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C151" t="n">
-        <v>572</v>
+        <v>61</v>
       </c>
       <c r="D151" t="n">
-        <v>133</v>
+        <v>706</v>
       </c>
       <c r="E151" t="n">
-        <v>3015</v>
+        <v>2091</v>
       </c>
       <c r="F151" t="n">
         <v>1</v>
@@ -10481,22 +10483,30 @@
       <c r="H151" t="n">
         <v>150</v>
       </c>
-      <c r="I151" t="inlineStr"/>
+      <c r="I151" t="n">
+        <v>12638</v>
+      </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
+        <v>1</v>
+      </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -10513,7 +10523,7 @@
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>4782988</v>
+        <v>19560087</v>
       </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
@@ -10524,19 +10534,19 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>5141</v>
+        <v>4031</v>
       </c>
       <c r="B152" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C152" t="n">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="D152" t="n">
-        <v>30</v>
+        <v>706</v>
       </c>
       <c r="E152" t="n">
-        <v>6006</v>
+        <v>2091</v>
       </c>
       <c r="F152" t="n">
         <v>1</v>
@@ -10547,15 +10557,17 @@
       <c r="H152" t="n">
         <v>151</v>
       </c>
-      <c r="I152" t="inlineStr"/>
+      <c r="I152" t="n">
+        <v>12568</v>
+      </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Itabirito/MG.</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
@@ -10579,7 +10591,7 @@
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>16317109</v>
+        <v>5550000</v>
       </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
@@ -10590,19 +10602,19 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>5391</v>
+        <v>4031</v>
       </c>
       <c r="B153" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C153" t="n">
-        <v>752</v>
+        <v>61</v>
       </c>
       <c r="D153" t="n">
-        <v>92</v>
+        <v>706</v>
       </c>
       <c r="E153" t="n">
-        <v>3004</v>
+        <v>2091</v>
       </c>
       <c r="F153" t="n">
         <v>1</v>
@@ -10613,15 +10625,17 @@
       <c r="H153" t="n">
         <v>152</v>
       </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="n">
+        <v>12627</v>
+      </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -10638,14 +10652,14 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>92004926</v>
+        <v>4000000</v>
       </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
@@ -10656,19 +10670,19 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>5391</v>
+        <v>4031</v>
       </c>
       <c r="B154" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C154" t="n">
-        <v>752</v>
+        <v>61</v>
       </c>
       <c r="D154" t="n">
-        <v>92</v>
+        <v>706</v>
       </c>
       <c r="E154" t="n">
-        <v>3004</v>
+        <v>2091</v>
       </c>
       <c r="F154" t="n">
         <v>1</v>
@@ -10679,15 +10693,17 @@
       <c r="H154" t="n">
         <v>153</v>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="n">
+        <v>12146</v>
+      </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -10699,19 +10715,19 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>10705994</v>
+        <v>13121711</v>
       </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
@@ -10722,19 +10738,19 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>5391</v>
+        <v>4031</v>
       </c>
       <c r="B155" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C155" t="n">
-        <v>752</v>
+        <v>61</v>
       </c>
       <c r="D155" t="n">
-        <v>92</v>
+        <v>706</v>
       </c>
       <c r="E155" t="n">
-        <v>3004</v>
+        <v>2091</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
@@ -10745,39 +10761,47 @@
       <c r="H155" t="n">
         <v>154</v>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="n">
+        <v>12400</v>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M155" t="n">
+        <v>1</v>
+      </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>10464844</v>
+        <v>18431199</v>
       </c>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
@@ -10788,19 +10812,19 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>5391</v>
+        <v>4031</v>
       </c>
       <c r="B156" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C156" t="n">
-        <v>752</v>
+        <v>61</v>
       </c>
       <c r="D156" t="n">
-        <v>92</v>
+        <v>706</v>
       </c>
       <c r="E156" t="n">
-        <v>3004</v>
+        <v>2091</v>
       </c>
       <c r="F156" t="n">
         <v>1</v>
@@ -10811,39 +10835,47 @@
       <c r="H156" t="n">
         <v>155</v>
       </c>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="n">
+        <v>12288</v>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M156" t="n">
+        <v>1</v>
+      </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>2098278</v>
+        <v>1950000</v>
       </c>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
@@ -10854,19 +10886,19 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>5391</v>
+        <v>5011</v>
       </c>
       <c r="B157" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C157" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="D157" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E157" t="n">
-        <v>3004</v>
+        <v>3017</v>
       </c>
       <c r="F157" t="n">
         <v>1</v>
@@ -10880,7 +10912,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10909,7 +10941,7 @@
         <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>96721858</v>
+        <v>800000</v>
       </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
@@ -10920,19 +10952,19 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>5391</v>
+        <v>5031</v>
       </c>
       <c r="B158" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C158" t="n">
-        <v>752</v>
+        <v>572</v>
       </c>
       <c r="D158" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E158" t="n">
-        <v>3004</v>
+        <v>3015</v>
       </c>
       <c r="F158" t="n">
         <v>1</v>
@@ -10946,7 +10978,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10963,19 +10995,19 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>16415074</v>
+        <v>4782988</v>
       </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
@@ -10986,19 +11018,19 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>5391</v>
+        <v>5141</v>
       </c>
       <c r="B159" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C159" t="n">
-        <v>752</v>
+        <v>126</v>
       </c>
       <c r="D159" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="E159" t="n">
-        <v>3004</v>
+        <v>6006</v>
       </c>
       <c r="F159" t="n">
         <v>1</v>
@@ -11012,7 +11044,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -11029,19 +11061,19 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>1</v>
+        <v>16317109</v>
       </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
@@ -11064,7 +11096,7 @@
         <v>92</v>
       </c>
       <c r="E160" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F160" t="n">
         <v>1</v>
@@ -11078,7 +11110,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -11107,7 +11139,7 @@
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>126817302</v>
+        <v>92004926</v>
       </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
@@ -11130,7 +11162,7 @@
         <v>92</v>
       </c>
       <c r="E161" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F161" t="n">
         <v>1</v>
@@ -11144,7 +11176,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -11173,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>16058991</v>
+        <v>10705994</v>
       </c>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
@@ -11196,7 +11228,7 @@
         <v>92</v>
       </c>
       <c r="E162" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
@@ -11210,7 +11242,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -11239,7 +11271,7 @@
         <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>65795530</v>
+        <v>10464844</v>
       </c>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
@@ -11262,7 +11294,7 @@
         <v>92</v>
       </c>
       <c r="E163" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
@@ -11276,7 +11308,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -11305,7 +11337,7 @@
         <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>44156794</v>
+        <v>2098278</v>
       </c>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
@@ -11328,7 +11360,7 @@
         <v>92</v>
       </c>
       <c r="E164" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
@@ -11342,7 +11374,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -11371,7 +11403,7 @@
         <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>140716908</v>
+        <v>96721858</v>
       </c>
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
@@ -11394,7 +11426,7 @@
         <v>92</v>
       </c>
       <c r="E165" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
@@ -11408,7 +11440,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11425,19 +11457,19 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>8715687</v>
+        <v>16415074</v>
       </c>
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
@@ -11460,7 +11492,7 @@
         <v>92</v>
       </c>
       <c r="E166" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
@@ -11474,7 +11506,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11491,19 +11523,19 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>24622611</v>
+        <v>1</v>
       </c>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
@@ -11523,10 +11555,10 @@
         <v>752</v>
       </c>
       <c r="D167" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E167" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
@@ -11540,7 +11572,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Expansão do Sistema de Geração</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11557,19 +11589,19 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>1</v>
+        <v>126817302</v>
       </c>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
@@ -11578,6 +11610,468 @@
       <c r="W167" t="inlineStr"/>
       <c r="X167" t="inlineStr"/>
     </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B168" t="n">
+        <v>25</v>
+      </c>
+      <c r="C168" t="n">
+        <v>752</v>
+      </c>
+      <c r="D168" t="n">
+        <v>92</v>
+      </c>
+      <c r="E168" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>167</v>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Montes Claros</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>16058991</v>
+      </c>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
+      <c r="W168" t="inlineStr"/>
+      <c r="X168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B169" t="n">
+        <v>25</v>
+      </c>
+      <c r="C169" t="n">
+        <v>752</v>
+      </c>
+      <c r="D169" t="n">
+        <v>92</v>
+      </c>
+      <c r="E169" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>168</v>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Juíz de Fora</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>65795530</v>
+      </c>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B170" t="n">
+        <v>25</v>
+      </c>
+      <c r="C170" t="n">
+        <v>752</v>
+      </c>
+      <c r="D170" t="n">
+        <v>92</v>
+      </c>
+      <c r="E170" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>169</v>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Uberlândia</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>44156794</v>
+      </c>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B171" t="n">
+        <v>25</v>
+      </c>
+      <c r="C171" t="n">
+        <v>752</v>
+      </c>
+      <c r="D171" t="n">
+        <v>92</v>
+      </c>
+      <c r="E171" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>170</v>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
+        <v>140716908</v>
+      </c>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr"/>
+      <c r="W171" t="inlineStr"/>
+      <c r="X171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B172" t="n">
+        <v>25</v>
+      </c>
+      <c r="C172" t="n">
+        <v>752</v>
+      </c>
+      <c r="D172" t="n">
+        <v>92</v>
+      </c>
+      <c r="E172" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>171</v>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Ipatinga</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="n">
+        <v>8715687</v>
+      </c>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr"/>
+      <c r="W172" t="inlineStr"/>
+      <c r="X172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B173" t="n">
+        <v>25</v>
+      </c>
+      <c r="C173" t="n">
+        <v>752</v>
+      </c>
+      <c r="D173" t="n">
+        <v>92</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>172</v>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Uberaba</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
+        <v>24622611</v>
+      </c>
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr"/>
+      <c r="W173" t="inlineStr"/>
+      <c r="X173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B174" t="n">
+        <v>25</v>
+      </c>
+      <c r="C174" t="n">
+        <v>752</v>
+      </c>
+      <c r="D174" t="n">
+        <v>94</v>
+      </c>
+      <c r="E174" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>173</v>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Expansão do Sistema de Geração</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>1</v>
+      </c>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr"/>
+      <c r="W174" t="inlineStr"/>
+      <c r="X174" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -499,42 +499,42 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>VALOR TESOURO 2026 (R$)</t>
+          <t>VALOR TESOURO 2027 (R$)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>VALOR OUTROS 2026 (R$)</t>
+          <t>VALOR OUTROS 2027 (R$)</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>VALOR TESOURO 2027 (R$)</t>
+          <t>VALOR TESOURO 2028 (R$)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>VALOR OUTROS 2027 (R$)</t>
+          <t>VALOR OUTROS 2028 (R$)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>VALOR TESOURO 2028 (R$)</t>
+          <t>VALOR TESOURO 2029 (R$)</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>VALOR OUTROS 2028 (R$)</t>
+          <t>VALOR OUTROS 2029 (R$)</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>VALOR TESOURO 2029 (R$)</t>
+          <t>VALOR TESOURO 2030 (R$)</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>VALOR OUTROS 2029 (R$)</t>
+          <t>VALOR OUTROS 2030 (R$)</t>
         </is>
       </c>
     </row>

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X268"/>
+  <dimension ref="A1:X274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5823,16 +5823,16 @@
         <v>1301</v>
       </c>
       <c r="B81" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C81" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D81" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E81" t="n">
-        <v>4290</v>
+        <v>4262</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -5843,12 +5843,10 @@
       <c r="H81" t="n">
         <v>80</v>
       </c>
-      <c r="I81" t="n">
-        <v>12510</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
+          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5865,19 +5863,19 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>10932874</v>
       </c>
       <c r="R81" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
@@ -5891,16 +5889,16 @@
         <v>1301</v>
       </c>
       <c r="B82" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C82" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D82" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E82" t="n">
-        <v>1036</v>
+        <v>4290</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -5912,11 +5910,11 @@
         <v>81</v>
       </c>
       <c r="I82" t="n">
-        <v>12453</v>
+        <v>12510</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
+          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5933,19 +5931,19 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>539924</v>
+        <v>40000000</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
@@ -5959,16 +5957,16 @@
         <v>1301</v>
       </c>
       <c r="B83" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C83" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D83" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E83" t="n">
-        <v>1036</v>
+        <v>4290</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -5979,17 +5977,15 @@
       <c r="H83" t="n">
         <v>82</v>
       </c>
-      <c r="I83" t="n">
-        <v>12454</v>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6001,19 +5997,19 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>478579</v>
       </c>
       <c r="R83" t="n">
-        <v>15337533</v>
+        <v>0</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
@@ -6027,16 +6023,16 @@
         <v>1301</v>
       </c>
       <c r="B84" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C84" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D84" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E84" t="n">
-        <v>1036</v>
+        <v>4290</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -6047,17 +6043,15 @@
       <c r="H84" t="n">
         <v>83</v>
       </c>
-      <c r="I84" t="n">
-        <v>11521</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6074,14 +6068,14 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>SABARÁ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>2246479</v>
       </c>
       <c r="R84" t="n">
-        <v>1440021</v>
+        <v>0</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
@@ -6095,16 +6089,16 @@
         <v>1301</v>
       </c>
       <c r="B85" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C85" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D85" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E85" t="n">
-        <v>1036</v>
+        <v>4290</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -6115,17 +6109,15 @@
       <c r="H85" t="n">
         <v>84</v>
       </c>
-      <c r="I85" t="n">
-        <v>11519</v>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6137,19 +6129,19 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>156926</v>
       </c>
       <c r="R85" t="n">
-        <v>6942767</v>
+        <v>0</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
@@ -6184,16 +6176,16 @@
         <v>85</v>
       </c>
       <c r="I86" t="n">
-        <v>11512</v>
+        <v>12453</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
+          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6205,19 +6197,19 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>14686005</v>
+        <v>539924</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
@@ -6252,11 +6244,11 @@
         <v>86</v>
       </c>
       <c r="I87" t="n">
-        <v>11514</v>
+        <v>12454</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
+          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6273,19 +6265,19 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>52160376</v>
+        <v>15337533</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
@@ -6320,11 +6312,11 @@
         <v>87</v>
       </c>
       <c r="I88" t="n">
-        <v>11511</v>
+        <v>11521</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
+          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6341,19 +6333,19 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SABARÁ</t>
         </is>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>20521500</v>
+        <v>1440021</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
@@ -6388,11 +6380,11 @@
         <v>88</v>
       </c>
       <c r="I89" t="n">
-        <v>11520</v>
+        <v>11519</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6409,19 +6401,19 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>SANTA LUZIA</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>6952445</v>
+        <v>6942767</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
@@ -6456,16 +6448,16 @@
         <v>89</v>
       </c>
       <c r="I90" t="n">
-        <v>11513</v>
+        <v>11512</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
+          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -6477,19 +6469,19 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>12959175</v>
+        <v>14686005</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
@@ -6524,11 +6516,11 @@
         <v>90</v>
       </c>
       <c r="I91" t="n">
-        <v>11977</v>
+        <v>11514</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6545,19 +6537,19 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>CATAGUASES</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>38244490</v>
+        <v>52160376</v>
       </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
@@ -6568,19 +6560,19 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="B92" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C92" t="n">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="D92" t="n">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="E92" t="n">
-        <v>4118</v>
+        <v>1036</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -6591,15 +6583,17 @@
       <c r="H92" t="n">
         <v>91</v>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>11511</v>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RIMC</t>
+          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -6611,19 +6605,19 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4547000</v>
+        <v>20521500</v>
       </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
@@ -6634,19 +6628,19 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="B93" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C93" t="n">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="D93" t="n">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="E93" t="n">
-        <v>4118</v>
+        <v>1036</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -6657,15 +6651,17 @@
       <c r="H93" t="n">
         <v>92</v>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>11520</v>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RITO</t>
+          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -6677,19 +6673,19 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
+          <t>SANTA LUZIA</t>
         </is>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>4547000</v>
+        <v>6952445</v>
       </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
@@ -6700,38 +6696,40 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B94" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C94" t="n">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="D94" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E94" t="n">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>93</v>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>11513</v>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
+          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -6752,10 +6750,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>904245</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>44308050</v>
+        <v>12959175</v>
       </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
@@ -6766,38 +6764,40 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B95" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C95" t="n">
-        <v>243</v>
+        <v>451</v>
       </c>
       <c r="D95" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E95" t="n">
-        <v>4441</v>
+        <v>1036</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>94</v>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>11977</v>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -6809,19 +6809,19 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>CATAGUASES</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>6999284</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>38244490</v>
       </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
@@ -6832,38 +6832,40 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B96" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C96" t="n">
-        <v>243</v>
+        <v>451</v>
       </c>
       <c r="D96" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E96" t="n">
-        <v>4441</v>
+        <v>1041</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>95</v>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>11855</v>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -6880,14 +6882,14 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>651694</v>
+        <v>6286532</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2728583</v>
       </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
@@ -6898,38 +6900,40 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B97" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C97" t="n">
-        <v>243</v>
+        <v>451</v>
       </c>
       <c r="D97" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E97" t="n">
-        <v>4441</v>
+        <v>1041</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
         <v>96</v>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>11973</v>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -6941,16 +6945,16 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>ALFENAS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>651694</v>
+        <v>193263</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
@@ -6964,25 +6968,25 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1451</v>
+        <v>1371</v>
       </c>
       <c r="B98" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C98" t="n">
-        <v>243</v>
+        <v>511</v>
       </c>
       <c r="D98" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="E98" t="n">
-        <v>4441</v>
+        <v>4118</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>97</v>
@@ -6990,12 +6994,12 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Programa Água Doce - RIMC</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -7007,19 +7011,19 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>1472757</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>4547000</v>
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
@@ -7030,25 +7034,25 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1451</v>
+        <v>1371</v>
       </c>
       <c r="B99" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C99" t="n">
-        <v>243</v>
+        <v>511</v>
       </c>
       <c r="D99" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="E99" t="n">
-        <v>4441</v>
+        <v>4118</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>98</v>
@@ -7056,12 +7060,12 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Programa Água Doce - RITO</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -7073,19 +7077,19 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651694</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>4547000</v>
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
@@ -7102,13 +7106,13 @@
         <v>6</v>
       </c>
       <c r="C100" t="n">
-        <v>243</v>
+        <v>421</v>
       </c>
       <c r="D100" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E100" t="n">
-        <v>4441</v>
+        <v>1048</v>
       </c>
       <c r="F100" t="n">
         <v>1</v>
@@ -7122,7 +7126,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7148,10 +7152,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>18572878</v>
+        <v>904245</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>44308050</v>
       </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
@@ -7162,25 +7166,25 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B101" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C101" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D101" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E101" t="n">
-        <v>4476</v>
+        <v>4441</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
         <v>100</v>
@@ -7188,12 +7192,12 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -7214,7 +7218,7 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>270000</v>
+        <v>6999284</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -7228,25 +7232,25 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C102" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D102" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E102" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" t="n">
         <v>101</v>
@@ -7254,12 +7258,12 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -7276,11 +7280,11 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>1100000</v>
+        <v>651694</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
@@ -7294,25 +7298,25 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C103" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D103" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E103" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" t="n">
         <v>102</v>
@@ -7320,12 +7324,12 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -7337,16 +7341,16 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ALFENAS</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>624000</v>
+        <v>651694</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
@@ -7360,25 +7364,25 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B104" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C104" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D104" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E104" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
         <v>103</v>
@@ -7386,12 +7390,12 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -7408,11 +7412,11 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>210000</v>
+        <v>1472757</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
@@ -7426,25 +7430,25 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B105" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C105" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D105" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E105" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>104</v>
@@ -7452,12 +7456,12 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -7469,16 +7473,16 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>150000</v>
+        <v>651694</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
@@ -7492,25 +7496,25 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B106" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C106" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D106" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E106" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
         <v>105</v>
@@ -7518,12 +7522,12 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -7535,16 +7539,16 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>3918408</v>
+        <v>18572878</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -7567,10 +7571,10 @@
         <v>122</v>
       </c>
       <c r="D107" t="n">
-        <v>705</v>
+        <v>147</v>
       </c>
       <c r="E107" t="n">
-        <v>2500</v>
+        <v>4476</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
@@ -7584,7 +7588,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7592,17 +7596,11 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M107" t="n">
-        <v>1</v>
-      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -7616,7 +7614,7 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>282000</v>
+        <v>270000</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -7630,19 +7628,19 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="B108" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D108" t="n">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="E108" t="n">
-        <v>1006</v>
+        <v>4465</v>
       </c>
       <c r="F108" t="n">
         <v>1</v>
@@ -7656,7 +7654,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
+          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7673,19 +7671,19 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>1100000</v>
       </c>
       <c r="R108" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
@@ -7696,19 +7694,19 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="B109" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C109" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D109" t="n">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="E109" t="n">
-        <v>4063</v>
+        <v>4465</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
@@ -7722,7 +7720,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
+          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7744,14 +7742,14 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>150000</v>
+        <v>624000</v>
       </c>
       <c r="R109" t="n">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
@@ -7762,19 +7760,19 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1541</v>
+        <v>1501</v>
       </c>
       <c r="B110" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C110" t="n">
         <v>122</v>
       </c>
       <c r="D110" t="n">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="E110" t="n">
-        <v>2500</v>
+        <v>4465</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
@@ -7788,12 +7786,12 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
+          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -7814,7 +7812,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>2896100</v>
+        <v>210000</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -7828,19 +7826,19 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2011</v>
+        <v>1501</v>
       </c>
       <c r="B111" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C111" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D111" t="n">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="E111" t="n">
-        <v>4231</v>
+        <v>4465</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
@@ -7851,12 +7849,10 @@
       <c r="H111" t="n">
         <v>110</v>
       </c>
-      <c r="I111" t="n">
-        <v>12871</v>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
+          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7882,10 +7878,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="R111" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
@@ -7896,19 +7892,19 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2011</v>
+        <v>1501</v>
       </c>
       <c r="B112" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D112" t="n">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="E112" t="n">
-        <v>4231</v>
+        <v>4465</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -7919,12 +7915,10 @@
       <c r="H112" t="n">
         <v>111</v>
       </c>
-      <c r="I112" t="n">
-        <v>9999</v>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
+          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7950,10 +7944,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3918408</v>
       </c>
       <c r="R112" t="n">
-        <v>1600000</v>
+        <v>0</v>
       </c>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
@@ -7964,10 +7958,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2011</v>
+        <v>1501</v>
       </c>
       <c r="B113" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C113" t="n">
         <v>122</v>
@@ -7987,12 +7981,10 @@
       <c r="H113" t="n">
         <v>112</v>
       </c>
-      <c r="I113" t="n">
-        <v>12690</v>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
+          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -8000,11 +7992,17 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>1</v>
+      </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8018,10 +8016,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>282000</v>
       </c>
       <c r="R113" t="n">
-        <v>2200000</v>
+        <v>0</v>
       </c>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
@@ -8032,19 +8030,19 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2151</v>
+        <v>1511</v>
       </c>
       <c r="B114" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C114" t="n">
-        <v>572</v>
+        <v>181</v>
       </c>
       <c r="D114" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="E114" t="n">
-        <v>1023</v>
+        <v>1006</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
@@ -8058,7 +8056,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
+          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -8075,19 +8073,19 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
@@ -8098,19 +8096,19 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2151</v>
+        <v>1511</v>
       </c>
       <c r="B115" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C115" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="D115" t="n">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="E115" t="n">
-        <v>2500</v>
+        <v>4063</v>
       </c>
       <c r="F115" t="n">
         <v>1</v>
@@ -8124,7 +8122,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
+          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8146,14 +8144,14 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>1500000</v>
+        <v>150000</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
@@ -8164,19 +8162,19 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2301</v>
+        <v>1541</v>
       </c>
       <c r="B116" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C116" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D116" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E116" t="n">
-        <v>4268</v>
+        <v>2500</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
@@ -8190,12 +8188,12 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
+          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -8207,19 +8205,19 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>2896100</v>
       </c>
       <c r="R116" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
@@ -8230,19 +8228,19 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2301</v>
+        <v>2011</v>
       </c>
       <c r="B117" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C117" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D117" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E117" t="n">
-        <v>4268</v>
+        <v>4231</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -8253,10 +8251,12 @@
       <c r="H117" t="n">
         <v>116</v>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="n">
+        <v>12871</v>
+      </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
+          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8273,19 +8273,19 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
@@ -8296,19 +8296,19 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2301</v>
+        <v>2011</v>
       </c>
       <c r="B118" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C118" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D118" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E118" t="n">
-        <v>4268</v>
+        <v>4231</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -8319,10 +8319,12 @@
       <c r="H118" t="n">
         <v>117</v>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>9999</v>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
+          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8339,19 +8341,19 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>10000000</v>
+        <v>1600000</v>
       </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
@@ -8362,19 +8364,19 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2301</v>
+        <v>2011</v>
       </c>
       <c r="B119" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C119" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D119" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E119" t="n">
-        <v>4268</v>
+        <v>2500</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -8385,10 +8387,12 @@
       <c r="H119" t="n">
         <v>118</v>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="n">
+        <v>12690</v>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
+          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8405,19 +8409,19 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>9792000</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>2200000</v>
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
@@ -8428,19 +8432,19 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2301</v>
+        <v>2151</v>
       </c>
       <c r="B120" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C120" t="n">
-        <v>782</v>
+        <v>572</v>
       </c>
       <c r="D120" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E120" t="n">
-        <v>4268</v>
+        <v>1023</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -8454,7 +8458,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8471,16 +8475,16 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
@@ -8494,19 +8498,19 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2301</v>
+        <v>2151</v>
       </c>
       <c r="B121" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C121" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D121" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E121" t="n">
-        <v>4268</v>
+        <v>2500</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -8520,7 +8524,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
+          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8537,16 +8541,16 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>143000</v>
+        <v>1500000</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
@@ -8586,7 +8590,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
+          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8612,10 +8616,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>5876140</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
@@ -8652,7 +8656,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
+          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8678,10 +8682,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>1132500</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
@@ -8718,7 +8722,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
+          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8744,10 +8748,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
@@ -8784,7 +8788,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
+          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8810,7 +8814,7 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>34710000</v>
+        <v>9792000</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
@@ -8850,7 +8854,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
+          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8876,7 +8880,7 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>59000000</v>
+        <v>1000000</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
@@ -8916,7 +8920,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
+          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8942,7 +8946,7 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>1000000</v>
+        <v>143000</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -8982,7 +8986,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -9008,7 +9012,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>1000000</v>
+        <v>5876140</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
@@ -9048,7 +9052,7 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -9074,7 +9078,7 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>200000</v>
+        <v>1132500</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -9114,7 +9118,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
+          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -9180,7 +9184,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -9206,7 +9210,7 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>30980000</v>
+        <v>34710000</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -9246,7 +9250,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -9272,7 +9276,7 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>25655000</v>
+        <v>59000000</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -9312,7 +9316,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9338,7 +9342,7 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>66560000</v>
+        <v>1000000</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -9378,7 +9382,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -9444,7 +9448,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
+          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9470,7 +9474,7 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>25464500</v>
+        <v>200000</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
@@ -9496,7 +9500,7 @@
         <v>81</v>
       </c>
       <c r="E136" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F136" t="n">
         <v>1</v>
@@ -9510,7 +9514,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9536,7 +9540,7 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
@@ -9562,7 +9566,7 @@
         <v>81</v>
       </c>
       <c r="E137" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F137" t="n">
         <v>1</v>
@@ -9576,7 +9580,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9602,7 +9606,7 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>24000000</v>
+        <v>30980000</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
@@ -9628,7 +9632,7 @@
         <v>81</v>
       </c>
       <c r="E138" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F138" t="n">
         <v>1</v>
@@ -9642,7 +9646,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9668,7 +9672,7 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>252000</v>
+        <v>25655000</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
@@ -9694,7 +9698,7 @@
         <v>81</v>
       </c>
       <c r="E139" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F139" t="n">
         <v>1</v>
@@ -9708,7 +9712,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9734,7 +9738,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>319200</v>
+        <v>66560000</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -9760,7 +9764,7 @@
         <v>81</v>
       </c>
       <c r="E140" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -9774,7 +9778,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9800,7 +9804,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>495600</v>
+        <v>1000000</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
@@ -9826,7 +9830,7 @@
         <v>81</v>
       </c>
       <c r="E141" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
@@ -9840,7 +9844,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
+          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9866,7 +9870,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>679000</v>
+        <v>25464500</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
@@ -9906,7 +9910,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
+          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9932,7 +9936,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440000</v>
+        <v>100000</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
@@ -9972,7 +9976,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
+          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9998,7 +10002,7 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>14920000</v>
+        <v>24000000</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -10038,7 +10042,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
+          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -10064,7 +10068,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>8798400</v>
+        <v>252000</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
@@ -10104,7 +10108,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10130,7 +10134,7 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>369600</v>
+        <v>319200</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -10170,7 +10174,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -10196,7 +10200,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>1000000</v>
+        <v>495600</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
@@ -10236,7 +10240,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -10262,7 +10266,7 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>1203643</v>
+        <v>679000</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
@@ -10302,7 +10306,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10328,7 +10332,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>730000</v>
+        <v>440000</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
@@ -10368,7 +10372,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10394,7 +10398,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>66619</v>
+        <v>14920000</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -10434,7 +10438,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10460,7 +10464,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>901000</v>
+        <v>8798400</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -10500,7 +10504,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10526,7 +10530,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>100000</v>
+        <v>369600</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
@@ -10566,7 +10570,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10592,7 +10596,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>170000</v>
+        <v>1000000</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -10632,7 +10636,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
+          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10658,7 +10662,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>2940000</v>
+        <v>1203643</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
@@ -10698,7 +10702,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10724,7 +10728,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>810000</v>
+        <v>730000</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
@@ -10764,7 +10768,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
+          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10790,7 +10794,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>542000</v>
+        <v>66619</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -10830,7 +10834,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
+          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10856,7 +10860,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>2163814</v>
+        <v>901000</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
@@ -10896,7 +10900,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
+          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10922,7 +10926,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>25000000</v>
+        <v>100000</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -10962,7 +10966,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
+          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10988,7 +10992,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>500000</v>
+        <v>170000</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
@@ -11028,7 +11032,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
+          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -11054,7 +11058,7 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>1382535</v>
+        <v>2940000</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -11094,7 +11098,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -11120,7 +11124,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>1000000</v>
+        <v>810000</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
@@ -11160,7 +11164,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -11186,7 +11190,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>900000</v>
+        <v>542000</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
@@ -11226,7 +11230,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
+          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -11252,7 +11256,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>168000</v>
+        <v>2163814</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
@@ -11292,7 +11296,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
+          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -11318,7 +11322,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>249000</v>
+        <v>25000000</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
@@ -11358,7 +11362,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
+          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -11384,7 +11388,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>705000</v>
+        <v>500000</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
@@ -11424,7 +11428,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
+          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11450,7 +11454,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>58800</v>
+        <v>1382535</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
@@ -11490,7 +11494,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11516,7 +11520,7 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>725000</v>
+        <v>1000000</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
@@ -11542,7 +11546,7 @@
         <v>81</v>
       </c>
       <c r="E167" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
@@ -11556,7 +11560,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11582,10 +11586,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="R167" t="n">
-        <v>82286728</v>
+        <v>0</v>
       </c>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
@@ -11608,7 +11612,7 @@
         <v>81</v>
       </c>
       <c r="E168" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -11622,7 +11626,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11648,10 +11652,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="R168" t="n">
-        <v>22137718</v>
+        <v>0</v>
       </c>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
@@ -11674,7 +11678,7 @@
         <v>81</v>
       </c>
       <c r="E169" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F169" t="n">
         <v>1</v>
@@ -11688,7 +11692,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11714,10 +11718,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>249000</v>
       </c>
       <c r="R169" t="n">
-        <v>21757581</v>
+        <v>0</v>
       </c>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr"/>
@@ -11740,7 +11744,7 @@
         <v>81</v>
       </c>
       <c r="E170" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F170" t="n">
         <v>1</v>
@@ -11754,7 +11758,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
+          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11780,10 +11784,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>705000</v>
       </c>
       <c r="R170" t="n">
-        <v>8036364</v>
+        <v>0</v>
       </c>
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr"/>
@@ -11806,7 +11810,7 @@
         <v>81</v>
       </c>
       <c r="E171" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F171" t="n">
         <v>1</v>
@@ -11820,7 +11824,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
+          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11846,10 +11850,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>58800</v>
       </c>
       <c r="R171" t="n">
-        <v>14063636</v>
+        <v>0</v>
       </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
@@ -11872,7 +11876,7 @@
         <v>81</v>
       </c>
       <c r="E172" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F172" t="n">
         <v>1</v>
@@ -11886,7 +11890,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
+          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -11912,10 +11916,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>725000</v>
       </c>
       <c r="R172" t="n">
-        <v>8100000</v>
+        <v>0</v>
       </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
@@ -11952,7 +11956,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
+          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -11981,7 +11985,7 @@
         <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>4804860</v>
+        <v>82286728</v>
       </c>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
@@ -12018,7 +12022,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
+          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -12047,7 +12051,7 @@
         <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>6000001</v>
+        <v>22137718</v>
       </c>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
@@ -12084,7 +12088,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
+          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -12110,10 +12114,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>11326937</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>21757581</v>
       </c>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
@@ -12150,7 +12154,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
+          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -12176,10 +12180,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>19000000</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>8036364</v>
       </c>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
@@ -12216,7 +12220,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
+          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -12242,10 +12246,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>74941120</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>14063636</v>
       </c>
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
@@ -12282,7 +12286,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
+          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -12308,10 +12312,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>38460000</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>8100000</v>
       </c>
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
@@ -12348,7 +12352,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -12374,10 +12378,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>4804860</v>
       </c>
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
@@ -12414,7 +12418,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
+          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -12440,10 +12444,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>7000000</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>6000001</v>
       </c>
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
@@ -12480,7 +12484,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -12506,7 +12510,7 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>1000000</v>
+        <v>11326937</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
@@ -12546,7 +12550,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12572,7 +12576,7 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>6121131</v>
+        <v>19000000</v>
       </c>
       <c r="R182" t="n">
         <v>0</v>
@@ -12612,7 +12616,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
+          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12638,7 +12642,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>1000000</v>
+        <v>74941120</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
@@ -12678,7 +12682,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
+          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12704,7 +12708,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>1000000</v>
+        <v>38460000</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
@@ -12744,7 +12748,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
+          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -12810,7 +12814,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
+          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12836,7 +12840,7 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="R186" t="n">
         <v>0</v>
@@ -12876,7 +12880,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
+          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -12942,7 +12946,7 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
+          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -12968,7 +12972,7 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>1000000</v>
+        <v>6121131</v>
       </c>
       <c r="R188" t="n">
         <v>0</v>
@@ -13008,7 +13012,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
+          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -13034,7 +13038,7 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>431808</v>
+        <v>1000000</v>
       </c>
       <c r="R189" t="n">
         <v>0</v>
@@ -13074,7 +13078,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -13140,7 +13144,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
+          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -13206,7 +13210,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
+          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -13272,7 +13276,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
+          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -13298,7 +13302,7 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>14356788</v>
+        <v>1000000</v>
       </c>
       <c r="R193" t="n">
         <v>0</v>
@@ -13338,7 +13342,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
+          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -13364,7 +13368,7 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="R194" t="n">
         <v>0</v>
@@ -13404,7 +13408,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
+          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13430,7 +13434,7 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>1000000</v>
+        <v>431808</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
@@ -13470,7 +13474,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
+          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13496,7 +13500,7 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>35359852</v>
+        <v>1000000</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
@@ -13536,7 +13540,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
+          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13562,7 +13566,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>29030000</v>
+        <v>1000000</v>
       </c>
       <c r="R197" t="n">
         <v>0</v>
@@ -13602,7 +13606,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
+          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13668,7 +13672,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
+          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13694,7 +13698,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>3541727</v>
+        <v>14356788</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
@@ -13734,7 +13738,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
+          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13760,7 +13764,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>31280000</v>
+        <v>100000</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
@@ -13786,7 +13790,7 @@
         <v>81</v>
       </c>
       <c r="E201" t="n">
-        <v>4287</v>
+        <v>4275</v>
       </c>
       <c r="F201" t="n">
         <v>1</v>
@@ -13800,7 +13804,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13826,7 +13830,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
@@ -13852,7 +13856,7 @@
         <v>81</v>
       </c>
       <c r="E202" t="n">
-        <v>4289</v>
+        <v>4275</v>
       </c>
       <c r="F202" t="n">
         <v>1</v>
@@ -13866,7 +13870,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -13892,7 +13896,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>1000</v>
+        <v>35359852</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -13918,7 +13922,7 @@
         <v>81</v>
       </c>
       <c r="E203" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F203" t="n">
         <v>1</v>
@@ -13932,7 +13936,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
+          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -13958,7 +13962,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>10000000</v>
+        <v>29030000</v>
       </c>
       <c r="R203" t="n">
         <v>0</v>
@@ -13984,7 +13988,7 @@
         <v>81</v>
       </c>
       <c r="E204" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F204" t="n">
         <v>1</v>
@@ -13998,7 +14002,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
+          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -14024,7 +14028,7 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>1406178</v>
+        <v>1000000</v>
       </c>
       <c r="R204" t="n">
         <v>0</v>
@@ -14050,7 +14054,7 @@
         <v>81</v>
       </c>
       <c r="E205" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F205" t="n">
         <v>1</v>
@@ -14064,7 +14068,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>04ª URG BARBACENA</t>
+          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -14090,10 +14094,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>3541727</v>
       </c>
       <c r="R205" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr"/>
@@ -14116,7 +14120,7 @@
         <v>81</v>
       </c>
       <c r="E206" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F206" t="n">
         <v>1</v>
@@ -14130,7 +14134,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>20ª URG FORMIGA</t>
+          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -14156,10 +14160,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>31280000</v>
       </c>
       <c r="R206" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr"/>
@@ -14182,7 +14186,7 @@
         <v>81</v>
       </c>
       <c r="E207" t="n">
-        <v>4293</v>
+        <v>4287</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -14196,7 +14200,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>28ª URG TEÓFILO OTONI</t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -14222,10 +14226,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R207" t="n">
-        <v>9575065</v>
+        <v>0</v>
       </c>
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr"/>
@@ -14248,7 +14252,7 @@
         <v>81</v>
       </c>
       <c r="E208" t="n">
-        <v>4293</v>
+        <v>4289</v>
       </c>
       <c r="F208" t="n">
         <v>1</v>
@@ -14262,7 +14266,7 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>30ª URG JUIZ DE FORA</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -14288,10 +14292,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R208" t="n">
-        <v>12375000</v>
+        <v>0</v>
       </c>
       <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr"/>
@@ -14328,7 +14332,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - SUL</t>
+          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -14354,10 +14358,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="R209" t="n">
-        <v>14850000</v>
+        <v>0</v>
       </c>
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr"/>
@@ -14394,7 +14398,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - NORTE</t>
+          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14420,10 +14424,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>1406178</v>
       </c>
       <c r="R210" t="n">
-        <v>14850000</v>
+        <v>0</v>
       </c>
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr"/>
@@ -14460,7 +14464,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>31ª URG ITUIUTABA</t>
+          <t>04ª URG BARBACENA</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14489,7 +14493,7 @@
         <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>9900000</v>
+        <v>12870000</v>
       </c>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
@@ -14526,7 +14530,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG'S</t>
+          <t>20ª URG FORMIGA</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14552,10 +14556,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>654124898</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>12870000</v>
       </c>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr"/>
@@ -14592,7 +14596,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
+          <t>28ª URG TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14618,10 +14622,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>30767851</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>9575065</v>
       </c>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr"/>
@@ -14658,7 +14662,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
+          <t>30ª URG JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14684,10 +14688,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>19976964</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>12375000</v>
       </c>
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr"/>
@@ -14724,7 +14728,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
+          <t>01ª URG BELO HORIZONTE - SUL</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14750,10 +14754,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>12895888</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>14850000</v>
       </c>
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr"/>
@@ -14790,7 +14794,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
+          <t>01ª URG BELO HORIZONTE - NORTE</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14816,10 +14820,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>11846334</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>14850000</v>
       </c>
       <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr"/>
@@ -14856,7 +14860,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
+          <t>31ª URG ITUIUTABA</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -14882,10 +14886,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>15201174</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>9900000</v>
       </c>
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr"/>
@@ -14922,7 +14926,7 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG'S</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -14948,7 +14952,7 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>12921920</v>
+        <v>654124898</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
@@ -14974,7 +14978,7 @@
         <v>81</v>
       </c>
       <c r="E219" t="n">
-        <v>4385</v>
+        <v>4293</v>
       </c>
       <c r="F219" t="n">
         <v>1</v>
@@ -14988,7 +14992,7 @@
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -15014,7 +15018,7 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>6382601</v>
+        <v>30767851</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
@@ -15040,7 +15044,7 @@
         <v>81</v>
       </c>
       <c r="E220" t="n">
-        <v>4385</v>
+        <v>4293</v>
       </c>
       <c r="F220" t="n">
         <v>1</v>
@@ -15054,7 +15058,7 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
+          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -15080,7 +15084,7 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>30000000</v>
+        <v>19976964</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
@@ -15106,7 +15110,7 @@
         <v>81</v>
       </c>
       <c r="E221" t="n">
-        <v>4385</v>
+        <v>4293</v>
       </c>
       <c r="F221" t="n">
         <v>1</v>
@@ -15120,7 +15124,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -15146,7 +15150,7 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>4000000</v>
+        <v>12895888</v>
       </c>
       <c r="R221" t="n">
         <v>0</v>
@@ -15169,10 +15173,10 @@
         <v>782</v>
       </c>
       <c r="D222" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E222" t="n">
-        <v>4280</v>
+        <v>4293</v>
       </c>
       <c r="F222" t="n">
         <v>1</v>
@@ -15186,7 +15190,7 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -15212,7 +15216,7 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>4000000</v>
+        <v>11846334</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
@@ -15235,10 +15239,10 @@
         <v>782</v>
       </c>
       <c r="D223" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E223" t="n">
-        <v>4280</v>
+        <v>4293</v>
       </c>
       <c r="F223" t="n">
         <v>1</v>
@@ -15252,7 +15256,7 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -15278,7 +15282,7 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470000</v>
+        <v>15201174</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
@@ -15301,10 +15305,10 @@
         <v>782</v>
       </c>
       <c r="D224" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E224" t="n">
-        <v>4280</v>
+        <v>4293</v>
       </c>
       <c r="F224" t="n">
         <v>1</v>
@@ -15318,7 +15322,7 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -15344,7 +15348,7 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>4000000</v>
+        <v>12921920</v>
       </c>
       <c r="R224" t="n">
         <v>0</v>
@@ -15367,10 +15371,10 @@
         <v>782</v>
       </c>
       <c r="D225" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E225" t="n">
-        <v>4280</v>
+        <v>4385</v>
       </c>
       <c r="F225" t="n">
         <v>1</v>
@@ -15384,7 +15388,7 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -15410,7 +15414,7 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>1000000</v>
+        <v>6382601</v>
       </c>
       <c r="R225" t="n">
         <v>0</v>
@@ -15433,10 +15437,10 @@
         <v>782</v>
       </c>
       <c r="D226" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E226" t="n">
-        <v>4280</v>
+        <v>4385</v>
       </c>
       <c r="F226" t="n">
         <v>1</v>
@@ -15450,7 +15454,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -15476,7 +15480,7 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>420000</v>
+        <v>30000000</v>
       </c>
       <c r="R226" t="n">
         <v>0</v>
@@ -15499,10 +15503,10 @@
         <v>782</v>
       </c>
       <c r="D227" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E227" t="n">
-        <v>4280</v>
+        <v>4385</v>
       </c>
       <c r="F227" t="n">
         <v>1</v>
@@ -15516,7 +15520,7 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -15542,7 +15546,7 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>790000</v>
+        <v>4000000</v>
       </c>
       <c r="R227" t="n">
         <v>0</v>
@@ -15556,19 +15560,19 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="B228" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C228" t="n">
-        <v>363</v>
+        <v>782</v>
       </c>
       <c r="D228" t="n">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="E228" t="n">
-        <v>4006</v>
+        <v>4280</v>
       </c>
       <c r="F228" t="n">
         <v>1</v>
@@ -15582,39 +15586,33 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>METRO QUADRADO</t>
-        </is>
-      </c>
-      <c r="M228" t="n">
-        <v>5000</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="R228" t="n">
         <v>0</v>
@@ -15628,19 +15626,19 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2321</v>
+        <v>2301</v>
       </c>
       <c r="B229" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C229" t="n">
-        <v>302</v>
+        <v>782</v>
       </c>
       <c r="D229" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="E229" t="n">
-        <v>4222</v>
+        <v>4280</v>
       </c>
       <c r="F229" t="n">
         <v>1</v>
@@ -15654,12 +15652,12 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L229" t="inlineStr"/>
@@ -15671,16 +15669,16 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>800291</v>
+        <v>470000</v>
       </c>
       <c r="R229" t="n">
         <v>0</v>
@@ -15694,19 +15692,19 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>2321</v>
+        <v>2301</v>
       </c>
       <c r="B230" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C230" t="n">
-        <v>302</v>
+        <v>782</v>
       </c>
       <c r="D230" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="E230" t="n">
-        <v>4222</v>
+        <v>4280</v>
       </c>
       <c r="F230" t="n">
         <v>1</v>
@@ -15720,12 +15718,12 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L230" t="inlineStr"/>
@@ -15737,16 +15735,16 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>174673</v>
+        <v>4000000</v>
       </c>
       <c r="R230" t="n">
         <v>0</v>
@@ -15760,19 +15758,19 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2321</v>
+        <v>2301</v>
       </c>
       <c r="B231" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C231" t="n">
-        <v>302</v>
+        <v>782</v>
       </c>
       <c r="D231" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="E231" t="n">
-        <v>4222</v>
+        <v>4280</v>
       </c>
       <c r="F231" t="n">
         <v>1</v>
@@ -15783,12 +15781,10 @@
       <c r="H231" t="n">
         <v>230</v>
       </c>
-      <c r="I231" t="n">
-        <v>11877</v>
-      </c>
+      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -15805,16 +15801,16 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>1088908</v>
+        <v>1000000</v>
       </c>
       <c r="R231" t="n">
         <v>0</v>
@@ -15828,19 +15824,19 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2361</v>
+        <v>2301</v>
       </c>
       <c r="B232" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C232" t="n">
-        <v>846</v>
+        <v>782</v>
       </c>
       <c r="D232" t="n">
-        <v>705</v>
+        <v>139</v>
       </c>
       <c r="E232" t="n">
-        <v>7004</v>
+        <v>4280</v>
       </c>
       <c r="F232" t="n">
         <v>1</v>
@@ -15854,7 +15850,7 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -15869,10 +15865,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
-      <c r="R232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>420000</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr"/>
       <c r="U232" t="inlineStr"/>
@@ -15882,19 +15890,19 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2361</v>
+        <v>2301</v>
       </c>
       <c r="B233" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C233" t="n">
-        <v>274</v>
+        <v>782</v>
       </c>
       <c r="D233" t="n">
-        <v>766</v>
+        <v>139</v>
       </c>
       <c r="E233" t="n">
-        <v>2113</v>
+        <v>4280</v>
       </c>
       <c r="F233" t="n">
         <v>1</v>
@@ -15908,7 +15916,7 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -15923,10 +15931,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
-      <c r="R233" t="inlineStr"/>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>790000</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr"/>
       <c r="U233" t="inlineStr"/>
@@ -15936,19 +15956,19 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2361</v>
+        <v>2311</v>
       </c>
       <c r="B234" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C234" t="n">
-        <v>274</v>
+        <v>363</v>
       </c>
       <c r="D234" t="n">
-        <v>767</v>
+        <v>7</v>
       </c>
       <c r="E234" t="n">
-        <v>2114</v>
+        <v>4006</v>
       </c>
       <c r="F234" t="n">
         <v>1</v>
@@ -15962,36 +15982,42 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M234" t="n">
+        <v>5000</v>
+      </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="R234" t="n">
-        <v>2754406</v>
+        <v>0</v>
       </c>
       <c r="S234" t="inlineStr"/>
       <c r="T234" t="inlineStr"/>
@@ -16002,19 +16028,19 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2371</v>
+        <v>2321</v>
       </c>
       <c r="B235" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C235" t="n">
-        <v>609</v>
+        <v>302</v>
       </c>
       <c r="D235" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E235" t="n">
-        <v>4238</v>
+        <v>4222</v>
       </c>
       <c r="F235" t="n">
         <v>1</v>
@@ -16028,12 +16054,12 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L235" t="inlineStr"/>
@@ -16054,7 +16080,7 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>8311374</v>
+        <v>800291</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
@@ -16068,19 +16094,19 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2421</v>
+        <v>2321</v>
       </c>
       <c r="B236" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C236" t="n">
-        <v>544</v>
+        <v>302</v>
       </c>
       <c r="D236" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E236" t="n">
-        <v>1016</v>
+        <v>4222</v>
       </c>
       <c r="F236" t="n">
         <v>1</v>
@@ -16094,12 +16120,12 @@
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
@@ -16111,16 +16137,16 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>477508</v>
+        <v>174673</v>
       </c>
       <c r="R236" t="n">
         <v>0</v>
@@ -16134,19 +16160,19 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>3051</v>
+        <v>2321</v>
       </c>
       <c r="B237" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C237" t="n">
-        <v>364</v>
+        <v>302</v>
       </c>
       <c r="D237" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="E237" t="n">
-        <v>4016</v>
+        <v>4222</v>
       </c>
       <c r="F237" t="n">
         <v>1</v>
@@ -16157,10 +16183,12 @@
       <c r="H237" t="n">
         <v>236</v>
       </c>
-      <c r="I237" t="inlineStr"/>
+      <c r="I237" t="n">
+        <v>11877</v>
+      </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -16177,16 +16205,16 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>4825656</v>
+        <v>1088908</v>
       </c>
       <c r="R237" t="n">
         <v>0</v>
@@ -16200,19 +16228,19 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>3051</v>
+        <v>2361</v>
       </c>
       <c r="B238" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C238" t="n">
-        <v>364</v>
+        <v>846</v>
       </c>
       <c r="D238" t="n">
-        <v>15</v>
+        <v>705</v>
       </c>
       <c r="E238" t="n">
-        <v>4016</v>
+        <v>7004</v>
       </c>
       <c r="F238" t="n">
         <v>1</v>
@@ -16226,7 +16254,7 @@
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -16241,22 +16269,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O238" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P238" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q238" t="n">
-        <v>12649000</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0</v>
-      </c>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr"/>
@@ -16266,19 +16282,19 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3051</v>
+        <v>2361</v>
       </c>
       <c r="B239" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C239" t="n">
-        <v>364</v>
+        <v>274</v>
       </c>
       <c r="D239" t="n">
-        <v>15</v>
+        <v>766</v>
       </c>
       <c r="E239" t="n">
-        <v>4016</v>
+        <v>2113</v>
       </c>
       <c r="F239" t="n">
         <v>1</v>
@@ -16292,7 +16308,7 @@
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -16307,22 +16323,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P239" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q239" t="n">
-        <v>3715000</v>
-      </c>
-      <c r="R239" t="n">
-        <v>0</v>
-      </c>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="inlineStr"/>
@@ -16332,19 +16336,19 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>3051</v>
+        <v>2361</v>
       </c>
       <c r="B240" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C240" t="n">
-        <v>571</v>
+        <v>274</v>
       </c>
       <c r="D240" t="n">
-        <v>16</v>
+        <v>767</v>
       </c>
       <c r="E240" t="n">
-        <v>4018</v>
+        <v>2114</v>
       </c>
       <c r="F240" t="n">
         <v>1</v>
@@ -16358,7 +16362,7 @@
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Melhoria da infraestrutura da pesquisa.</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -16375,19 +16379,19 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q240" t="n">
         <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>250000</v>
+        <v>2754406</v>
       </c>
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr"/>
@@ -16398,19 +16402,19 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>3051</v>
+        <v>2371</v>
       </c>
       <c r="B241" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C241" t="n">
-        <v>571</v>
+        <v>609</v>
       </c>
       <c r="D241" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E241" t="n">
-        <v>4018</v>
+        <v>4238</v>
       </c>
       <c r="F241" t="n">
         <v>1</v>
@@ -16424,7 +16428,7 @@
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -16441,19 +16445,19 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>8311374</v>
       </c>
       <c r="R241" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr"/>
@@ -16464,19 +16468,19 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>4031</v>
+        <v>2421</v>
       </c>
       <c r="B242" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C242" t="n">
-        <v>61</v>
+        <v>544</v>
       </c>
       <c r="D242" t="n">
-        <v>706</v>
+        <v>101</v>
       </c>
       <c r="E242" t="n">
-        <v>2091</v>
+        <v>1016</v>
       </c>
       <c r="F242" t="n">
         <v>1</v>
@@ -16487,47 +16491,39 @@
       <c r="H242" t="n">
         <v>241</v>
       </c>
-      <c r="I242" t="n">
-        <v>12054</v>
-      </c>
+      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M242" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>0</v>
+        <v>477508</v>
       </c>
       <c r="R242" t="n">
-        <v>10431496</v>
+        <v>0</v>
       </c>
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="inlineStr"/>
@@ -16538,19 +16534,19 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B243" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C243" t="n">
-        <v>61</v>
+        <v>364</v>
       </c>
       <c r="D243" t="n">
-        <v>706</v>
+        <v>15</v>
       </c>
       <c r="E243" t="n">
-        <v>2091</v>
+        <v>4016</v>
       </c>
       <c r="F243" t="n">
         <v>1</v>
@@ -16561,17 +16557,15 @@
       <c r="H243" t="n">
         <v>242</v>
       </c>
-      <c r="I243" t="n">
-        <v>12702</v>
-      </c>
+      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>CINCÃO - Fornecimento e montagem de estante tipo porta-paletes e de planos metálicos para os armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente do TRIBUNAL</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L243" t="inlineStr"/>
@@ -16583,19 +16577,19 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>4825656</v>
       </c>
       <c r="R243" t="n">
-        <v>102247</v>
+        <v>0</v>
       </c>
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr"/>
@@ -16606,19 +16600,19 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B244" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C244" t="n">
-        <v>61</v>
+        <v>364</v>
       </c>
       <c r="D244" t="n">
-        <v>706</v>
+        <v>15</v>
       </c>
       <c r="E244" t="n">
-        <v>2091</v>
+        <v>4016</v>
       </c>
       <c r="F244" t="n">
         <v>1</v>
@@ -16629,30 +16623,22 @@
       <c r="H244" t="n">
         <v>243</v>
       </c>
-      <c r="I244" t="n">
-        <v>12806</v>
-      </c>
+      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M244" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -16666,10 +16652,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>0</v>
+        <v>12649000</v>
       </c>
       <c r="R244" t="n">
-        <v>19560087</v>
+        <v>0</v>
       </c>
       <c r="S244" t="inlineStr"/>
       <c r="T244" t="inlineStr"/>
@@ -16680,19 +16666,19 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B245" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C245" t="n">
-        <v>61</v>
+        <v>364</v>
       </c>
       <c r="D245" t="n">
-        <v>706</v>
+        <v>15</v>
       </c>
       <c r="E245" t="n">
-        <v>2091</v>
+        <v>4016</v>
       </c>
       <c r="F245" t="n">
         <v>1</v>
@@ -16703,30 +16689,22 @@
       <c r="H245" t="n">
         <v>244</v>
       </c>
-      <c r="I245" t="n">
-        <v>12638</v>
-      </c>
+      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M245" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -16740,10 +16718,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>0</v>
+        <v>3715000</v>
       </c>
       <c r="R245" t="n">
-        <v>19560087</v>
+        <v>0</v>
       </c>
       <c r="S245" t="inlineStr"/>
       <c r="T245" t="inlineStr"/>
@@ -16754,19 +16732,19 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B246" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C246" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D246" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E246" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F246" t="n">
         <v>1</v>
@@ -16777,17 +16755,15 @@
       <c r="H246" t="n">
         <v>245</v>
       </c>
-      <c r="I246" t="n">
-        <v>12568</v>
-      </c>
+      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Itabirito/MG.</t>
+          <t>Melhoria da infraestrutura da pesquisa.</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L246" t="inlineStr"/>
@@ -16811,7 +16787,7 @@
         <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>5550000</v>
+        <v>250000</v>
       </c>
       <c r="S246" t="inlineStr"/>
       <c r="T246" t="inlineStr"/>
@@ -16822,19 +16798,19 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B247" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C247" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D247" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E247" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F247" t="n">
         <v>1</v>
@@ -16845,17 +16821,15 @@
       <c r="H247" t="n">
         <v>246</v>
       </c>
-      <c r="I247" t="n">
-        <v>12627</v>
-      </c>
+      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L247" t="inlineStr"/>
@@ -16867,19 +16841,19 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q247" t="n">
         <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>4000000</v>
+        <v>250000</v>
       </c>
       <c r="S247" t="inlineStr"/>
       <c r="T247" t="inlineStr"/>
@@ -16914,11 +16888,11 @@
         <v>247</v>
       </c>
       <c r="I248" t="n">
-        <v>12146</v>
+        <v>12054</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -16926,28 +16900,34 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M248" t="n">
+        <v>1</v>
+      </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q248" t="n">
         <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>13121711</v>
+        <v>10431496</v>
       </c>
       <c r="S248" t="inlineStr"/>
       <c r="T248" t="inlineStr"/>
@@ -16982,11 +16962,11 @@
         <v>248</v>
       </c>
       <c r="I249" t="n">
-        <v>12400</v>
+        <v>12702</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t>CINCÃO - Fornecimento e montagem de estante tipo porta-paletes e de planos metálicos para os armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente do TRIBUNAL</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -16994,34 +16974,28 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M249" t="n">
-        <v>1</v>
-      </c>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q249" t="n">
         <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>18431199</v>
+        <v>102247</v>
       </c>
       <c r="S249" t="inlineStr"/>
       <c r="T249" t="inlineStr"/>
@@ -17056,11 +17030,11 @@
         <v>249</v>
       </c>
       <c r="I250" t="n">
-        <v>12288</v>
+        <v>12806</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -17095,7 +17069,7 @@
         <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>1950000</v>
+        <v>19560087</v>
       </c>
       <c r="S250" t="inlineStr"/>
       <c r="T250" t="inlineStr"/>
@@ -17106,19 +17080,19 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>5011</v>
+        <v>4031</v>
       </c>
       <c r="B251" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C251" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="D251" t="n">
-        <v>133</v>
+        <v>706</v>
       </c>
       <c r="E251" t="n">
-        <v>3017</v>
+        <v>2091</v>
       </c>
       <c r="F251" t="n">
         <v>1</v>
@@ -17129,22 +17103,30 @@
       <c r="H251" t="n">
         <v>250</v>
       </c>
-      <c r="I251" t="inlineStr"/>
+      <c r="I251" t="n">
+        <v>12638</v>
+      </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M251" t="n">
+        <v>1</v>
+      </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -17161,7 +17143,7 @@
         <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>800000</v>
+        <v>19560087</v>
       </c>
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr"/>
@@ -17172,19 +17154,19 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>5031</v>
+        <v>4031</v>
       </c>
       <c r="B252" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C252" t="n">
-        <v>572</v>
+        <v>61</v>
       </c>
       <c r="D252" t="n">
-        <v>133</v>
+        <v>706</v>
       </c>
       <c r="E252" t="n">
-        <v>3015</v>
+        <v>2091</v>
       </c>
       <c r="F252" t="n">
         <v>1</v>
@@ -17195,15 +17177,17 @@
       <c r="H252" t="n">
         <v>251</v>
       </c>
-      <c r="I252" t="inlineStr"/>
+      <c r="I252" t="n">
+        <v>12568</v>
+      </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
+          <t>Obra de construção do novo Fórum da Comarca de Itabirito/MG.</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L252" t="inlineStr"/>
@@ -17227,7 +17211,7 @@
         <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>4782988</v>
+        <v>5550000</v>
       </c>
       <c r="S252" t="inlineStr"/>
       <c r="T252" t="inlineStr"/>
@@ -17238,19 +17222,19 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>5141</v>
+        <v>4031</v>
       </c>
       <c r="B253" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C253" t="n">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="D253" t="n">
-        <v>30</v>
+        <v>706</v>
       </c>
       <c r="E253" t="n">
-        <v>6006</v>
+        <v>2091</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
@@ -17261,15 +17245,17 @@
       <c r="H253" t="n">
         <v>252</v>
       </c>
-      <c r="I253" t="inlineStr"/>
+      <c r="I253" t="n">
+        <v>12627</v>
+      </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L253" t="inlineStr"/>
@@ -17281,19 +17267,19 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q253" t="n">
         <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>16317109</v>
+        <v>4000000</v>
       </c>
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr"/>
@@ -17304,19 +17290,19 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>5391</v>
+        <v>4031</v>
       </c>
       <c r="B254" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C254" t="n">
-        <v>752</v>
+        <v>61</v>
       </c>
       <c r="D254" t="n">
-        <v>92</v>
+        <v>706</v>
       </c>
       <c r="E254" t="n">
-        <v>3004</v>
+        <v>2091</v>
       </c>
       <c r="F254" t="n">
         <v>1</v>
@@ -17327,15 +17313,17 @@
       <c r="H254" t="n">
         <v>253</v>
       </c>
-      <c r="I254" t="inlineStr"/>
+      <c r="I254" t="n">
+        <v>12146</v>
+      </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L254" t="inlineStr"/>
@@ -17352,14 +17340,14 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q254" t="n">
         <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>92004926</v>
+        <v>13121711</v>
       </c>
       <c r="S254" t="inlineStr"/>
       <c r="T254" t="inlineStr"/>
@@ -17370,19 +17358,19 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>5391</v>
+        <v>4031</v>
       </c>
       <c r="B255" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C255" t="n">
-        <v>752</v>
+        <v>61</v>
       </c>
       <c r="D255" t="n">
-        <v>92</v>
+        <v>706</v>
       </c>
       <c r="E255" t="n">
-        <v>3004</v>
+        <v>2091</v>
       </c>
       <c r="F255" t="n">
         <v>1</v>
@@ -17393,39 +17381,47 @@
       <c r="H255" t="n">
         <v>254</v>
       </c>
-      <c r="I255" t="inlineStr"/>
+      <c r="I255" t="n">
+        <v>12400</v>
+      </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M255" t="n">
+        <v>1</v>
+      </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q255" t="n">
         <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>10705994</v>
+        <v>18431199</v>
       </c>
       <c r="S255" t="inlineStr"/>
       <c r="T255" t="inlineStr"/>
@@ -17436,19 +17432,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>5391</v>
+        <v>4031</v>
       </c>
       <c r="B256" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C256" t="n">
-        <v>752</v>
+        <v>61</v>
       </c>
       <c r="D256" t="n">
-        <v>92</v>
+        <v>706</v>
       </c>
       <c r="E256" t="n">
-        <v>3004</v>
+        <v>2091</v>
       </c>
       <c r="F256" t="n">
         <v>1</v>
@@ -17459,39 +17455,47 @@
       <c r="H256" t="n">
         <v>255</v>
       </c>
-      <c r="I256" t="inlineStr"/>
+      <c r="I256" t="n">
+        <v>12288</v>
+      </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M256" t="n">
+        <v>1</v>
+      </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q256" t="n">
         <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>10464844</v>
+        <v>1950000</v>
       </c>
       <c r="S256" t="inlineStr"/>
       <c r="T256" t="inlineStr"/>
@@ -17502,19 +17506,19 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>5391</v>
+        <v>5011</v>
       </c>
       <c r="B257" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C257" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="D257" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E257" t="n">
-        <v>3004</v>
+        <v>3017</v>
       </c>
       <c r="F257" t="n">
         <v>1</v>
@@ -17528,7 +17532,7 @@
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -17545,19 +17549,19 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q257" t="n">
         <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>2098278</v>
+        <v>800000</v>
       </c>
       <c r="S257" t="inlineStr"/>
       <c r="T257" t="inlineStr"/>
@@ -17568,19 +17572,19 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>5391</v>
+        <v>5031</v>
       </c>
       <c r="B258" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C258" t="n">
-        <v>752</v>
+        <v>572</v>
       </c>
       <c r="D258" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E258" t="n">
-        <v>3004</v>
+        <v>3015</v>
       </c>
       <c r="F258" t="n">
         <v>1</v>
@@ -17594,7 +17598,7 @@
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -17623,7 +17627,7 @@
         <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>96721858</v>
+        <v>4782988</v>
       </c>
       <c r="S258" t="inlineStr"/>
       <c r="T258" t="inlineStr"/>
@@ -17634,19 +17638,19 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>5391</v>
+        <v>5141</v>
       </c>
       <c r="B259" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C259" t="n">
-        <v>752</v>
+        <v>126</v>
       </c>
       <c r="D259" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="E259" t="n">
-        <v>3004</v>
+        <v>6006</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -17660,7 +17664,7 @@
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -17677,19 +17681,19 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q259" t="n">
         <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>16415074</v>
+        <v>16317109</v>
       </c>
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr"/>
@@ -17743,19 +17747,19 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>1</v>
+        <v>92004926</v>
       </c>
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr"/>
@@ -17778,7 +17782,7 @@
         <v>92</v>
       </c>
       <c r="E261" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F261" t="n">
         <v>1</v>
@@ -17792,7 +17796,7 @@
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17809,19 +17813,19 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q261" t="n">
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>126817302</v>
+        <v>10705994</v>
       </c>
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr"/>
@@ -17844,7 +17848,7 @@
         <v>92</v>
       </c>
       <c r="E262" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F262" t="n">
         <v>1</v>
@@ -17858,7 +17862,7 @@
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -17875,19 +17879,19 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>16058991</v>
+        <v>10464844</v>
       </c>
       <c r="S262" t="inlineStr"/>
       <c r="T262" t="inlineStr"/>
@@ -17910,7 +17914,7 @@
         <v>92</v>
       </c>
       <c r="E263" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F263" t="n">
         <v>1</v>
@@ -17924,7 +17928,7 @@
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -17941,19 +17945,19 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>65795530</v>
+        <v>2098278</v>
       </c>
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr"/>
@@ -17976,7 +17980,7 @@
         <v>92</v>
       </c>
       <c r="E264" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F264" t="n">
         <v>1</v>
@@ -17990,7 +17994,7 @@
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -18007,19 +18011,19 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>44156794</v>
+        <v>96721858</v>
       </c>
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr"/>
@@ -18042,7 +18046,7 @@
         <v>92</v>
       </c>
       <c r="E265" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F265" t="n">
         <v>1</v>
@@ -18056,7 +18060,7 @@
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -18073,19 +18077,19 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>140716908</v>
+        <v>16415074</v>
       </c>
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr"/>
@@ -18108,7 +18112,7 @@
         <v>92</v>
       </c>
       <c r="E266" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F266" t="n">
         <v>1</v>
@@ -18122,7 +18126,7 @@
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -18151,7 +18155,7 @@
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>8715687</v>
+        <v>1</v>
       </c>
       <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr"/>
@@ -18205,19 +18209,19 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>24622611</v>
+        <v>126817302</v>
       </c>
       <c r="S267" t="inlineStr"/>
       <c r="T267" t="inlineStr"/>
@@ -18237,10 +18241,10 @@
         <v>752</v>
       </c>
       <c r="D268" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E268" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="F268" t="n">
         <v>1</v>
@@ -18254,7 +18258,7 @@
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Expansão do Sistema de Geração</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -18271,19 +18275,19 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>1</v>
+        <v>16058991</v>
       </c>
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr"/>
@@ -18292,6 +18296,402 @@
       <c r="W268" t="inlineStr"/>
       <c r="X268" t="inlineStr"/>
     </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B269" t="n">
+        <v>25</v>
+      </c>
+      <c r="C269" t="n">
+        <v>752</v>
+      </c>
+      <c r="D269" t="n">
+        <v>92</v>
+      </c>
+      <c r="E269" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="n">
+        <v>268</v>
+      </c>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Juíz de Fora</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>0</v>
+      </c>
+      <c r="R269" t="n">
+        <v>65795530</v>
+      </c>
+      <c r="S269" t="inlineStr"/>
+      <c r="T269" t="inlineStr"/>
+      <c r="U269" t="inlineStr"/>
+      <c r="V269" t="inlineStr"/>
+      <c r="W269" t="inlineStr"/>
+      <c r="X269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B270" t="n">
+        <v>25</v>
+      </c>
+      <c r="C270" t="n">
+        <v>752</v>
+      </c>
+      <c r="D270" t="n">
+        <v>92</v>
+      </c>
+      <c r="E270" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F270" t="n">
+        <v>1</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="n">
+        <v>269</v>
+      </c>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Uberlândia</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>44156794</v>
+      </c>
+      <c r="S270" t="inlineStr"/>
+      <c r="T270" t="inlineStr"/>
+      <c r="U270" t="inlineStr"/>
+      <c r="V270" t="inlineStr"/>
+      <c r="W270" t="inlineStr"/>
+      <c r="X270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B271" t="n">
+        <v>25</v>
+      </c>
+      <c r="C271" t="n">
+        <v>752</v>
+      </c>
+      <c r="D271" t="n">
+        <v>92</v>
+      </c>
+      <c r="E271" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>270</v>
+      </c>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="n">
+        <v>140716908</v>
+      </c>
+      <c r="S271" t="inlineStr"/>
+      <c r="T271" t="inlineStr"/>
+      <c r="U271" t="inlineStr"/>
+      <c r="V271" t="inlineStr"/>
+      <c r="W271" t="inlineStr"/>
+      <c r="X271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B272" t="n">
+        <v>25</v>
+      </c>
+      <c r="C272" t="n">
+        <v>752</v>
+      </c>
+      <c r="D272" t="n">
+        <v>92</v>
+      </c>
+      <c r="E272" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F272" t="n">
+        <v>1</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" t="n">
+        <v>271</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Ipatinga</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>0</v>
+      </c>
+      <c r="R272" t="n">
+        <v>8715687</v>
+      </c>
+      <c r="S272" t="inlineStr"/>
+      <c r="T272" t="inlineStr"/>
+      <c r="U272" t="inlineStr"/>
+      <c r="V272" t="inlineStr"/>
+      <c r="W272" t="inlineStr"/>
+      <c r="X272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B273" t="n">
+        <v>25</v>
+      </c>
+      <c r="C273" t="n">
+        <v>752</v>
+      </c>
+      <c r="D273" t="n">
+        <v>92</v>
+      </c>
+      <c r="E273" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>272</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Uberaba</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>0</v>
+      </c>
+      <c r="R273" t="n">
+        <v>24622611</v>
+      </c>
+      <c r="S273" t="inlineStr"/>
+      <c r="T273" t="inlineStr"/>
+      <c r="U273" t="inlineStr"/>
+      <c r="V273" t="inlineStr"/>
+      <c r="W273" t="inlineStr"/>
+      <c r="X273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B274" t="n">
+        <v>25</v>
+      </c>
+      <c r="C274" t="n">
+        <v>752</v>
+      </c>
+      <c r="D274" t="n">
+        <v>94</v>
+      </c>
+      <c r="E274" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" t="n">
+        <v>273</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Expansão do Sistema de Geração</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>0</v>
+      </c>
+      <c r="R274" t="n">
+        <v>1</v>
+      </c>
+      <c r="S274" t="inlineStr"/>
+      <c r="T274" t="inlineStr"/>
+      <c r="U274" t="inlineStr"/>
+      <c r="V274" t="inlineStr"/>
+      <c r="W274" t="inlineStr"/>
+      <c r="X274" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X274"/>
+  <dimension ref="A1:X277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,10 +1217,12 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1283,10 +1285,12 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1349,10 +1353,12 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1415,10 +1421,12 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1481,10 +1489,12 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1547,10 +1557,12 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1613,10 +1625,12 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1679,10 +1693,12 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1745,10 +1761,12 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1811,10 +1829,12 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1877,10 +1897,12 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1943,10 +1965,12 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2009,10 +2033,12 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2075,10 +2101,12 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2141,10 +2169,12 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2207,10 +2237,12 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2273,10 +2305,12 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2339,10 +2373,12 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2405,10 +2441,12 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2471,10 +2509,12 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2537,10 +2577,12 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2603,10 +2645,12 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2669,10 +2713,12 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2735,10 +2781,12 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2801,10 +2849,12 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2867,28 +2917,18 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>250000000</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -2933,10 +2973,12 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2999,10 +3041,12 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3065,10 +3109,12 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3131,10 +3177,12 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3197,10 +3245,12 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3263,10 +3313,12 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3329,10 +3381,12 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3395,10 +3449,12 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3461,10 +3517,12 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3527,10 +3585,12 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3593,10 +3653,12 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3659,10 +3721,12 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3725,10 +3789,12 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="n">
+        <v>1</v>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3791,10 +3857,12 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3857,10 +3925,12 @@
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3923,10 +3993,12 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3989,10 +4061,12 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4055,10 +4129,12 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4121,10 +4197,12 @@
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4187,10 +4265,12 @@
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4253,10 +4333,12 @@
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4319,10 +4401,12 @@
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4385,10 +4469,12 @@
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4451,10 +4537,12 @@
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4517,10 +4605,12 @@
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="n">
+        <v>1</v>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4583,10 +4673,12 @@
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4649,10 +4741,12 @@
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4715,10 +4809,12 @@
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4781,10 +4877,12 @@
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4847,10 +4945,12 @@
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4913,10 +5013,12 @@
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4979,10 +5081,12 @@
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5045,10 +5149,12 @@
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="n">
+        <v>1</v>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5111,10 +5217,12 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5196,7 +5304,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>280106</v>
       </c>
       <c r="R71" t="n">
         <v>519640</v>
@@ -5264,7 +5372,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>894720</v>
       </c>
       <c r="R72" t="n">
         <v>4087644</v>
@@ -5332,7 +5440,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>8264640</v>
       </c>
       <c r="R73" t="n">
         <v>19153735</v>
@@ -5400,7 +5508,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3155040</v>
       </c>
       <c r="R74" t="n">
         <v>23943007</v>
@@ -5468,7 +5576,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4840800</v>
       </c>
       <c r="R75" t="n">
         <v>26593690</v>
@@ -5536,7 +5644,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>613500</v>
       </c>
       <c r="R76" t="n">
         <v>2870210</v>
@@ -5604,7 +5712,7 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>5963400</v>
       </c>
       <c r="R77" t="n">
         <v>23280000</v>
@@ -5672,7 +5780,7 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3620820</v>
       </c>
       <c r="R78" t="n">
         <v>19100000</v>
@@ -5806,10 +5914,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>1839798</v>
       </c>
       <c r="R80" t="n">
-        <v>300000</v>
+        <v>3269655</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
@@ -5832,7 +5940,7 @@
         <v>99</v>
       </c>
       <c r="E81" t="n">
-        <v>4262</v>
+        <v>1038</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -5843,10 +5951,12 @@
       <c r="H81" t="n">
         <v>80</v>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>11531</v>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
+          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5863,16 +5973,16 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>10932874</v>
+        <v>222899</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
@@ -5889,16 +5999,16 @@
         <v>1301</v>
       </c>
       <c r="B82" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C82" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D82" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E82" t="n">
-        <v>4290</v>
+        <v>4262</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -5909,12 +6019,10 @@
       <c r="H82" t="n">
         <v>81</v>
       </c>
-      <c r="I82" t="n">
-        <v>12510</v>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
+          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5931,19 +6039,19 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>10932874</v>
       </c>
       <c r="R82" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
@@ -5977,15 +6085,17 @@
       <c r="H83" t="n">
         <v>82</v>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>12510</v>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
+          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6006,10 +6116,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478579</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
@@ -6046,7 +6156,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6072,7 +6182,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>2246479</v>
+        <v>478579</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -6112,7 +6222,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6138,7 +6248,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>156926</v>
+        <v>2246479</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -6155,16 +6265,16 @@
         <v>1301</v>
       </c>
       <c r="B86" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C86" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D86" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E86" t="n">
-        <v>1036</v>
+        <v>4290</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -6175,17 +6285,15 @@
       <c r="H86" t="n">
         <v>85</v>
       </c>
-      <c r="I86" t="n">
-        <v>12453</v>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6197,19 +6305,19 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>156926</v>
       </c>
       <c r="R86" t="n">
-        <v>539924</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
@@ -6244,11 +6352,11 @@
         <v>86</v>
       </c>
       <c r="I87" t="n">
-        <v>12454</v>
+        <v>12453</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
+          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6270,14 +6378,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>15337533</v>
+        <v>539924</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
@@ -6312,11 +6420,11 @@
         <v>87</v>
       </c>
       <c r="I88" t="n">
-        <v>11521</v>
+        <v>12454</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6333,19 +6441,19 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>SABARÁ</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>1440021</v>
+        <v>15337533</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
@@ -6380,11 +6488,11 @@
         <v>88</v>
       </c>
       <c r="I89" t="n">
-        <v>11519</v>
+        <v>11521</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6401,19 +6509,19 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>SABARÁ</t>
         </is>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>6942767</v>
+        <v>1440021</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
@@ -6448,16 +6556,16 @@
         <v>89</v>
       </c>
       <c r="I90" t="n">
-        <v>11512</v>
+        <v>11519</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
+          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -6474,14 +6582,14 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>14686005</v>
+        <v>6942767</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
@@ -6516,16 +6624,16 @@
         <v>90</v>
       </c>
       <c r="I91" t="n">
-        <v>11514</v>
+        <v>11512</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
+          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -6537,19 +6645,19 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>52160376</v>
+        <v>14686005</v>
       </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
@@ -6584,11 +6692,11 @@
         <v>91</v>
       </c>
       <c r="I92" t="n">
-        <v>11511</v>
+        <v>11514</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
+          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6605,19 +6713,19 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>20521500</v>
+        <v>52160376</v>
       </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
@@ -6652,11 +6760,11 @@
         <v>92</v>
       </c>
       <c r="I93" t="n">
-        <v>11520</v>
+        <v>11511</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6673,19 +6781,19 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>SANTA LUZIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>6952445</v>
+        <v>20521500</v>
       </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
@@ -6720,11 +6828,11 @@
         <v>93</v>
       </c>
       <c r="I94" t="n">
-        <v>11513</v>
+        <v>11520</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
+          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6741,19 +6849,19 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SANTA LUZIA</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>12959175</v>
+        <v>6952445</v>
       </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
@@ -6788,11 +6896,11 @@
         <v>94</v>
       </c>
       <c r="I95" t="n">
-        <v>11977</v>
+        <v>11513</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6809,19 +6917,19 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>CATAGUASES</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>38244490</v>
+        <v>12959175</v>
       </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
@@ -6844,7 +6952,7 @@
         <v>139</v>
       </c>
       <c r="E96" t="n">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
@@ -6856,11 +6964,11 @@
         <v>95</v>
       </c>
       <c r="I96" t="n">
-        <v>11855</v>
+        <v>11977</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
+          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6877,19 +6985,19 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CATAGUASES</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>6286532</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2728583</v>
+        <v>38244490</v>
       </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
@@ -6912,7 +7020,7 @@
         <v>139</v>
       </c>
       <c r="E97" t="n">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
@@ -6924,11 +7032,11 @@
         <v>96</v>
       </c>
       <c r="I97" t="n">
-        <v>11973</v>
+        <v>11162</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
+          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6945,16 +7053,16 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>193263</v>
+        <v>9858067</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
@@ -6968,19 +7076,19 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="B98" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C98" t="n">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="D98" t="n">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="E98" t="n">
-        <v>4118</v>
+        <v>1039</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
@@ -6991,15 +7099,17 @@
       <c r="H98" t="n">
         <v>97</v>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>12699</v>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RIMC</t>
+          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -7011,19 +7121,19 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>299895</v>
       </c>
       <c r="R98" t="n">
-        <v>4547000</v>
+        <v>0</v>
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
@@ -7034,19 +7144,19 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="B99" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C99" t="n">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="D99" t="n">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="E99" t="n">
-        <v>4118</v>
+        <v>1039</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -7057,15 +7167,17 @@
       <c r="H99" t="n">
         <v>98</v>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="n">
+        <v>11536</v>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RITO</t>
+          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -7077,19 +7189,19 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>4565604</v>
       </c>
       <c r="R99" t="n">
-        <v>4547000</v>
+        <v>0</v>
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
@@ -7100,38 +7212,40 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B100" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C100" t="n">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="D100" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E100" t="n">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="F100" t="n">
         <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>99</v>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>11855</v>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
+          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -7143,19 +7257,19 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>904245</v>
+        <v>6286532</v>
       </c>
       <c r="R100" t="n">
-        <v>44308050</v>
+        <v>2728583</v>
       </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
@@ -7166,38 +7280,40 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1451</v>
+        <v>1301</v>
       </c>
       <c r="B101" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C101" t="n">
-        <v>243</v>
+        <v>451</v>
       </c>
       <c r="D101" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E101" t="n">
-        <v>4441</v>
+        <v>1041</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>100</v>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>11973</v>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -7214,11 +7330,11 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>6999284</v>
+        <v>193263</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -7232,25 +7348,25 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1451</v>
+        <v>1371</v>
       </c>
       <c r="B102" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C102" t="n">
-        <v>243</v>
+        <v>511</v>
       </c>
       <c r="D102" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="E102" t="n">
-        <v>4441</v>
+        <v>4118</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
         <v>101</v>
@@ -7258,12 +7374,12 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Programa Água Doce - RIMC</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -7275,19 +7391,19 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651694</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>4547000</v>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -7298,25 +7414,25 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1451</v>
+        <v>1371</v>
       </c>
       <c r="B103" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C103" t="n">
-        <v>243</v>
+        <v>511</v>
       </c>
       <c r="D103" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="E103" t="n">
-        <v>4441</v>
+        <v>4118</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
         <v>102</v>
@@ -7324,12 +7440,12 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Programa Água Doce - RITO</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -7341,19 +7457,19 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>ALFENAS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>651694</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>4547000</v>
       </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
@@ -7370,13 +7486,13 @@
         <v>6</v>
       </c>
       <c r="C104" t="n">
-        <v>243</v>
+        <v>421</v>
       </c>
       <c r="D104" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E104" t="n">
-        <v>4441</v>
+        <v>1048</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
@@ -7390,7 +7506,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7407,19 +7523,19 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>1472757</v>
+        <v>904245</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>44308050</v>
       </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
@@ -7473,16 +7589,16 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>651694</v>
+        <v>6999284</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
@@ -7539,16 +7655,16 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>18572878</v>
+        <v>651694</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -7562,25 +7678,25 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B107" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C107" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D107" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E107" t="n">
-        <v>4476</v>
+        <v>4441</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
         <v>106</v>
@@ -7588,12 +7704,12 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -7605,16 +7721,16 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ALFENAS</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>270000</v>
+        <v>651694</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -7628,25 +7744,25 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B108" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C108" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D108" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E108" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F108" t="n">
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" t="n">
         <v>107</v>
@@ -7654,12 +7770,12 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -7676,11 +7792,11 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>1100000</v>
+        <v>1472757</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
@@ -7694,25 +7810,25 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C109" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D109" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E109" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
         <v>108</v>
@@ -7720,12 +7836,12 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -7737,16 +7853,16 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>624000</v>
+        <v>651694</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -7760,25 +7876,25 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C110" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D110" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E110" t="n">
-        <v>4465</v>
+        <v>4441</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
         <v>109</v>
@@ -7786,12 +7902,12 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -7803,16 +7919,16 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>210000</v>
+        <v>18572878</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -7835,10 +7951,10 @@
         <v>122</v>
       </c>
       <c r="D111" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E111" t="n">
-        <v>4465</v>
+        <v>4476</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
@@ -7852,7 +7968,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7878,7 +7994,7 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>150000</v>
+        <v>270000</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -7918,7 +8034,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
+          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7944,7 +8060,7 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>3918408</v>
+        <v>1100000</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
@@ -7967,10 +8083,10 @@
         <v>122</v>
       </c>
       <c r="D113" t="n">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="E113" t="n">
-        <v>2500</v>
+        <v>4465</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -7984,7 +8100,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
+          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7992,17 +8108,11 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M113" t="n">
-        <v>1</v>
-      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8016,7 +8126,7 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>282000</v>
+        <v>624000</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -8030,19 +8140,19 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="B114" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C114" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D114" t="n">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="E114" t="n">
-        <v>1006</v>
+        <v>4465</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
@@ -8056,7 +8166,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
+          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -8073,19 +8183,19 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="R114" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
@@ -8096,19 +8206,19 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="B115" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D115" t="n">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="E115" t="n">
-        <v>4063</v>
+        <v>4465</v>
       </c>
       <c r="F115" t="n">
         <v>1</v>
@@ -8122,7 +8232,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
+          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8144,14 +8254,14 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q115" t="n">
         <v>150000</v>
       </c>
       <c r="R115" t="n">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
@@ -8162,19 +8272,19 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1541</v>
+        <v>1501</v>
       </c>
       <c r="B116" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C116" t="n">
         <v>122</v>
       </c>
       <c r="D116" t="n">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="E116" t="n">
-        <v>2500</v>
+        <v>4465</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
@@ -8188,12 +8298,12 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
+          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -8214,7 +8324,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>2896100</v>
+        <v>3918408</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
@@ -8228,19 +8338,19 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2011</v>
+        <v>1501</v>
       </c>
       <c r="B117" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D117" t="n">
-        <v>88</v>
+        <v>705</v>
       </c>
       <c r="E117" t="n">
-        <v>4231</v>
+        <v>2500</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -8251,12 +8361,10 @@
       <c r="H117" t="n">
         <v>116</v>
       </c>
-      <c r="I117" t="n">
-        <v>12871</v>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
+          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8264,11 +8372,17 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>1</v>
+      </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -8282,10 +8396,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>282000</v>
       </c>
       <c r="R117" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
@@ -8296,19 +8410,19 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2011</v>
+        <v>1511</v>
       </c>
       <c r="B118" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C118" t="n">
-        <v>302</v>
+        <v>181</v>
       </c>
       <c r="D118" t="n">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="E118" t="n">
-        <v>4231</v>
+        <v>1006</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -8319,12 +8433,10 @@
       <c r="H118" t="n">
         <v>117</v>
       </c>
-      <c r="I118" t="n">
-        <v>9999</v>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
+          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8341,19 +8453,19 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>1600000</v>
+        <v>1000000</v>
       </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
@@ -8364,19 +8476,19 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2011</v>
+        <v>1511</v>
       </c>
       <c r="B119" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C119" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="D119" t="n">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="E119" t="n">
-        <v>2500</v>
+        <v>4063</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -8387,12 +8499,10 @@
       <c r="H119" t="n">
         <v>118</v>
       </c>
-      <c r="I119" t="n">
-        <v>12690</v>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
+          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8414,14 +8524,14 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="R119" t="n">
-        <v>2200000</v>
+        <v>20000000</v>
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
@@ -8432,19 +8542,19 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2151</v>
+        <v>1541</v>
       </c>
       <c r="B120" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C120" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="D120" t="n">
-        <v>75</v>
+        <v>705</v>
       </c>
       <c r="E120" t="n">
-        <v>1023</v>
+        <v>2500</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -8458,12 +8568,12 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
+          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -8480,11 +8590,11 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>200000</v>
+        <v>2896100</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
@@ -8498,19 +8608,19 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2151</v>
+        <v>2011</v>
       </c>
       <c r="B121" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C121" t="n">
-        <v>122</v>
+        <v>302</v>
       </c>
       <c r="D121" t="n">
-        <v>705</v>
+        <v>88</v>
       </c>
       <c r="E121" t="n">
-        <v>2500</v>
+        <v>4231</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -8521,10 +8631,12 @@
       <c r="H121" t="n">
         <v>120</v>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="n">
+        <v>12871</v>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
+          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8546,14 +8658,14 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
@@ -8564,19 +8676,19 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2301</v>
+        <v>2011</v>
       </c>
       <c r="B122" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C122" t="n">
-        <v>782</v>
+        <v>302</v>
       </c>
       <c r="D122" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E122" t="n">
-        <v>4268</v>
+        <v>4231</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -8587,10 +8699,12 @@
       <c r="H122" t="n">
         <v>121</v>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>9999</v>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
+          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8607,19 +8721,19 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>5000000</v>
+        <v>1600000</v>
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
@@ -8630,19 +8744,19 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2301</v>
+        <v>2011</v>
       </c>
       <c r="B123" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C123" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D123" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E123" t="n">
-        <v>4268</v>
+        <v>2500</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -8653,10 +8767,12 @@
       <c r="H123" t="n">
         <v>122</v>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="n">
+        <v>12690</v>
+      </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
+          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8673,19 +8789,19 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>5000000</v>
+        <v>2200000</v>
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
@@ -8696,19 +8812,19 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2301</v>
+        <v>2151</v>
       </c>
       <c r="B124" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C124" t="n">
-        <v>782</v>
+        <v>572</v>
       </c>
       <c r="D124" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E124" t="n">
-        <v>4268</v>
+        <v>1023</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -8722,7 +8838,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8739,19 +8855,19 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="R124" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
@@ -8762,19 +8878,19 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2301</v>
+        <v>2151</v>
       </c>
       <c r="B125" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C125" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D125" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E125" t="n">
-        <v>4268</v>
+        <v>2500</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -8788,7 +8904,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
+          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8805,16 +8921,16 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>9792000</v>
+        <v>1500000</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
@@ -8854,7 +8970,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
+          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8880,10 +8996,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
@@ -8920,7 +9036,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
+          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8946,10 +9062,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>143000</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
@@ -8986,7 +9102,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
+          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -9012,10 +9128,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>5876140</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
@@ -9052,7 +9168,7 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
+          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -9078,7 +9194,7 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>1132500</v>
+        <v>9792000</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -9118,7 +9234,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
+          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -9184,7 +9300,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
+          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -9210,7 +9326,7 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>34710000</v>
+        <v>143000</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -9250,7 +9366,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -9276,7 +9392,7 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>59000000</v>
+        <v>5876140</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -9316,7 +9432,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9342,7 +9458,7 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>1000000</v>
+        <v>1132500</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -9382,7 +9498,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
+          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -9448,7 +9564,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9474,7 +9590,7 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>200000</v>
+        <v>34710000</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
@@ -9514,7 +9630,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9540,7 +9656,7 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>1000000</v>
+        <v>59000000</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
@@ -9580,7 +9696,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9606,7 +9722,7 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>30980000</v>
+        <v>1000000</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
@@ -9646,7 +9762,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9672,7 +9788,7 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>25655000</v>
+        <v>1000000</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
@@ -9712,7 +9828,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9738,7 +9854,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>66560000</v>
+        <v>200000</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -9778,7 +9894,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9844,7 +9960,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9870,7 +9986,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>25464500</v>
+        <v>30980000</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
@@ -9896,7 +10012,7 @@
         <v>81</v>
       </c>
       <c r="E142" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -9910,7 +10026,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9936,7 +10052,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>100000</v>
+        <v>25655000</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
@@ -9962,7 +10078,7 @@
         <v>81</v>
       </c>
       <c r="E143" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
@@ -9976,7 +10092,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
+          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -10002,7 +10118,7 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>24000000</v>
+        <v>66560000</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -10028,7 +10144,7 @@
         <v>81</v>
       </c>
       <c r="E144" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F144" t="n">
         <v>1</v>
@@ -10042,7 +10158,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
+          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -10068,7 +10184,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>252000</v>
+        <v>1000000</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
@@ -10094,7 +10210,7 @@
         <v>81</v>
       </c>
       <c r="E145" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -10108,7 +10224,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10134,7 +10250,7 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>319200</v>
+        <v>25464500</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -10174,7 +10290,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -10200,7 +10316,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>495600</v>
+        <v>100000</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
@@ -10240,7 +10356,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
+          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -10266,7 +10382,7 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>679000</v>
+        <v>24000000</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
@@ -10306,7 +10422,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
+          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10332,7 +10448,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>440000</v>
+        <v>252000</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
@@ -10372,7 +10488,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10398,7 +10514,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>14920000</v>
+        <v>319200</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -10438,7 +10554,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10464,7 +10580,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>8798400</v>
+        <v>495600</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -10504,7 +10620,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10530,7 +10646,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>369600</v>
+        <v>679000</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
@@ -10570,7 +10686,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10596,7 +10712,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>1000000</v>
+        <v>440000</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -10636,7 +10752,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10662,7 +10778,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>1203643</v>
+        <v>14920000</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
@@ -10702,7 +10818,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10728,7 +10844,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>730000</v>
+        <v>8798400</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
@@ -10768,7 +10884,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
+          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10794,7 +10910,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>66619</v>
+        <v>369600</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -10834,7 +10950,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
+          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10860,7 +10976,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>901000</v>
+        <v>1000000</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
@@ -10900,7 +11016,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10926,7 +11042,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>100000</v>
+        <v>1203643</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -10966,7 +11082,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10992,7 +11108,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>170000</v>
+        <v>730000</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
@@ -11032,7 +11148,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
+          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -11058,7 +11174,7 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>2940000</v>
+        <v>66619</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -11098,7 +11214,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -11124,7 +11240,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>810000</v>
+        <v>901000</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
@@ -11164,7 +11280,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
+          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -11190,7 +11306,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>542000</v>
+        <v>100000</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
@@ -11230,7 +11346,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
+          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -11256,7 +11372,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>2163814</v>
+        <v>170000</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
@@ -11296,7 +11412,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
+          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -11322,7 +11438,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>25000000</v>
+        <v>2940000</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
@@ -11362,7 +11478,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
+          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -11388,7 +11504,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>500000</v>
+        <v>810000</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
@@ -11428,7 +11544,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
+          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11454,7 +11570,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>1382535</v>
+        <v>542000</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
@@ -11494,7 +11610,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11520,7 +11636,7 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>1000000</v>
+        <v>2163814</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
@@ -11560,7 +11676,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11586,7 +11702,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>900000</v>
+        <v>25000000</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
@@ -11626,7 +11742,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
+          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11652,7 +11768,7 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>168000</v>
+        <v>500000</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
@@ -11692,7 +11808,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
+          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11718,7 +11834,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>249000</v>
+        <v>1382535</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
@@ -11758,7 +11874,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11784,7 +11900,7 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>705000</v>
+        <v>1000000</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
@@ -11824,7 +11940,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11850,7 +11966,7 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>58800</v>
+        <v>900000</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
@@ -11890,7 +12006,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -11916,7 +12032,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>725000</v>
+        <v>168000</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
@@ -11942,7 +12058,7 @@
         <v>81</v>
       </c>
       <c r="E173" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F173" t="n">
         <v>1</v>
@@ -11956,7 +12072,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -11982,10 +12098,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>249000</v>
       </c>
       <c r="R173" t="n">
-        <v>82286728</v>
+        <v>0</v>
       </c>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
@@ -12008,7 +12124,7 @@
         <v>81</v>
       </c>
       <c r="E174" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F174" t="n">
         <v>1</v>
@@ -12022,7 +12138,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
+          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -12048,10 +12164,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>705000</v>
       </c>
       <c r="R174" t="n">
-        <v>22137718</v>
+        <v>0</v>
       </c>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
@@ -12074,7 +12190,7 @@
         <v>81</v>
       </c>
       <c r="E175" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F175" t="n">
         <v>1</v>
@@ -12088,7 +12204,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
+          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -12114,10 +12230,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>58800</v>
       </c>
       <c r="R175" t="n">
-        <v>21757581</v>
+        <v>0</v>
       </c>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
@@ -12140,7 +12256,7 @@
         <v>81</v>
       </c>
       <c r="E176" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F176" t="n">
         <v>1</v>
@@ -12154,7 +12270,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
+          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -12180,10 +12296,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>725000</v>
       </c>
       <c r="R176" t="n">
-        <v>8036364</v>
+        <v>0</v>
       </c>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
@@ -12220,7 +12336,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
+          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -12249,7 +12365,7 @@
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>14063636</v>
+        <v>82286728</v>
       </c>
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
@@ -12286,7 +12402,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
+          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -12315,7 +12431,7 @@
         <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>8100000</v>
+        <v>22137718</v>
       </c>
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
@@ -12352,7 +12468,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
+          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -12381,7 +12497,7 @@
         <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>4804860</v>
+        <v>21757581</v>
       </c>
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
@@ -12418,7 +12534,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
+          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -12447,7 +12563,7 @@
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>6000001</v>
+        <v>8036364</v>
       </c>
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
@@ -12484,7 +12600,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
+          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -12510,10 +12626,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>11326937</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>14063636</v>
       </c>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr"/>
@@ -12550,7 +12666,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
+          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12576,10 +12692,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>19000000</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>8100000</v>
       </c>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
@@ -12616,7 +12732,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12642,10 +12758,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>74941120</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>4804860</v>
       </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
@@ -12682,7 +12798,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
+          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12708,10 +12824,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>38460000</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>6000001</v>
       </c>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
@@ -12748,7 +12864,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -12774,7 +12890,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>1000000</v>
+        <v>11326937</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
@@ -12814,7 +12930,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12840,7 +12956,7 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>7000000</v>
+        <v>19000000</v>
       </c>
       <c r="R186" t="n">
         <v>0</v>
@@ -12880,7 +12996,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
+          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -12906,7 +13022,7 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>1000000</v>
+        <v>74941120</v>
       </c>
       <c r="R187" t="n">
         <v>0</v>
@@ -12946,7 +13062,7 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
+          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -12972,7 +13088,7 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>6121131</v>
+        <v>38460000</v>
       </c>
       <c r="R188" t="n">
         <v>0</v>
@@ -13012,7 +13128,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
+          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -13078,7 +13194,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
+          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -13104,7 +13220,7 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="R190" t="n">
         <v>0</v>
@@ -13144,7 +13260,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
+          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -13210,7 +13326,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
+          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -13236,7 +13352,7 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>1000000</v>
+        <v>6121131</v>
       </c>
       <c r="R192" t="n">
         <v>0</v>
@@ -13276,7 +13392,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
+          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -13342,7 +13458,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -13408,7 +13524,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
+          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13434,7 +13550,7 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>431808</v>
+        <v>1000000</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
@@ -13474,7 +13590,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
+          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13540,7 +13656,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
+          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13606,7 +13722,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
+          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13672,7 +13788,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
+          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13698,7 +13814,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>14356788</v>
+        <v>431808</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
@@ -13738,7 +13854,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
+          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13764,7 +13880,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
@@ -13804,7 +13920,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
+          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13870,7 +13986,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
+          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -13896,7 +14012,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>35359852</v>
+        <v>1000000</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -13936,7 +14052,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
+          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -13962,7 +14078,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>29030000</v>
+        <v>14356788</v>
       </c>
       <c r="R203" t="n">
         <v>0</v>
@@ -14002,7 +14118,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
+          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -14028,7 +14144,7 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="R204" t="n">
         <v>0</v>
@@ -14068,7 +14184,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
+          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -14094,7 +14210,7 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>3541727</v>
+        <v>1000000</v>
       </c>
       <c r="R205" t="n">
         <v>0</v>
@@ -14134,7 +14250,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
+          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -14160,7 +14276,7 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>31280000</v>
+        <v>35359852</v>
       </c>
       <c r="R206" t="n">
         <v>0</v>
@@ -14186,7 +14302,7 @@
         <v>81</v>
       </c>
       <c r="E207" t="n">
-        <v>4287</v>
+        <v>4275</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -14200,7 +14316,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -14226,7 +14342,7 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>1000</v>
+        <v>29030000</v>
       </c>
       <c r="R207" t="n">
         <v>0</v>
@@ -14252,7 +14368,7 @@
         <v>81</v>
       </c>
       <c r="E208" t="n">
-        <v>4289</v>
+        <v>4275</v>
       </c>
       <c r="F208" t="n">
         <v>1</v>
@@ -14266,7 +14382,7 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -14292,7 +14408,7 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
@@ -14318,7 +14434,7 @@
         <v>81</v>
       </c>
       <c r="E209" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F209" t="n">
         <v>1</v>
@@ -14332,7 +14448,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
+          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -14358,7 +14474,7 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>10000000</v>
+        <v>3541727</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
@@ -14384,7 +14500,7 @@
         <v>81</v>
       </c>
       <c r="E210" t="n">
-        <v>4293</v>
+        <v>4275</v>
       </c>
       <c r="F210" t="n">
         <v>1</v>
@@ -14398,7 +14514,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
+          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14424,7 +14540,7 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>1406178</v>
+        <v>31280000</v>
       </c>
       <c r="R210" t="n">
         <v>0</v>
@@ -14450,7 +14566,7 @@
         <v>81</v>
       </c>
       <c r="E211" t="n">
-        <v>4293</v>
+        <v>4287</v>
       </c>
       <c r="F211" t="n">
         <v>1</v>
@@ -14464,7 +14580,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>04ª URG BARBACENA</t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14490,10 +14606,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R211" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
@@ -14516,7 +14632,7 @@
         <v>81</v>
       </c>
       <c r="E212" t="n">
-        <v>4293</v>
+        <v>4289</v>
       </c>
       <c r="F212" t="n">
         <v>1</v>
@@ -14530,7 +14646,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>20ª URG FORMIGA</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14556,10 +14672,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R212" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr"/>
@@ -14596,7 +14712,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>28ª URG TEÓFILO OTONI</t>
+          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14622,10 +14738,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="R213" t="n">
-        <v>9575065</v>
+        <v>0</v>
       </c>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr"/>
@@ -14662,7 +14778,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>30ª URG JUIZ DE FORA</t>
+          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14688,10 +14804,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>1406178</v>
       </c>
       <c r="R214" t="n">
-        <v>12375000</v>
+        <v>0</v>
       </c>
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr"/>
@@ -14728,7 +14844,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - SUL</t>
+          <t>04ª URG BARBACENA</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14757,7 +14873,7 @@
         <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>14850000</v>
+        <v>12870000</v>
       </c>
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr"/>
@@ -14794,7 +14910,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - NORTE</t>
+          <t>20ª URG FORMIGA</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14823,7 +14939,7 @@
         <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>14850000</v>
+        <v>12870000</v>
       </c>
       <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr"/>
@@ -14860,7 +14976,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>31ª URG ITUIUTABA</t>
+          <t>28ª URG TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -14889,7 +15005,7 @@
         <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>9900000</v>
+        <v>9575065</v>
       </c>
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr"/>
@@ -14926,7 +15042,7 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG'S</t>
+          <t>30ª URG JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -14952,10 +15068,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>654124898</v>
+        <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>12375000</v>
       </c>
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
@@ -14992,7 +15108,7 @@
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
+          <t>01ª URG BELO HORIZONTE - SUL</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -15018,10 +15134,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>30767851</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>0</v>
+        <v>14850000</v>
       </c>
       <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
@@ -15058,7 +15174,7 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
+          <t>01ª URG BELO HORIZONTE - NORTE</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -15084,10 +15200,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>19976964</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>14850000</v>
       </c>
       <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr"/>
@@ -15124,7 +15240,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
+          <t>31ª URG ITUIUTABA</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -15150,10 +15266,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>12895888</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>0</v>
+        <v>9900000</v>
       </c>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
@@ -15190,7 +15306,7 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG'S</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -15216,7 +15332,7 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>11846334</v>
+        <v>654124898</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
@@ -15256,7 +15372,7 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -15282,7 +15398,7 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>15201174</v>
+        <v>30767861</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
@@ -15322,7 +15438,7 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
+          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -15348,7 +15464,7 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>12921920</v>
+        <v>19976964</v>
       </c>
       <c r="R224" t="n">
         <v>0</v>
@@ -15374,7 +15490,7 @@
         <v>81</v>
       </c>
       <c r="E225" t="n">
-        <v>4385</v>
+        <v>4293</v>
       </c>
       <c r="F225" t="n">
         <v>1</v>
@@ -15388,7 +15504,7 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -15414,7 +15530,7 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>6382601</v>
+        <v>12895888</v>
       </c>
       <c r="R225" t="n">
         <v>0</v>
@@ -15440,7 +15556,7 @@
         <v>81</v>
       </c>
       <c r="E226" t="n">
-        <v>4385</v>
+        <v>4293</v>
       </c>
       <c r="F226" t="n">
         <v>1</v>
@@ -15454,7 +15570,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -15480,7 +15596,7 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>30000000</v>
+        <v>11846334</v>
       </c>
       <c r="R226" t="n">
         <v>0</v>
@@ -15506,7 +15622,7 @@
         <v>81</v>
       </c>
       <c r="E227" t="n">
-        <v>4385</v>
+        <v>4293</v>
       </c>
       <c r="F227" t="n">
         <v>1</v>
@@ -15520,7 +15636,7 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -15546,7 +15662,7 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>4000000</v>
+        <v>15201174</v>
       </c>
       <c r="R227" t="n">
         <v>0</v>
@@ -15569,10 +15685,10 @@
         <v>782</v>
       </c>
       <c r="D228" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E228" t="n">
-        <v>4280</v>
+        <v>4293</v>
       </c>
       <c r="F228" t="n">
         <v>1</v>
@@ -15586,7 +15702,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -15612,7 +15728,7 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>4000000</v>
+        <v>12921920</v>
       </c>
       <c r="R228" t="n">
         <v>0</v>
@@ -15635,10 +15751,10 @@
         <v>782</v>
       </c>
       <c r="D229" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E229" t="n">
-        <v>4280</v>
+        <v>4385</v>
       </c>
       <c r="F229" t="n">
         <v>1</v>
@@ -15652,7 +15768,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
+          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15678,7 +15794,7 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470000</v>
+        <v>6382601</v>
       </c>
       <c r="R229" t="n">
         <v>0</v>
@@ -15701,10 +15817,10 @@
         <v>782</v>
       </c>
       <c r="D230" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E230" t="n">
-        <v>4280</v>
+        <v>4385</v>
       </c>
       <c r="F230" t="n">
         <v>1</v>
@@ -15718,7 +15834,7 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -15744,7 +15860,7 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>4000000</v>
+        <v>30000000</v>
       </c>
       <c r="R230" t="n">
         <v>0</v>
@@ -15767,10 +15883,10 @@
         <v>782</v>
       </c>
       <c r="D231" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E231" t="n">
-        <v>4280</v>
+        <v>4385</v>
       </c>
       <c r="F231" t="n">
         <v>1</v>
@@ -15784,7 +15900,7 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -15810,7 +15926,7 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="R231" t="n">
         <v>0</v>
@@ -15850,7 +15966,7 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
+          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -15876,7 +15992,7 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>420000</v>
+        <v>4000000</v>
       </c>
       <c r="R232" t="n">
         <v>0</v>
@@ -15916,7 +16032,7 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
+          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -15942,7 +16058,7 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>790000</v>
+        <v>470000</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
@@ -15956,19 +16072,19 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="B234" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C234" t="n">
-        <v>363</v>
+        <v>782</v>
       </c>
       <c r="D234" t="n">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="E234" t="n">
-        <v>4006</v>
+        <v>4280</v>
       </c>
       <c r="F234" t="n">
         <v>1</v>
@@ -15982,39 +16098,33 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>METRO QUADRADO</t>
-        </is>
-      </c>
-      <c r="M234" t="n">
-        <v>5000</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="R234" t="n">
         <v>0</v>
@@ -16028,19 +16138,19 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2321</v>
+        <v>2301</v>
       </c>
       <c r="B235" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C235" t="n">
-        <v>302</v>
+        <v>782</v>
       </c>
       <c r="D235" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="E235" t="n">
-        <v>4222</v>
+        <v>4280</v>
       </c>
       <c r="F235" t="n">
         <v>1</v>
@@ -16054,12 +16164,12 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L235" t="inlineStr"/>
@@ -16071,16 +16181,16 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>800291</v>
+        <v>1000000</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
@@ -16094,19 +16204,19 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>2321</v>
+        <v>2301</v>
       </c>
       <c r="B236" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C236" t="n">
-        <v>302</v>
+        <v>782</v>
       </c>
       <c r="D236" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="E236" t="n">
-        <v>4222</v>
+        <v>4280</v>
       </c>
       <c r="F236" t="n">
         <v>1</v>
@@ -16120,12 +16230,12 @@
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
@@ -16137,16 +16247,16 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>174673</v>
+        <v>420000</v>
       </c>
       <c r="R236" t="n">
         <v>0</v>
@@ -16160,19 +16270,19 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>2321</v>
+        <v>2301</v>
       </c>
       <c r="B237" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C237" t="n">
-        <v>302</v>
+        <v>782</v>
       </c>
       <c r="D237" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="E237" t="n">
-        <v>4222</v>
+        <v>4280</v>
       </c>
       <c r="F237" t="n">
         <v>1</v>
@@ -16183,12 +16293,10 @@
       <c r="H237" t="n">
         <v>236</v>
       </c>
-      <c r="I237" t="n">
-        <v>11877</v>
-      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -16205,16 +16313,16 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>1088908</v>
+        <v>790000</v>
       </c>
       <c r="R237" t="n">
         <v>0</v>
@@ -16228,19 +16336,19 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>2361</v>
+        <v>2311</v>
       </c>
       <c r="B238" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C238" t="n">
-        <v>846</v>
+        <v>363</v>
       </c>
       <c r="D238" t="n">
-        <v>705</v>
+        <v>7</v>
       </c>
       <c r="E238" t="n">
-        <v>7004</v>
+        <v>4006</v>
       </c>
       <c r="F238" t="n">
         <v>1</v>
@@ -16254,25 +16362,43 @@
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M238" t="n">
+        <v>5000</v>
+      </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
-      <c r="R238" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Patos de Minas</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>UNAÍ</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr"/>
@@ -16282,19 +16408,19 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2361</v>
+        <v>2321</v>
       </c>
       <c r="B239" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C239" t="n">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="D239" t="n">
-        <v>766</v>
+        <v>87</v>
       </c>
       <c r="E239" t="n">
-        <v>2113</v>
+        <v>4222</v>
       </c>
       <c r="F239" t="n">
         <v>1</v>
@@ -16308,12 +16434,12 @@
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L239" t="inlineStr"/>
@@ -16323,10 +16449,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr"/>
-      <c r="R239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>BELO HORIZONTE</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>800291</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="inlineStr"/>
@@ -16336,19 +16474,19 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2361</v>
+        <v>2321</v>
       </c>
       <c r="B240" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C240" t="n">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="D240" t="n">
-        <v>767</v>
+        <v>87</v>
       </c>
       <c r="E240" t="n">
-        <v>2114</v>
+        <v>4222</v>
       </c>
       <c r="F240" t="n">
         <v>1</v>
@@ -16362,12 +16500,12 @@
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L240" t="inlineStr"/>
@@ -16384,14 +16522,14 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>0</v>
+        <v>174673</v>
       </c>
       <c r="R240" t="n">
-        <v>2754406</v>
+        <v>0</v>
       </c>
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr"/>
@@ -16402,19 +16540,19 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>2371</v>
+        <v>2321</v>
       </c>
       <c r="B241" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C241" t="n">
-        <v>609</v>
+        <v>302</v>
       </c>
       <c r="D241" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E241" t="n">
-        <v>4238</v>
+        <v>4222</v>
       </c>
       <c r="F241" t="n">
         <v>1</v>
@@ -16425,10 +16563,12 @@
       <c r="H241" t="n">
         <v>240</v>
       </c>
-      <c r="I241" t="inlineStr"/>
+      <c r="I241" t="n">
+        <v>11877</v>
+      </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -16445,16 +16585,16 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>8311374</v>
+        <v>1088908</v>
       </c>
       <c r="R241" t="n">
         <v>0</v>
@@ -16468,19 +16608,19 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>2421</v>
+        <v>2361</v>
       </c>
       <c r="B242" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C242" t="n">
-        <v>544</v>
+        <v>846</v>
       </c>
       <c r="D242" t="n">
-        <v>101</v>
+        <v>705</v>
       </c>
       <c r="E242" t="n">
-        <v>1016</v>
+        <v>7004</v>
       </c>
       <c r="F242" t="n">
         <v>1</v>
@@ -16494,7 +16634,7 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -16509,22 +16649,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Montes Claros</t>
-        </is>
-      </c>
-      <c r="P242" t="inlineStr">
-        <is>
-          <t>MONTES CLAROS</t>
-        </is>
-      </c>
-      <c r="Q242" t="n">
-        <v>477508</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="inlineStr"/>
       <c r="U242" t="inlineStr"/>
@@ -16534,19 +16662,19 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>3051</v>
+        <v>2361</v>
       </c>
       <c r="B243" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C243" t="n">
-        <v>364</v>
+        <v>274</v>
       </c>
       <c r="D243" t="n">
-        <v>15</v>
+        <v>766</v>
       </c>
       <c r="E243" t="n">
-        <v>4016</v>
+        <v>2113</v>
       </c>
       <c r="F243" t="n">
         <v>1</v>
@@ -16560,7 +16688,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -16575,22 +16703,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O243" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P243" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q243" t="n">
-        <v>4825656</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0</v>
-      </c>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr"/>
       <c r="U243" t="inlineStr"/>
@@ -16600,19 +16716,19 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>3051</v>
+        <v>2361</v>
       </c>
       <c r="B244" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C244" t="n">
-        <v>364</v>
+        <v>274</v>
       </c>
       <c r="D244" t="n">
-        <v>15</v>
+        <v>767</v>
       </c>
       <c r="E244" t="n">
-        <v>4016</v>
+        <v>2114</v>
       </c>
       <c r="F244" t="n">
         <v>1</v>
@@ -16626,7 +16742,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -16643,19 +16759,19 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>12649000</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>2754406</v>
       </c>
       <c r="S244" t="inlineStr"/>
       <c r="T244" t="inlineStr"/>
@@ -16666,19 +16782,19 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>3051</v>
+        <v>2371</v>
       </c>
       <c r="B245" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C245" t="n">
-        <v>364</v>
+        <v>609</v>
       </c>
       <c r="D245" t="n">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="E245" t="n">
-        <v>4016</v>
+        <v>4238</v>
       </c>
       <c r="F245" t="n">
         <v>1</v>
@@ -16692,7 +16808,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -16709,16 +16825,16 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>3715000</v>
+        <v>8311374</v>
       </c>
       <c r="R245" t="n">
         <v>0</v>
@@ -16732,19 +16848,19 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>3051</v>
+        <v>2421</v>
       </c>
       <c r="B246" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C246" t="n">
-        <v>571</v>
+        <v>544</v>
       </c>
       <c r="D246" t="n">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="E246" t="n">
-        <v>4018</v>
+        <v>1016</v>
       </c>
       <c r="F246" t="n">
         <v>1</v>
@@ -16758,7 +16874,7 @@
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Melhoria da infraestrutura da pesquisa.</t>
+          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -16775,19 +16891,19 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>0</v>
+        <v>477508</v>
       </c>
       <c r="R246" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="S246" t="inlineStr"/>
       <c r="T246" t="inlineStr"/>
@@ -16801,16 +16917,16 @@
         <v>3051</v>
       </c>
       <c r="B247" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C247" t="n">
-        <v>571</v>
+        <v>364</v>
       </c>
       <c r="D247" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E247" t="n">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="F247" t="n">
         <v>1</v>
@@ -16824,7 +16940,7 @@
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -16850,10 +16966,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>4825656</v>
       </c>
       <c r="R247" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="S247" t="inlineStr"/>
       <c r="T247" t="inlineStr"/>
@@ -16864,19 +16980,19 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B248" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C248" t="n">
-        <v>61</v>
+        <v>364</v>
       </c>
       <c r="D248" t="n">
-        <v>706</v>
+        <v>15</v>
       </c>
       <c r="E248" t="n">
-        <v>2091</v>
+        <v>4016</v>
       </c>
       <c r="F248" t="n">
         <v>1</v>
@@ -16887,30 +17003,22 @@
       <c r="H248" t="n">
         <v>247</v>
       </c>
-      <c r="I248" t="n">
-        <v>12054</v>
-      </c>
+      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M248" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -16924,10 +17032,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>0</v>
+        <v>12649000</v>
       </c>
       <c r="R248" t="n">
-        <v>10431496</v>
+        <v>0</v>
       </c>
       <c r="S248" t="inlineStr"/>
       <c r="T248" t="inlineStr"/>
@@ -16938,19 +17046,19 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B249" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C249" t="n">
-        <v>61</v>
+        <v>364</v>
       </c>
       <c r="D249" t="n">
-        <v>706</v>
+        <v>15</v>
       </c>
       <c r="E249" t="n">
-        <v>2091</v>
+        <v>4016</v>
       </c>
       <c r="F249" t="n">
         <v>1</v>
@@ -16961,17 +17069,15 @@
       <c r="H249" t="n">
         <v>248</v>
       </c>
-      <c r="I249" t="n">
-        <v>12702</v>
-      </c>
+      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
-          <t>CINCÃO - Fornecimento e montagem de estante tipo porta-paletes e de planos metálicos para os armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente do TRIBUNAL</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L249" t="inlineStr"/>
@@ -16983,19 +17089,19 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>3715000</v>
       </c>
       <c r="R249" t="n">
-        <v>102247</v>
+        <v>0</v>
       </c>
       <c r="S249" t="inlineStr"/>
       <c r="T249" t="inlineStr"/>
@@ -17006,19 +17112,19 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B250" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C250" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D250" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E250" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F250" t="n">
         <v>1</v>
@@ -17029,30 +17135,22 @@
       <c r="H250" t="n">
         <v>249</v>
       </c>
-      <c r="I250" t="n">
-        <v>12806</v>
-      </c>
+      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M250" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -17069,7 +17167,7 @@
         <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>19560087</v>
+        <v>250000</v>
       </c>
       <c r="S250" t="inlineStr"/>
       <c r="T250" t="inlineStr"/>
@@ -17104,11 +17202,11 @@
         <v>250</v>
       </c>
       <c r="I251" t="n">
-        <v>12638</v>
+        <v>12054</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -17129,22 +17227,10 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P251" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
-      <c r="R251" t="n">
-        <v>19560087</v>
-      </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr"/>
       <c r="U251" t="inlineStr"/>
@@ -17178,11 +17264,11 @@
         <v>251</v>
       </c>
       <c r="I252" t="n">
-        <v>12568</v>
+        <v>12702</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Itabirito/MG.</t>
+          <t>CINCÃO - Fornecimento e montagem de estante tipo porta-paletes e de planos metálicos para os armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente do TRIBUNAL</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -17197,22 +17283,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
-      <c r="R252" t="n">
-        <v>5550000</v>
-      </c>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr"/>
       <c r="T252" t="inlineStr"/>
       <c r="U252" t="inlineStr"/>
@@ -17246,11 +17320,11 @@
         <v>252</v>
       </c>
       <c r="I253" t="n">
-        <v>12627</v>
+        <v>12806</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -17258,29 +17332,23 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M253" t="n">
+        <v>1</v>
+      </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P253" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
-      <c r="R253" t="n">
-        <v>4000000</v>
-      </c>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr"/>
       <c r="U253" t="inlineStr"/>
@@ -17314,11 +17382,11 @@
         <v>253</v>
       </c>
       <c r="I254" t="n">
-        <v>12146</v>
+        <v>12638</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -17326,29 +17394,23 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M254" t="n">
+        <v>1</v>
+      </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P254" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
-      <c r="R254" t="n">
-        <v>13121711</v>
-      </c>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
+      <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr"/>
       <c r="T254" t="inlineStr"/>
       <c r="U254" t="inlineStr"/>
@@ -17382,11 +17444,11 @@
         <v>254</v>
       </c>
       <c r="I255" t="n">
-        <v>12400</v>
+        <v>12568</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Itabirito/MG.</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -17394,35 +17456,17 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M255" t="n">
-        <v>1</v>
-      </c>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P255" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
-      <c r="R255" t="n">
-        <v>18431199</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr"/>
       <c r="T255" t="inlineStr"/>
       <c r="U255" t="inlineStr"/>
@@ -17456,11 +17500,11 @@
         <v>255</v>
       </c>
       <c r="I256" t="n">
-        <v>12288</v>
+        <v>12627</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -17468,35 +17512,17 @@
           <t>EXECUÇÃO</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M256" t="n">
-        <v>1</v>
-      </c>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P256" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
-      <c r="R256" t="n">
-        <v>1950000</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
+      <c r="R256" t="inlineStr"/>
       <c r="S256" t="inlineStr"/>
       <c r="T256" t="inlineStr"/>
       <c r="U256" t="inlineStr"/>
@@ -17506,19 +17532,19 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>5011</v>
+        <v>4031</v>
       </c>
       <c r="B257" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C257" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="D257" t="n">
-        <v>133</v>
+        <v>706</v>
       </c>
       <c r="E257" t="n">
-        <v>3017</v>
+        <v>2091</v>
       </c>
       <c r="F257" t="n">
         <v>1</v>
@@ -17529,15 +17555,17 @@
       <c r="H257" t="n">
         <v>256</v>
       </c>
-      <c r="I257" t="inlineStr"/>
+      <c r="I257" t="n">
+        <v>12146</v>
+      </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L257" t="inlineStr"/>
@@ -17547,22 +17575,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P257" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
-      <c r="R257" t="n">
-        <v>800000</v>
-      </c>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
+      <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr"/>
       <c r="T257" t="inlineStr"/>
       <c r="U257" t="inlineStr"/>
@@ -17572,19 +17588,19 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>5031</v>
+        <v>4031</v>
       </c>
       <c r="B258" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C258" t="n">
-        <v>572</v>
+        <v>61</v>
       </c>
       <c r="D258" t="n">
-        <v>133</v>
+        <v>706</v>
       </c>
       <c r="E258" t="n">
-        <v>3015</v>
+        <v>2091</v>
       </c>
       <c r="F258" t="n">
         <v>1</v>
@@ -17595,40 +17611,36 @@
       <c r="H258" t="n">
         <v>257</v>
       </c>
-      <c r="I258" t="inlineStr"/>
+      <c r="I258" t="n">
+        <v>12400</v>
+      </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M258" t="n">
+        <v>1</v>
+      </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O258" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P258" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
-      <c r="R258" t="n">
-        <v>4782988</v>
-      </c>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr"/>
       <c r="T258" t="inlineStr"/>
       <c r="U258" t="inlineStr"/>
@@ -17638,19 +17650,19 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>5141</v>
+        <v>4031</v>
       </c>
       <c r="B259" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C259" t="n">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="D259" t="n">
-        <v>30</v>
+        <v>706</v>
       </c>
       <c r="E259" t="n">
-        <v>6006</v>
+        <v>2091</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -17661,40 +17673,36 @@
       <c r="H259" t="n">
         <v>258</v>
       </c>
-      <c r="I259" t="inlineStr"/>
+      <c r="I259" t="n">
+        <v>12288</v>
+      </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
-        </is>
-      </c>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
+          <t>EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M259" t="n">
+        <v>1</v>
+      </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O259" t="inlineStr">
-        <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="P259" t="inlineStr">
-        <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
-      <c r="R259" t="n">
-        <v>16317109</v>
-      </c>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr"/>
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr"/>
       <c r="U259" t="inlineStr"/>
@@ -17704,19 +17712,19 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>5391</v>
+        <v>5011</v>
       </c>
       <c r="B260" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C260" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="D260" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E260" t="n">
-        <v>3004</v>
+        <v>3017</v>
       </c>
       <c r="F260" t="n">
         <v>1</v>
@@ -17730,7 +17738,7 @@
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -17747,19 +17755,19 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>92004926</v>
+        <v>800000</v>
       </c>
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr"/>
@@ -17770,19 +17778,19 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>5391</v>
+        <v>5031</v>
       </c>
       <c r="B261" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C261" t="n">
-        <v>752</v>
+        <v>572</v>
       </c>
       <c r="D261" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E261" t="n">
-        <v>3004</v>
+        <v>3015</v>
       </c>
       <c r="F261" t="n">
         <v>1</v>
@@ -17796,7 +17804,7 @@
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17813,19 +17821,19 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q261" t="n">
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>10705994</v>
+        <v>4782988</v>
       </c>
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr"/>
@@ -17836,19 +17844,19 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>5391</v>
+        <v>5141</v>
       </c>
       <c r="B262" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C262" t="n">
-        <v>752</v>
+        <v>126</v>
       </c>
       <c r="D262" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="E262" t="n">
-        <v>3004</v>
+        <v>6006</v>
       </c>
       <c r="F262" t="n">
         <v>1</v>
@@ -17862,7 +17870,7 @@
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -17879,19 +17887,19 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>10464844</v>
+        <v>16317109</v>
       </c>
       <c r="S262" t="inlineStr"/>
       <c r="T262" t="inlineStr"/>
@@ -17945,19 +17953,19 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>2098278</v>
+        <v>92004926</v>
       </c>
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr"/>
@@ -18011,19 +18019,19 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>96721858</v>
+        <v>10705994</v>
       </c>
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr"/>
@@ -18077,19 +18085,19 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>16415074</v>
+        <v>10464844</v>
       </c>
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr"/>
@@ -18143,19 +18151,19 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>1</v>
+        <v>2098278</v>
       </c>
       <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr"/>
@@ -18178,7 +18186,7 @@
         <v>92</v>
       </c>
       <c r="E267" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F267" t="n">
         <v>1</v>
@@ -18192,7 +18200,7 @@
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -18209,19 +18217,19 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>126817302</v>
+        <v>96721858</v>
       </c>
       <c r="S267" t="inlineStr"/>
       <c r="T267" t="inlineStr"/>
@@ -18244,7 +18252,7 @@
         <v>92</v>
       </c>
       <c r="E268" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F268" t="n">
         <v>1</v>
@@ -18258,7 +18266,7 @@
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -18275,19 +18283,19 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>16058991</v>
+        <v>16415074</v>
       </c>
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr"/>
@@ -18310,7 +18318,7 @@
         <v>92</v>
       </c>
       <c r="E269" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F269" t="n">
         <v>1</v>
@@ -18324,7 +18332,7 @@
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -18341,19 +18349,19 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>65795530</v>
+        <v>1</v>
       </c>
       <c r="S269" t="inlineStr"/>
       <c r="T269" t="inlineStr"/>
@@ -18407,19 +18415,19 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>44156794</v>
+        <v>126817302</v>
       </c>
       <c r="S270" t="inlineStr"/>
       <c r="T270" t="inlineStr"/>
@@ -18473,19 +18481,19 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q271" t="n">
         <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>140716908</v>
+        <v>16058991</v>
       </c>
       <c r="S271" t="inlineStr"/>
       <c r="T271" t="inlineStr"/>
@@ -18539,19 +18547,19 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q272" t="n">
         <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>8715687</v>
+        <v>65795530</v>
       </c>
       <c r="S272" t="inlineStr"/>
       <c r="T272" t="inlineStr"/>
@@ -18605,19 +18613,19 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q273" t="n">
         <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>24622611</v>
+        <v>44156794</v>
       </c>
       <c r="S273" t="inlineStr"/>
       <c r="T273" t="inlineStr"/>
@@ -18637,10 +18645,10 @@
         <v>752</v>
       </c>
       <c r="D274" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E274" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="F274" t="n">
         <v>1</v>
@@ -18654,7 +18662,7 @@
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Expansão do Sistema de Geração</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -18683,7 +18691,7 @@
         <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>1</v>
+        <v>140716908</v>
       </c>
       <c r="S274" t="inlineStr"/>
       <c r="T274" t="inlineStr"/>
@@ -18692,6 +18700,204 @@
       <c r="W274" t="inlineStr"/>
       <c r="X274" t="inlineStr"/>
     </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B275" t="n">
+        <v>25</v>
+      </c>
+      <c r="C275" t="n">
+        <v>752</v>
+      </c>
+      <c r="D275" t="n">
+        <v>92</v>
+      </c>
+      <c r="E275" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="n">
+        <v>274</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Ipatinga</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>0</v>
+      </c>
+      <c r="R275" t="n">
+        <v>8715687</v>
+      </c>
+      <c r="S275" t="inlineStr"/>
+      <c r="T275" t="inlineStr"/>
+      <c r="U275" t="inlineStr"/>
+      <c r="V275" t="inlineStr"/>
+      <c r="W275" t="inlineStr"/>
+      <c r="X275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B276" t="n">
+        <v>25</v>
+      </c>
+      <c r="C276" t="n">
+        <v>752</v>
+      </c>
+      <c r="D276" t="n">
+        <v>92</v>
+      </c>
+      <c r="E276" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F276" t="n">
+        <v>1</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="n">
+        <v>275</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Uberaba</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>0</v>
+      </c>
+      <c r="R276" t="n">
+        <v>24622611</v>
+      </c>
+      <c r="S276" t="inlineStr"/>
+      <c r="T276" t="inlineStr"/>
+      <c r="U276" t="inlineStr"/>
+      <c r="V276" t="inlineStr"/>
+      <c r="W276" t="inlineStr"/>
+      <c r="X276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B277" t="n">
+        <v>25</v>
+      </c>
+      <c r="C277" t="n">
+        <v>752</v>
+      </c>
+      <c r="D277" t="n">
+        <v>94</v>
+      </c>
+      <c r="E277" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" t="n">
+        <v>276</v>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Expansão do Sistema de Geração</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>0</v>
+      </c>
+      <c r="R277" t="n">
+        <v>1</v>
+      </c>
+      <c r="S277" t="inlineStr"/>
+      <c r="T277" t="inlineStr"/>
+      <c r="U277" t="inlineStr"/>
+      <c r="V277" t="inlineStr"/>
+      <c r="W277" t="inlineStr"/>
+      <c r="X277" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -990,7 +990,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M118" t="n">
@@ -8597,7 +8597,7 @@
         <v>150000</v>
       </c>
       <c r="R120" t="n">
-        <v>20000000</v>
+        <v>19850000</v>
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M125" t="n">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>METRO QUADRADO</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M247" t="n">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M260" t="n">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M261" t="n">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M262" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M263" t="n">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M264" t="n">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M265" t="n">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M266" t="n">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M267" t="n">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M268" t="n">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M269" t="n">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M270" t="n">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M271" t="n">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M272" t="n">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M273" t="n">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M274" t="n">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M275" t="n">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M276" t="n">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M277" t="n">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M278" t="n">
@@ -19224,7 +19224,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M279" t="n">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M280" t="n">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M281" t="n">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M282" t="n">

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -990,7 +990,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M118" t="n">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M125" t="n">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>METRO QUADRADO</t>
         </is>
       </c>
       <c r="M247" t="n">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M260" t="n">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M261" t="n">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M262" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M263" t="n">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M264" t="n">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M265" t="n">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M266" t="n">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M267" t="n">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M268" t="n">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M269" t="n">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M270" t="n">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M271" t="n">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M272" t="n">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M273" t="n">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M274" t="n">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M275" t="n">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M276" t="n">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M277" t="n">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M278" t="n">
@@ -19224,7 +19224,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M279" t="n">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M280" t="n">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M281" t="n">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>UNIDADE</t>
         </is>
       </c>
       <c r="M282" t="n">

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -8034,7 +8034,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO'S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -15916,7 +15916,7 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG'S</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">

--- a/data/BASE_DETALHAMENTO_OBRAS.xlsx
+++ b/data/BASE_DETALHAMENTO_OBRAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X301"/>
+  <dimension ref="A1:X302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,19 +804,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1251</v>
+        <v>1091</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>302</v>
+        <v>62</v>
       </c>
       <c r="D6" t="n">
-        <v>135</v>
+        <v>714</v>
       </c>
       <c r="E6" t="n">
-        <v>2060</v>
+        <v>1064</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -827,12 +827,10 @@
       <c r="H6" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="n">
-        <v>12876</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Adequação da estrutura física do NAIS/9ª RPM, visando ao atendimento dos requisitos necessários à regularização junto aos órgãos de controle, especialmente à Vigilância Sanitária e à Secretaria de Saúde</t>
+          <t>Sedes Próprias Diversas</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -840,31 +838,25 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>60000</v>
+        <v>19960975</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -902,11 +894,11 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>12882</v>
+        <v>12876</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Projeto elétrico, hidráulico, esgoto, rede, serralheria (prateleiras) e arquitetônico para reforma do CAO/CODONT; Valor estimado: R$ 197.856,73.</t>
+          <t>Adequação da estrutura física do NAIS/9ª RPM, visando ao atendimento dos requisitos necessários à regularização junto aos órgãos de controle, especialmente à Vigilância Sanitária e à Secretaria de Saúde</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -929,16 +921,16 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>197857</v>
+        <v>60000</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -976,11 +968,11 @@
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>12880</v>
+        <v>12882</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Projeto de reestruturação dos consultórios de roseta para linha;</t>
+          <t xml:space="preserve"> Projeto elétrico, hidráulico, esgoto, rede, serralheria (prateleiras) e arquitetônico para reforma do CAO/CODONT; Valor estimado: R$ 197.856,73.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1012,7 +1004,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>1929103</v>
+        <v>197857</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1050,11 +1042,11 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>12881</v>
+        <v>12880</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Execução das obras de reestruturação dos consultórios de roseta para linha;</t>
+          <t xml:space="preserve"> Projeto de reestruturação dos consultórios de roseta para linha;</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1124,11 +1116,11 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>12878</v>
+        <v>12881</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Contratação de elaboração de estudo e projeto para adaptação do NAIS/5GRS, em atendimento às normas de vigilância sanitária para coleta de resíduos sólidos médico-hospitalares e construção de vestiários.</t>
+          <t>Execução das obras de reestruturação dos consultórios de roseta para linha;</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1151,16 +1143,16 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>GOVERNADOR VALADARES</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>41022</v>
+        <v>1929103</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1198,11 +1190,11 @@
         <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>12875</v>
+        <v>12878</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Construlção de local adequado para o armazenamento e descarte de resíduos de serviços de saúde, sendo necessária a adequação da estrutura física para atendimento às exigências dos órgãos de controle e consequente obtenção do alvará sanitário.</t>
+          <t>Contratação de elaboração de estudo e projeto para adaptação do NAIS/5GRS, em atendimento às normas de vigilância sanitária para coleta de resíduos sólidos médico-hospitalares e construção de vestiários.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1225,16 +1217,16 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DIAMANTINA</t>
+          <t>GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>100000</v>
+        <v>41022</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1248,33 +1240,35 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="D12" t="n">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="E12" t="n">
-        <v>4519</v>
+        <v>2060</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>11</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>12875</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORÇO ESTRUTURAL, REFORMA E AMPLIAÇÃO - EE ABRE CAMPO</t>
+          <t>Construlção de local adequado para o armazenamento e descarte de resíduos de serviços de saúde, sendo necessária a adequação da estrutura física para atendimento às exigências dos órgãos de controle e consequente obtenção do alvará sanitário.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1282,7 +1276,11 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
@@ -1293,16 +1291,16 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ABRE CAMPO</t>
+          <t>DIAMANTINA</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380000</v>
+        <v>100000</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1342,7 +1340,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>OBRA DE COMBATE A INCÊNDIO DE TODO O COMPLEXO E ACESSIBILIDADE NO CAMPUS GAMELEIRA - PRÉDIOS A,B,C,D (INCLUNDO MUSEU ESCOLA ANA MARIA CASASANTA PEIXOTO E MUSEU LEOPOLDO CATHOUD) E EE LEON RENAULT</t>
+          <t>OBRA PARA REFORÇO ESTRUTURAL, REFORMA E AMPLIAÇÃO - EE ABRE CAMPO</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1361,16 +1359,16 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ABRE CAMPO</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>653600</v>
+        <v>380000</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1410,7 +1408,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE GETÚLIO VARGAS</t>
+          <t>OBRA DE COMBATE A INCÊNDIO DE TODO O COMPLEXO E ACESSIBILIDADE NO CAMPUS GAMELEIRA - PRÉDIOS A,B,C,D (INCLUNDO MUSEU ESCOLA ANA MARIA CASASANTA PEIXOTO E MUSEU LEOPOLDO CATHOUD) E EE LEON RENAULT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1438,7 +1436,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>332120</v>
+        <v>653600</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1478,7 +1476,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE JOSÉ BONIFÁCIO</t>
+          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE GETÚLIO VARGAS</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1506,7 +1504,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>1033600</v>
+        <v>332120</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1546,7 +1544,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PROJETOS EXECUTIVOS PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
+          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE JOSÉ BONIFÁCIO</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1574,7 +1572,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>59660</v>
+        <v>1033600</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1614,7 +1612,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
+          <t>PROJETOS EXECUTIVOS PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1642,7 +1640,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>83600</v>
+        <v>59660</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1682,7 +1680,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>OBRAS DE REFORMA GERAL EE PROF CAETANO AZEREDO</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO EE OLEGÁRIO MACIEL</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1710,7 +1708,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805600</v>
+        <v>83600</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1750,7 +1748,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>OBRA PARA REGULARIZAÇÃO DO PROCESSO DE SEGURANÇA CONTRA INCÊNDIO E PÂNICO (PSCIP), ADEQUAÇÃO À ACESSIBILIDADE EE PEDRO II</t>
+          <t>OBRAS DE REFORMA GERAL EE PROF CAETANO AZEREDO</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1778,7 +1776,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387600</v>
+        <v>805600</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -1818,7 +1816,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO (SOLUÇÃO DE PROBLEMAS ESTRUTURAIS) EE SANDOVAL AZEVEDO</t>
+          <t>OBRA PARA REGULARIZAÇÃO DO PROCESSO DE SEGURANÇA CONTRA INCÊNDIO E PÂNICO (PSCIP), ADEQUAÇÃO À ACESSIBILIDADE EE PEDRO II</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1846,7 +1844,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>251560</v>
+        <v>387600</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -1886,7 +1884,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA GERAL/RESTAURAÇÃO (MENOS TELHADO DA CASA MODELO, MURO DE ARRIMO) EE SÃO RAFAEL</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO (SOLUÇÃO DE PROBLEMAS ESTRUTURAIS) EE SANDOVAL AZEVEDO</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1914,7 +1912,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>2121920</v>
+        <v>251560</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -1954,7 +1952,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA - ESTRUTURA ESCOLA GUIGNARD UEMG</t>
+          <t>OBRA DE REFORMA GERAL/RESTAURAÇÃO (MENOS TELHADO DA CASA MODELO, MURO DE ARRIMO) EE SÃO RAFAEL</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1982,7 +1980,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>1929640</v>
+        <v>2121920</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2022,12 +2020,12 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>OBRAS DE REFORMA E RESTAURAÇÃO DOS PRÉDIOS INSTITUTO DE EDUCAÇÃO DE MINAS GERAIS - IEMG</t>
+          <t>OBRA DE REFORMA - ESTRUTURA ESCOLA GUIGNARD UEMG</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2050,7 +2048,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>3040000</v>
+        <v>1929640</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2090,12 +2088,12 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA, DO PRÉDIO DO ANTIGO AUDITÓRIO DO CAMPUS DA SEE-  GAMELEIRA, PARA ABRIGAR A NOVA SEDE DA SRE MET B - SEDE DA SRE MET B - AUDITÓRIO GAMELEIRA</t>
+          <t>OBRAS DE REFORMA E RESTAURAÇÃO DOS PRÉDIOS INSTITUTO DE EDUCAÇÃO DE MINAS GERAIS - IEMG</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -2118,7 +2116,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>3025160</v>
+        <v>3040000</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2158,7 +2156,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>OBRA  PARA REFORMA/RESTAURAÇÃO EE SÃO JOAQUIM</t>
+          <t>OBRA PARA REFORMA, DO PRÉDIO DO ANTIGO AUDITÓRIO DO CAMPUS DA SEE-  GAMELEIRA, PARA ABRIGAR A NOVA SEDE DA SRE MET B - SEDE DA SRE MET B - AUDITÓRIO GAMELEIRA</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2182,11 +2180,11 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CONCEIÇÃO DO MATO DENTRO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>2105200</v>
+        <v>3025160</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2226,12 +2224,12 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>OBRA DE ESTRUTURA E OUTRAS, EM PRÉDIO TOMBADO</t>
+          <t>OBRA  PARA REFORMA/RESTAURAÇÃO EE SÃO JOAQUIM</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2250,11 +2248,11 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CORDISBURGO</t>
+          <t>CONCEIÇÃO DO MATO DENTRO</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>260300</v>
+        <v>2105200</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2294,12 +2292,12 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E SOLUÇÃO DE PROBLEMAS ESTRUTURAIS EE ODILON BEHRENS</t>
+          <t>OBRA DE ESTRUTURA E OUTRAS, EM PRÉDIO TOMBADO</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2313,16 +2311,16 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Região Intermediária de Governador Valadares</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>GUANHÃES</t>
+          <t>CORDISBURGO</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>1705060</v>
+        <v>260300</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2362,7 +2360,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OBRA PARA SOLUÇÃO DE DESLIZAMENTO DE TERRA DE PARTE DO TALUDE E A RUPTURA DE PARTE DO MURO DIVISÓRIO INTERNO EE SELIM JOSÉ DE SALES</t>
+          <t>OBRA PARA REFORMA E SOLUÇÃO DE PROBLEMAS ESTRUTURAIS EE ODILON BEHRENS</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2381,16 +2379,16 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Governador Valadares</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>GUANHÃES</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>190000</v>
+        <v>1705060</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2430,7 +2428,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>OBRAS PARA RESTAURAÇÃO DO PRÉDIO EE WENCESLAU BRAZ</t>
+          <t xml:space="preserve"> OBRA PARA SOLUÇÃO DE DESLIZAMENTO DE TERRA DE PARTE DO TALUDE E A RUPTURA DE PARTE DO MURO DIVISÓRIO INTERNO EE SELIM JOSÉ DE SALES</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2449,16 +2447,16 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>ITAJUBÁ</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>2420600</v>
+        <v>190000</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2498,7 +2496,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E CONTENÇÃO E ESTABILIDADE DE TALUDE E DO PRÉDIO EE SÃO JOSÉ</t>
+          <t>OBRAS PARA RESTAURAÇÃO DO PRÉDIO EE WENCESLAU BRAZ</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2517,16 +2515,16 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691600</v>
+        <v>2420600</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2566,7 +2564,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE RAUL SOARES</t>
+          <t>OBRA PARA REFORMA E CONTENÇÃO E ESTABILIDADE DE TALUDE E DO PRÉDIO EE SÃO JOSÉ</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2585,16 +2583,16 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>ARAGUARI</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380000</v>
+        <v>691600</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2634,12 +2632,12 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA GERAL E RESTAURAÇÃO EE AFONSO PENA</t>
+          <t>OBRA PARA RESTAURAÇÃO DO PRÉDIO EE RAUL SOARES</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2653,16 +2651,16 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ARAGUARI</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>1194340</v>
+        <v>380000</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2702,12 +2700,12 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE FRANCISCO SALES</t>
+          <t>OBRA PARA REFORMA GERAL E RESTAURAÇÃO EE AFONSO PENA</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2730,7 +2728,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>407740</v>
+        <v>1194340</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -2770,7 +2768,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO COMPLEMENTARES - UNIDADE I EE GOV MILTON CAMPOS</t>
+          <t>REFORMA GERAL, RESTAURAÇÃO E RECUPERAÇÃO ESTRUTURAL EE FRANCISCO SALES</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2798,7 +2796,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>1102000</v>
+        <v>407740</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -2838,7 +2836,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>OBRA PARA TALUDE E MURO EE PROFA MARIA AMÉLIA GUIMARÃES</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO COMPLEMENTARES - UNIDADE I EE GOV MILTON CAMPOS</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2866,7 +2864,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>190000</v>
+        <v>1102000</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -2906,7 +2904,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO, CONSERVAÇÃO E PRESERVAÇÃO ANTIGA ESCOLA DE APRENDIZES MARINHEIROS E CASA DO COMANDANTE - FUCAM (EE PROFESSORA MARIETA AMORIM VIEIRA)</t>
+          <t>OBRA PARA TALUDE E MURO EE PROFA MARIA AMÉLIA GUIMARÃES</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2925,16 +2923,16 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BURITIZEIRO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>235600</v>
+        <v>190000</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -2974,7 +2972,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>ATENDIMENTOS ESCOLAS ESTADUAIS - CAIXAS ESCOLARES E CONVÊNIOS</t>
+          <t>RESTAURAÇÃO, CONSERVAÇÃO E PRESERVAÇÃO ANTIGA ESCOLA DE APRENDIZES MARINHEIROS E CASA DO COMANDANTE - FUCAM (EE PROFESSORA MARIETA AMORIM VIEIRA)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2991,10 +2989,22 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Montes Claros</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>BURITIZEIRO</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>235600</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -3030,7 +3040,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
+          <t>ATENDIMENTOS ESCOLAS ESTADUAIS - CAIXAS ESCOLARES E CONVÊNIOS</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3047,22 +3057,10 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Varginha</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>GUAPÉ</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>387600</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -3098,7 +3096,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
+          <t>OBRA - PROBLEMAS ESTRUTURAIS, ALÉM DE REFORMA E AMPLIAÇÃO DO PRÉDIO EE DR LAURO CORREA DO AMARAL</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3117,16 +3115,16 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>GUAPÉ</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361760</v>
+        <v>387600</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3166,7 +3164,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
+          <t>CONCLUSÃO DA OBRA DE CONTENÇÃO DE TALUDE E RECUPERAÇÕES NA CONSTRUÇÃO EE ANTÔNIO MARINHO CAMPOS</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3185,16 +3183,16 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>218500</v>
+        <v>361760</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3234,7 +3232,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
+          <t>OBRA DE CONTENÇÃO, REFORMA E REFORÇO ESTRUTURAL DO PRÉDIO EE ANTÔNIO PAPINI</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3253,16 +3251,16 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>1976000</v>
+        <v>218500</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3302,7 +3300,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO E  REPAROS ESTRUTURAIS EE DUQUE DE CAXIAS</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3321,16 +3319,16 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>805600</v>
+        <v>1976000</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3370,7 +3368,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
+          <t>OBRA DE CONSTRUÇÃO DA SEDESEDE DA SRE DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3389,16 +3387,16 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>760000</v>
+        <v>805600</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3438,7 +3436,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
+          <t>OBRAS DE CONTENÇÃO EE AUGUSTO DE LIMA</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3457,16 +3455,16 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>653600</v>
+        <v>760000</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -3506,12 +3504,12 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS  ESTRUTURAIS NO EDIFÍCIO, INCLUINDO INFILTRAÇÃO NAS PAREDES, DETERIORAÇÃO DO GUARDA-CORPO NA FACHADA, ABATIMENTO NO PISO, ASSOALHO DANIFICADO E INCLINAÇÃO DA FACHADA.EE PROFESSOR PINHEIRO CAMPOS</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3525,16 +3523,16 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>1204600</v>
+        <v>653600</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -3574,12 +3572,12 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
+          <t>REFORMA GERAL E RESTAURAÇÃO EE DOM PEDRO II</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3593,16 +3591,16 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PATOS DE MINAS</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>1927740</v>
+        <v>1204600</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -3642,7 +3640,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
+          <t>OBRA PARA RESTAURAÇÃO EE PROFESSOR ANTÔNIO DIAS MACIEL</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3661,16 +3659,16 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>JUIZ DE FORA</t>
+          <t>PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>653600</v>
+        <v>1927740</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -3710,7 +3708,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
+          <t>OBRA RESTAURAÇÃO INSTITUTO DE EDUCAÇÃO DE JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3738,7 +3736,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>19000</v>
+        <v>653600</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -3778,7 +3776,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE HENRIQUE BURNIER</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3846,7 +3844,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
+          <t>OBRA - PROBLEMAS REFERENTES À CONTENÇÃO DE TALUDE E DRENAGEM PLUVIALEE BATISTA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3865,16 +3863,16 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>MATUTINA</t>
+          <t>JUIZ DE FORA</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>1318600</v>
+        <v>19000</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -3914,12 +3912,12 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
+          <t>OBRA REFORMA, RESTAURAÇÃO E AMPLIAÇÃOEE ANA ROCHA (PREDIO EE FREI LEOPOLDO)</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3933,16 +3931,16 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>MATUTINA</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>653600</v>
+        <v>1318600</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -3982,12 +3980,12 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
+          <t>OBRA PARA REFORMA DA EDIFICAÇÃO E EXECUÇÃO DAS OBRAS DE ESTABILIZAÇÃO DE TALUDE, REFORÇO DA CONTENÇÃO E CONSTRUÇÃO DE NOVO MURO DE DIVISA EE JULIETA DE OLIVEIRA MACEDO</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -4010,7 +4008,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>19000</v>
+        <v>653600</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -4050,7 +4048,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
+          <t>CONSTRUÇÃO DE PRÉDIO DA SEDE DA SRE DE MURIAÉ</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4069,12 +4067,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -4118,7 +4116,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
+          <t>OBRA DE REFORMA SEDE DA SRE DE NOVA ERA</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4137,16 +4135,16 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>NOVA ERA</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>760000</v>
+        <v>19000</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -4186,7 +4184,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
+          <t>OBRAS PARA PROBLEMAS ESTRUTURAIS NO AUDITÓRIO (ESTRUTURA PISO E TELHADO) - REFORMA GERAL E RESTAURAÇÃO - PRÉDIO TOMBADOEE FRANCISCO FERNANDES</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4205,16 +4203,16 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PARAOPEBA</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>19000</v>
+        <v>760000</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -4254,7 +4252,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
+          <t xml:space="preserve">OBRA PARA REFORMA GERAL / RESTAURAÇÃO EE CONSELHEIRO AFONSO PENA </t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4273,12 +4271,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PATROCÍNIO</t>
+          <t>PARAOPEBA</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -4322,7 +4320,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
+          <t>OBRA PARA RESTAURAÇÃOEE DOM LUSTOSA</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4390,7 +4388,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
+          <t>OBRA DE RESTAURAÇÃOSEDE DA SRE DE PATROCÍNIO</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4409,16 +4407,16 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PITANGUI</t>
+          <t>PATROCÍNIO</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434720</v>
+        <v>19000</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -4458,7 +4456,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃO DO PRÉDIOEE FRANCISCA BOTELHO</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4477,16 +4475,16 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO</t>
+          <t>PITANGUI</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>221160</v>
+        <v>434720</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -4526,7 +4524,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
+          <t>OBRA  DE REFORMA E RESTAURAÇÃOCESEC TANCREDO NEVES (PRÉDIO OCUPADO ANTERIORMENTE PELA EE FARNESE MACIEL )</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4545,16 +4543,16 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>1748000</v>
+        <v>221160</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -4594,7 +4592,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
+          <t>CONCLUSÃO DA OBRA DE REFORMA E RESTAURAÇÃO EE JOAO DOS SANTOS</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4613,16 +4611,16 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>479560</v>
+        <v>1748000</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -4662,7 +4660,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISSEDE DA SRE DE SETE LAGOAS</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4681,16 +4679,16 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>UBÁ</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>228000</v>
+        <v>479560</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -4730,12 +4728,12 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
+          <t>OBRA PARA REPAROS ESTRUTURAIS (EXECUÇÃO DO REFORÇO DE FUNDAÇÃO E SERVIÇOS CORRELATOS) - 1A ETAPAEE DEPUTADO CARLOS PEIXOTO FILHO</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -4749,16 +4747,16 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>UBÁ</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>2552080</v>
+        <v>228000</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -4798,12 +4796,12 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
+          <t>CONSTRUÇÃO DE ESCOLA - 16 SALAS DE AULA (NO BAIRRO JARDIM CÉLIA)EE 13 DE MAIO</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4817,16 +4815,16 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>1386240</v>
+        <v>2552080</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -4866,7 +4864,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
+          <t>REFORMA / REFORÇO ESTRUTURALEE CORAÇÃO DE JESUS</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4894,7 +4892,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>1900000</v>
+        <v>1386240</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -4934,7 +4932,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
+          <t>OBRA PARA REFORMA/RESTAURAÇÃO EE BRASIL</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4958,11 +4956,11 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>1008140</v>
+        <v>1900000</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -5002,7 +5000,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
+          <t>OBRA DE REFORMA E RESTAURAÇÃOEE DR. JOÃO PINHEIRO</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5021,16 +5019,16 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>SERRO</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>380000</v>
+        <v>1008140</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -5070,7 +5068,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
+          <t>OBRAS PARA MURO DE ARRIMO E DRENAGEM, ALÉM DE REFORMA/RESTAURAÇÃO EE MINISTRO EDMUNDO LINS</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5089,16 +5087,16 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>SERRO</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>228000</v>
+        <v>380000</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -5138,7 +5136,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
+          <t>OBRA PARA REFORMA E RESTAURAÇÃOEE DR. ARTHUR BERNARDES</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5157,16 +5155,16 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539600</v>
+        <v>228000</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -5206,7 +5204,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
+          <t>OBRA PARA SOLUÇÃO DE PROBLEMAS ESTRUTURAISEE HAYDÉE DE SOUZA ABREU</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5225,16 +5223,16 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>UBERLÂNDIA</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>19000</v>
+        <v>539600</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -5274,12 +5272,12 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
+          <t>OBRA - MANUTENÇÃO E REVISÃO COMPLETA DAS COBERTURAS; PINTURA EXTERNA E INTERNA; RESTAURO DE ESQUADRIAS;  REVISÃO DE TODA A REDE ELÉTRICA; RESTAURO DA PINTURA ARTÍSTICA DO RODATETO E PROSPECÇÃO EXPLORATÓRIA NO HALL DE ENTRADA, VISANDO AVALIAR A EXISTÊ</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5293,16 +5291,16 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>VARGINHA</t>
+          <t>UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>2074800</v>
+        <v>19000</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -5316,35 +5314,33 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1301</v>
+        <v>1261</v>
       </c>
       <c r="B72" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C72" t="n">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="D72" t="n">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="E72" t="n">
-        <v>1037</v>
+        <v>4519</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
         <v>71</v>
       </c>
-      <c r="I72" t="n">
-        <v>12404</v>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
+          <t>OBRA PARA RESTAURAÇÃO EE AFONSO PENA</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5353,10 +5349,12 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5366,14 +5364,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>VARGINHA</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>280106</v>
+        <v>2074800</v>
       </c>
       <c r="R72" t="n">
-        <v>519640</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -5408,11 +5406,11 @@
         <v>72</v>
       </c>
       <c r="I73" t="n">
-        <v>12780</v>
+        <v>12404</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
+          <t>DC-018/2023-Execução das serviço de Aumento de capacidade e Recuperação de Rodovia (aumento de capacidade) no trecho Três Pontas - Varginhas (Estaca 80 a 610), com 10,60 km de extensão, na Rodovia MG-167</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5429,19 +5427,19 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>894720</v>
+        <v>280106</v>
       </c>
       <c r="R73" t="n">
-        <v>4087644</v>
+        <v>519640</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -5476,11 +5474,11 @@
         <v>73</v>
       </c>
       <c r="I74" t="n">
-        <v>10397</v>
+        <v>12780</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
+          <t>Execução das obras de Implantação de Passarela na Rodovia MG-010, Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00 m</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5497,19 +5495,19 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>IBERTIOGA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>8264640</v>
+        <v>894720</v>
       </c>
       <c r="R74" t="n">
-        <v>19153735</v>
+        <v>4087644</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -5544,11 +5542,11 @@
         <v>74</v>
       </c>
       <c r="I75" t="n">
-        <v>12850</v>
+        <v>10397</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
+          <t>PRC-22.021/18 -Melhoramento e pavimentação no trecho Ibertioga  Piedade do Rio Grande, na Rodovia MG/338, extensão de 13,25km</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5565,19 +5563,19 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Barbacena</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS</t>
+          <t>IBERTIOGA</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>3155040</v>
+        <v>8264640</v>
       </c>
       <c r="R75" t="n">
-        <v>23943007</v>
+        <v>19153735</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -5612,11 +5610,11 @@
         <v>75</v>
       </c>
       <c r="I76" t="n">
-        <v>12634</v>
+        <v>12850</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
+          <t>Melhoramento e pavimentação do trecho de Jaboticatubas - Lagoa Santa, em rodovia Municipal.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5633,19 +5631,19 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>ITAPAGIPE</t>
+          <t>JABOTICATUBAS</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>4840800</v>
+        <v>3155040</v>
       </c>
       <c r="R76" t="n">
-        <v>26593690</v>
+        <v>23943007</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -5680,11 +5678,11 @@
         <v>76</v>
       </c>
       <c r="I77" t="n">
-        <v>12785</v>
+        <v>12634</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
+          <t>Melhoramento e pavimentação do Trecho Itapagipe - Entrº 364 (Campina Verde) MGC 154 - LOTE 01</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5706,14 +5704,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>ITURAMA</t>
+          <t>ITAPAGIPE</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>613500</v>
+        <v>4840800</v>
       </c>
       <c r="R77" t="n">
-        <v>2870210</v>
+        <v>26593690</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -5748,11 +5746,11 @@
         <v>77</v>
       </c>
       <c r="I78" t="n">
-        <v>12824</v>
+        <v>12785</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
+          <t>Execução da Obra de Engenharia de Melhoramento e pavimentação da Interseção de acesso ao Presídio de Iturama, na via Municipal, com extensão de 2,000 km.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5769,19 +5767,19 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>PARACATU</t>
+          <t>ITURAMA</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>5963400</v>
+        <v>613500</v>
       </c>
       <c r="R78" t="n">
-        <v>23280000</v>
+        <v>2870210</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -5816,11 +5814,11 @@
         <v>78</v>
       </c>
       <c r="I79" t="n">
-        <v>4716</v>
+        <v>12824</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
+          <t>Melhoramento e Pavimentação em Rodovia de Ligação no trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700 km e Segmento 2 (835 a 1250), extensão 8,300 km.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5837,19 +5835,19 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>MONTE CARMELO</t>
+          <t>PARACATU</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>3620820</v>
+        <v>5963400</v>
       </c>
       <c r="R79" t="n">
-        <v>19100000</v>
+        <v>23280000</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
@@ -5883,15 +5881,17 @@
       <c r="H80" t="n">
         <v>79</v>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>4716</v>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
+          <t>Entr. BR/365-Entr. LMG/782 (p/ Iraí de Minas), Monte Carmelo-Chapada de Minas e Pindaibas-Ent.BR/365</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -5903,19 +5903,19 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTE CARMELO</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3620820</v>
       </c>
       <c r="R80" t="n">
-        <v>11755000</v>
+        <v>19100000</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         <v>451</v>
       </c>
       <c r="D81" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E81" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -5949,17 +5949,15 @@
       <c r="H81" t="n">
         <v>80</v>
       </c>
-      <c r="I81" t="n">
-        <v>11140</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
+          <t>Recapeamento de vias / pavimentação de trecho rodoviário / pavimentação e obra de arte especial no trecho viário; para melhoria da infraestrutura viária do Estado de Minas Gerais (8 propostas de novos convênios)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -5971,19 +5969,19 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>1839798</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3269655</v>
+        <v>11755000</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
@@ -6018,11 +6016,11 @@
         <v>81</v>
       </c>
       <c r="I82" t="n">
-        <v>11531</v>
+        <v>11140</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
+          <t xml:space="preserve">CONSTRUÇÃO DE 64 UNIDADES HABITACIONAIS PAC FNHIS </t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6048,10 +6046,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>222899</v>
+        <v>1839798</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3269655</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
@@ -6074,7 +6072,7 @@
         <v>99</v>
       </c>
       <c r="E83" t="n">
-        <v>4262</v>
+        <v>1038</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -6085,10 +6083,12 @@
       <c r="H83" t="n">
         <v>82</v>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>11531</v>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
+          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL DO RIBEIRÃO ARRUDAS - FNHIS/2009 - Continuidade da execução do PTTS (Programa de Trabalho Técnico-Social)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6105,16 +6105,16 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>10932874</v>
+        <v>222899</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -6131,16 +6131,16 @@
         <v>1301</v>
       </c>
       <c r="B84" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C84" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D84" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E84" t="n">
-        <v>4290</v>
+        <v>4262</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -6151,12 +6151,10 @@
       <c r="H84" t="n">
         <v>83</v>
       </c>
-      <c r="I84" t="n">
-        <v>12510</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
+          <t>Aquisição de materiais para obras - mata-burros, vigas metálicas e bueiros metálicos</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6173,19 +6171,19 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>10932874</v>
       </c>
       <c r="R84" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
@@ -6219,15 +6217,17 @@
       <c r="H85" t="n">
         <v>84</v>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>12510</v>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
+          <t xml:space="preserve"> tratamento viário para implantação de sistema BRS em dois corredores de importância metropolitana na Região Metropolitana de Belo Horizonte (RMBH)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6248,10 +6248,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478579</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
@@ -6288,7 +6288,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Brasília)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>2246479</v>
+        <v>478579</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE - Obra Av Civilização/Vilarinho)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>156926</v>
+        <v>2246479</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -6397,16 +6397,16 @@
         <v>1301</v>
       </c>
       <c r="B88" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C88" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D88" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E88" t="n">
-        <v>1036</v>
+        <v>4290</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -6417,17 +6417,15 @@
       <c r="H88" t="n">
         <v>87</v>
       </c>
-      <c r="I88" t="n">
-        <v>12453</v>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
+          <t>Pagamento reajuste previsão INCC - Contrato de repasse 970648 (PAC MOBILIDADE -  Obras Estações  BRT MG10)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -6439,19 +6437,19 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>ALÉM PARAÍBA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>156926</v>
       </c>
       <c r="R88" t="n">
-        <v>539924</v>
+        <v>0</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
@@ -6486,11 +6484,11 @@
         <v>88</v>
       </c>
       <c r="I89" t="n">
-        <v>12454</v>
+        <v>12453</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
+          <t>LOTE 1 EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM ALEM PARAIBA</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6512,14 +6510,14 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>MURIAÉ</t>
+          <t>ALÉM PARAÍBA</t>
         </is>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>15337533</v>
+        <v>539924</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
@@ -6554,11 +6552,11 @@
         <v>89</v>
       </c>
       <c r="I90" t="n">
-        <v>11521</v>
+        <v>12454</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>LOTE  2 -  EXECUCAO DAS OBRAS DE ESTABILIZACAO E CONTENCAO DE ENCOSTAS EM AREAS URBANAS EM MURIAE</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6575,19 +6573,19 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>SABARÁ</t>
+          <t>MURIAÉ</t>
         </is>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1440021</v>
+        <v>15337533</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
@@ -6622,11 +6620,11 @@
         <v>90</v>
       </c>
       <c r="I91" t="n">
-        <v>11519</v>
+        <v>11521</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de contenção de encostas em Sabará - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6643,19 +6641,19 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>JOÃO MONLEVADE</t>
+          <t>SABARÁ</t>
         </is>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>6942767</v>
+        <v>1440021</v>
       </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
@@ -6690,16 +6688,16 @@
         <v>91</v>
       </c>
       <c r="I92" t="n">
-        <v>11512</v>
+        <v>11519</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
+          <t>Obras de contenção de encostas em João Monlevade - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -6716,14 +6714,14 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>JOÃO MONLEVADE</t>
         </is>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>14686005</v>
+        <v>6942767</v>
       </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
@@ -6758,16 +6756,16 @@
         <v>92</v>
       </c>
       <c r="I93" t="n">
-        <v>11514</v>
+        <v>11512</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
+          <t>bras de contenção de encostas em Timóteo - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Respostas a Desastres.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -6779,19 +6777,19 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>52160376</v>
+        <v>14686005</v>
       </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
@@ -6826,11 +6824,11 @@
         <v>93</v>
       </c>
       <c r="I94" t="n">
-        <v>11511</v>
+        <v>11514</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
+          <t>Obras de Contenção de encostas em Ouro Preto - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e resposta a desastres.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6847,19 +6845,19 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>20521500</v>
+        <v>52160376</v>
       </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
@@ -6894,11 +6892,11 @@
         <v>94</v>
       </c>
       <c r="I95" t="n">
-        <v>11520</v>
+        <v>11511</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Manhumirim, Lajinha, Ervália,Sabinópolis e Diogo de Vasconcelos - Intervenção em setores de risco alto e muito alto. No ambito do Programa PAC gestão de riscos e proposta a desastres.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6915,19 +6913,19 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>SANTA LUZIA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>6952445</v>
+        <v>20521500</v>
       </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
@@ -6962,11 +6960,11 @@
         <v>95</v>
       </c>
       <c r="I96" t="n">
-        <v>11513</v>
+        <v>11520</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
+          <t>Obras de contenção de encostas em Santa Luzia - Intervenção em setores de risco alto e muito alto, no âmbito do Programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6983,19 +6981,19 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>SANTA LUZIA</t>
         </is>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>12959175</v>
+        <v>6952445</v>
       </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
@@ -7030,11 +7028,11 @@
         <v>96</v>
       </c>
       <c r="I97" t="n">
-        <v>11977</v>
+        <v>11513</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
+          <t>Obras de Contenção de encostas em Ewbank da Câmara, Matias Barbosa e Visconde do Rio Branco - Intervenção em setores de risco alto e muito alto, no ambito do programa PAC gestão de riscos e proposta a desastre.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7051,19 +7049,19 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>CATAGUASES</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>38244490</v>
+        <v>12959175</v>
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
@@ -7098,11 +7096,11 @@
         <v>97</v>
       </c>
       <c r="I98" t="n">
-        <v>11162</v>
+        <v>11977</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
+          <t>Execução de Obras de Contenção de Encostas em Cataguases/MG - Intervenção em setores de risco alto e muito alto, no âmbito do programa PAC Gestão de Riscos e Resposta a Desastres.</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7119,19 +7117,19 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>CATAGUASES</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>9858067</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>38244490</v>
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
@@ -7154,7 +7152,7 @@
         <v>139</v>
       </c>
       <c r="E99" t="n">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -7166,11 +7164,11 @@
         <v>98</v>
       </c>
       <c r="I99" t="n">
-        <v>12699</v>
+        <v>11162</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
+          <t>OBRAS DE ESTABILIZAÇÃO E CONTENÇÃO DE ENCOSTAS E DESLIZAMENTOS EM ÁREAS URBANAS</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7187,16 +7185,16 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>299895</v>
+        <v>9858067</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -7234,11 +7232,11 @@
         <v>99</v>
       </c>
       <c r="I100" t="n">
-        <v>11536</v>
+        <v>12699</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
+          <t>SERVIÇOS TÉCNICOS ESPECIALIZADOS PARA A CONCLUSÃO DA IMPLEMENTAÇÃO DO PTTS  PROJETO DE TRABALHO TÉCNICO SOCIAL- PROGRAMA DE REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7264,7 +7262,7 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>4565604</v>
+        <v>299895</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -7290,7 +7288,7 @@
         <v>139</v>
       </c>
       <c r="E101" t="n">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -7302,11 +7300,11 @@
         <v>100</v>
       </c>
       <c r="I101" t="n">
-        <v>11855</v>
+        <v>11536</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
+          <t>Construção de 192 unidades habitacionais referente a 2ª etapa da Requalificação urbana e ambiental do Córrego Ferrugem</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7332,10 +7330,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>6286532</v>
+        <v>4565604</v>
       </c>
       <c r="R101" t="n">
-        <v>2728583</v>
+        <v>0</v>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
@@ -7370,11 +7368,11 @@
         <v>101</v>
       </c>
       <c r="I102" t="n">
-        <v>11973</v>
+        <v>11855</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
+          <t>REMANESCENTE DAS OBRAS DE INFRAESTRUTURA PARA A CONCLUSAO DAS BACIAS DO CONTROLE DE CHEIAS DO CORREGO RIACHO DAS PEDRAS.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7400,10 +7398,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>193263</v>
+        <v>6286532</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2728583</v>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -7414,19 +7412,19 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="B103" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C103" t="n">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="D103" t="n">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="E103" t="n">
-        <v>4118</v>
+        <v>1041</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -7437,15 +7435,17 @@
       <c r="H103" t="n">
         <v>102</v>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>11973</v>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RIMC</t>
+          <t>execução do Plano de Trabalho Técnico-Social - PTTS, que é uma exigência do contrato de financiamento PAC RIACHO</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -7457,19 +7457,19 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>193263</v>
       </c>
       <c r="R103" t="n">
-        <v>4547000</v>
+        <v>0</v>
       </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
@@ -7506,7 +7506,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Programa Água Doce - RITO</t>
+          <t>Programa Água Doce - RIMC</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Região Intermediária de Teófilo Otoni</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -7546,25 +7546,25 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1451</v>
+        <v>1371</v>
       </c>
       <c r="B105" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C105" t="n">
-        <v>421</v>
+        <v>511</v>
       </c>
       <c r="D105" t="n">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="E105" t="n">
-        <v>1048</v>
+        <v>4118</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>104</v>
@@ -7572,12 +7572,12 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
+          <t>Programa Água Doce - RITO</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -7589,19 +7589,19 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Teófilo Otoni</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>904245</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>44308050</v>
+        <v>4547000</v>
       </c>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
@@ -7618,13 +7618,13 @@
         <v>6</v>
       </c>
       <c r="C106" t="n">
-        <v>243</v>
+        <v>421</v>
       </c>
       <c r="D106" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E106" t="n">
-        <v>4441</v>
+        <v>1048</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -7638,7 +7638,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
+          <t>Construção de uma unidade prisional de segurança média com aproximadamente 800 (oitocentas) vagas.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7655,19 +7655,19 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>6999284</v>
+        <v>904245</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>44308050</v>
       </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
@@ -7726,11 +7726,11 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651694</v>
+        <v>6999284</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>ALFENAS</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -7853,16 +7853,16 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ALFENAS</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>1472757</v>
+        <v>651694</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -7919,16 +7919,16 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>651694</v>
+        <v>1472757</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -7985,16 +7985,16 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>18572878</v>
+        <v>651694</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -8008,25 +8008,25 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="B112" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C112" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D112" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E112" t="n">
-        <v>4476</v>
+        <v>4441</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
         <v>111</v>
@@ -8034,12 +8034,12 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
+          <t>Construção e implementação de modelos alternativos de prestação da Medida Socioeducativa de Privação de Liberdade no Estado de Minas Gerais.</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -8051,16 +8051,16 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>270000</v>
+        <v>18572878</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
@@ -8083,10 +8083,10 @@
         <v>122</v>
       </c>
       <c r="D113" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E113" t="n">
-        <v>4465</v>
+        <v>4476</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -8100,7 +8100,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
+          <t>REDIMENSIONAMENTO DE REDE ELÉTRICA (NRPMSO`S) - Garantir a segurança elétrica para implementação de novos equipamentos</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>1100000</v>
+        <v>270000</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -8166,7 +8166,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
+          <t>Construção de um abrigo de Resíduos Sólidos e guaritas de segurança externa na CAMG</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>624000</v>
+        <v>1100000</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -8232,7 +8232,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
+          <t xml:space="preserve">Execução do projeto de reutilização da água da purga </t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>210000</v>
+        <v>624000</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -8298,7 +8298,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
+          <t>Projeto de modernização da alimentação elétrica emergencial dos elevadores</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>150000</v>
+        <v>210000</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
@@ -8364,7 +8364,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
+          <t>Programa de monitoramento e responsabilidade técnica das barragens da Cidade Administrativa</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>3918408</v>
+        <v>150000</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
@@ -8413,10 +8413,10 @@
         <v>122</v>
       </c>
       <c r="D118" t="n">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="E118" t="n">
-        <v>2500</v>
+        <v>4465</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -8430,7 +8430,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
+          <t>Impermeabilização das coberturas do prédio Alterosa e reforço estrutural do estacionamento do Alterosas</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8438,17 +8438,11 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M118" t="n">
-        <v>1</v>
-      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -8462,7 +8456,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>282000</v>
+        <v>3918408</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
@@ -8476,19 +8470,19 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="B119" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="D119" t="n">
-        <v>32</v>
+        <v>705</v>
       </c>
       <c r="E119" t="n">
-        <v>1006</v>
+        <v>2500</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -8502,7 +8496,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
+          <t>Projeto AVCB para o antigo prédio do IOF na av. Augusto de Lima</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -8510,28 +8504,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>1</v>
+      </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>282000</v>
       </c>
       <c r="R119" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
@@ -8554,7 +8554,7 @@
         <v>32</v>
       </c>
       <c r="E120" t="n">
-        <v>4063</v>
+        <v>1006</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -8568,7 +8568,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
+          <t xml:space="preserve">1ª Fase da Execução da Obra de Reformas e Adaptações da Antiga Cadeia Pública de Teofilo Otoni onde será instalada a Nova Delegacia Especializada no Atendimento a Mulher da DRPC de Teofilo Otoni. </t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8585,19 +8585,19 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>19850000</v>
+        <v>1000000</v>
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
@@ -8608,19 +8608,19 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1541</v>
+        <v>1511</v>
       </c>
       <c r="B121" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C121" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="D121" t="n">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="E121" t="n">
-        <v>2500</v>
+        <v>4063</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -8634,12 +8634,12 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
+          <t>Construção do Complexo que irá abrigar o Núcleo Integrado de Perícias</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -8656,14 +8656,14 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>2896100</v>
+        <v>150000</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>19850000</v>
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
@@ -8674,19 +8674,19 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2011</v>
+        <v>1541</v>
       </c>
       <c r="B122" t="n">
         <v>10</v>
       </c>
       <c r="C122" t="n">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="D122" t="n">
-        <v>88</v>
+        <v>705</v>
       </c>
       <c r="E122" t="n">
-        <v>4231</v>
+        <v>2500</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -8697,17 +8697,15 @@
       <c r="H122" t="n">
         <v>121</v>
       </c>
-      <c r="I122" t="n">
-        <v>12871</v>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
+          <t>REFORMA DA ESCOLA DE SAÚDE PÚBLICA DO MUNICÍPIO DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -8728,10 +8726,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>2896100</v>
       </c>
       <c r="R122" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
@@ -8766,11 +8764,11 @@
         <v>122</v>
       </c>
       <c r="I123" t="n">
-        <v>9999</v>
+        <v>12871</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
+          <t xml:space="preserve">EXECUCAO DE OBRAS POR CONTRATO DE BENS PATRIMONIAVEIS adequação do HGIP para obtenção do AVCB                       </t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8799,7 +8797,7 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>1600000</v>
+        <v>2000000</v>
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
@@ -8816,13 +8814,13 @@
         <v>10</v>
       </c>
       <c r="C124" t="n">
-        <v>122</v>
+        <v>302</v>
       </c>
       <c r="D124" t="n">
-        <v>705</v>
+        <v>88</v>
       </c>
       <c r="E124" t="n">
-        <v>2500</v>
+        <v>4231</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -8834,11 +8832,11 @@
         <v>123</v>
       </c>
       <c r="I124" t="n">
-        <v>12690</v>
+        <v>9999</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
+          <t xml:space="preserve">Reforma da Endoscopia - HGIP </t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8867,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2200000</v>
+        <v>1600000</v>
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
@@ -8878,19 +8876,19 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2101</v>
+        <v>2011</v>
       </c>
       <c r="B125" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C125" t="n">
-        <v>541</v>
+        <v>122</v>
       </c>
       <c r="D125" t="n">
-        <v>31</v>
+        <v>705</v>
       </c>
       <c r="E125" t="n">
-        <v>4058</v>
+        <v>2500</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -8901,10 +8899,12 @@
       <c r="H125" t="n">
         <v>124</v>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>12690</v>
+      </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Construção do Cetras de Governador Valadares</t>
+          <t>Apoio à GELENG, no atendimento às demandas de serviços de reforma e manutenção nas unidades.</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8912,34 +8912,28 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M125" t="n">
-        <v>1</v>
-      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2200000</v>
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
@@ -8962,7 +8956,7 @@
         <v>31</v>
       </c>
       <c r="E126" t="n">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -8976,7 +8970,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>APA Parque Cataguás</t>
+          <t>Construção do Cetras de Governador Valadares</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -9008,7 +9002,7 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>1000000</v>
+        <v>350000</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
@@ -9022,19 +9016,19 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2151</v>
+        <v>2101</v>
       </c>
       <c r="B127" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C127" t="n">
-        <v>572</v>
+        <v>541</v>
       </c>
       <c r="D127" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="E127" t="n">
-        <v>1023</v>
+        <v>4059</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
@@ -9048,7 +9042,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
+          <t>APA Parque Cataguás</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -9056,25 +9050,31 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>IBIRITÉ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -9094,13 +9094,13 @@
         <v>12</v>
       </c>
       <c r="C128" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="D128" t="n">
-        <v>705</v>
+        <v>75</v>
       </c>
       <c r="E128" t="n">
-        <v>2500</v>
+        <v>1023</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
@@ -9114,7 +9114,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, LEVANTAMENTOS TOPOGRÁFICOS, SONDAGENS, ESTUDOS AMBIENTAIS, PROJETOS DE ARQUITETURA E ENGENHARIA, ORÇAMENTOS, MEMORIAIS DESCRITIVOS E AFINS</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
@@ -9154,19 +9154,19 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2161</v>
+        <v>2151</v>
       </c>
       <c r="B129" t="n">
         <v>12</v>
       </c>
       <c r="C129" t="n">
-        <v>242</v>
+        <v>122</v>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>705</v>
       </c>
       <c r="E129" t="n">
-        <v>1030</v>
+        <v>2500</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
@@ -9180,12 +9180,12 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Projeto para melhoria de acessibilidade nas unidades da FUCAM</t>
+          <t>CONTRATAÇÃO DO CONSÓRCIO PGM / SINAURB CIDERSU (PGM CONSTRUÇÕES E EMPREENDIMENTOS LTDA E SINAURB SERVIÇOS E EMPREENDIMENTOS LTDA) PRESTAÇÃO DE SERVIÇOS COMUNS E CONTÍNUOS DE ENGENHARIA, SOB DEMANDA, DESTINADOS À MANUTENÇÃO PREDIAL, CONSERVAÇÃO E EXEC</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -9197,16 +9197,16 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>IBIRITÉ</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>14000</v>
+        <v>1500000</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -9263,16 +9263,16 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -9329,12 +9329,12 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>ESMERALDAS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE PATOS DE MINAS</t>
         </is>
       </c>
       <c r="Q131" t="n">
@@ -9352,19 +9352,19 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2261</v>
+        <v>2161</v>
       </c>
       <c r="B132" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C132" t="n">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="D132" t="n">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>4460</v>
+        <v>1030</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -9375,17 +9375,15 @@
       <c r="H132" t="n">
         <v>131</v>
       </c>
-      <c r="I132" t="n">
-        <v>12502</v>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Execução de Obras da nova sede da Divisão de Controle de Qualidade.</t>
+          <t>Projeto para melhoria de acessibilidade nas unidades da FUCAM</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>PARALISADO</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -9402,11 +9400,11 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>ESMERALDAS</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>500000</v>
+        <v>3000</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -9426,13 +9424,13 @@
         <v>10</v>
       </c>
       <c r="C133" t="n">
-        <v>122</v>
+        <v>303</v>
       </c>
       <c r="D133" t="n">
-        <v>705</v>
+        <v>154</v>
       </c>
       <c r="E133" t="n">
-        <v>2500</v>
+        <v>4460</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
@@ -9444,11 +9442,11 @@
         <v>132</v>
       </c>
       <c r="I133" t="n">
-        <v>12500</v>
+        <v>12502</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Novo Prédio Administrativo da FUNED em Steel Frame (Unidade IV)</t>
+          <t>Execução de Obras da nova sede da Divisão de Controle de Qualidade.</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9474,7 +9472,7 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>10535000</v>
+        <v>500000</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -9511,10 +9509,12 @@
       <c r="H134" t="n">
         <v>133</v>
       </c>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="n">
+        <v>12500</v>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Obras de adequação estrutural do refeitório para atendimento às exigências da Vigilância Sanitária Municipal.</t>
+          <t>Novo Prédio Administrativo da FUNED em Steel Frame (Unidade IV)</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>500000</v>
+        <v>10535000</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -9554,19 +9554,19 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2301</v>
+        <v>2261</v>
       </c>
       <c r="B135" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C135" t="n">
-        <v>782</v>
+        <v>122</v>
       </c>
       <c r="D135" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="E135" t="n">
-        <v>4268</v>
+        <v>2500</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
@@ -9580,7 +9580,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
+          <t>Obras de adequação estrutural do refeitório para atendimento às exigências da Vigilância Sanitária Municipal.</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9597,19 +9597,19 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="R135" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
@@ -9646,7 +9646,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
+          <t>REABILITAÇÃO DA MG-010 (CONCEIÇÃO DO MATO DENTRO A SERRO)</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9712,7 +9712,7 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
+          <t>REABILITAÇÃO DA MG-129 (OURO PRETO A OURO BRANCO)</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9741,7 +9741,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
@@ -9778,7 +9778,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
+          <t>RESTAURAÇÃO RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO) E RECOMPOSIÇÃO DE TALUDE ERODIDO</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>9792000</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
@@ -9844,7 +9844,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
+          <t>ARCOS - CORUMBÁ - RODOVIA: MG-170 (ENTR BR-354 - AGRIMIG)</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>1000000</v>
+        <v>9792000</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
+          <t>MG-129 - OURO PRETO A OURO BRANCO</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>143000</v>
+        <v>1000000</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
@@ -9976,7 +9976,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
+          <t>RECUPERAÇÃO DE EROSÃO EM TALUDE DE CORTE NA RODOVIA MGC-354, KM 167,8, TRECHO: RIBEIRÃO DA MATA - AV MARABÁ (PATOS DE MINAS)</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -10002,7 +10002,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>5876140</v>
+        <v>143000</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
@@ -10042,7 +10042,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 150,9, TRECHO: TRAVESSIA URBANA DE PRESIDENTE OLEGÁRIO</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>1132500</v>
+        <v>5876140</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
+          <t>RESTAURAÇÃO DA INTERSEÇÃO NA RODOVIA MGC-354, KM 176,2, TRECHO: AV MARABÁ (PATOS DE MINAS) - ENTR BR 365</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>1000000</v>
+        <v>1132500</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
@@ -10174,7 +10174,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
+          <t>RESTAURAÇÃO E 3ª FAIXA, TRECHO ENTR. BR-354 (CAXAMBÚ) - ENTR. BR-381 (PALMELA DISTRITO DE CAMPANHA), NA MGC-267</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -10200,7 +10200,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>34710000</v>
+        <v>1000000</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
@@ -10240,7 +10240,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE (3ª FAIXA) DO TRECHO SERRA DO SALITRE - SALITRE DE MINAS, NA MG-230</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -10266,7 +10266,7 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>59000000</v>
+        <v>34710000</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
@@ -10306,7 +10306,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO MG-344 (ENTR. P/ CÁSSIA) - DIVISA MG/SP, NA MG-444, EXT. 23,9 KM</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -10332,7 +10332,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>1000000</v>
+        <v>59000000</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
@@ -10372,7 +10372,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO PARÁ DE MINAS - PAPAGAIOS (3ª FAIXA) - LOTE 1</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -10438,7 +10438,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
+          <t>RESTAURAÇÃO E AUMENTO DE CAPACIDADE DO TRECHO: UNAÍ A GARAPUAVA</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -10464,7 +10464,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
@@ -10504,7 +10504,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TIMÓTEO - ENTR. LMG-760 (CAVA GRANDE), NA MG-425</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -10570,7 +10570,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. LMG764 (P/ MATUTINA) - SÃO GOTARDO, NA MG- 235 - 3ª FAIXA</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>30980000</v>
+        <v>1000000</v>
       </c>
       <c r="R150" t="n">
         <v>0</v>
@@ -10636,7 +10636,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-120 (B) (DONA EUZÉBIA) - ENTR. MGC-265, NA MG-285</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>25655000</v>
+        <v>30980000</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
@@ -10702,7 +10702,7 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
+          <t>RESTAURAÇÃO TRECHO ENTR. MGC-265/MG-452 (P/ PAIVA) - ENTR. BR-040, NA MG-448</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>66560000</v>
+        <v>25655000</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
@@ -10768,7 +10768,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
+          <t>RESTAURAÇÃO TRECHO PIRAÚBA (ENTR. MG-285) - PAIVA (ENTR. MG-488/MG-455), NA MG-265 E 3ª FAIXA</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10794,7 +10794,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>1000000</v>
+        <v>66560000</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
@@ -10834,7 +10834,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
+          <t>RESTAURAÇÃO TRECHO SÃO GOTARDO - ENTR. BR-354 (P/ PATOS DE MINAS), NA MG-235</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10860,7 +10860,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>25464500</v>
+        <v>1000000</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
@@ -10886,7 +10886,7 @@
         <v>81</v>
       </c>
       <c r="E155" t="n">
-        <v>4272</v>
+        <v>4268</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
@@ -10900,7 +10900,7 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>RESTAURAÇÃO TRÊS PONTAS - VARGINHA, NA MG-167</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10926,7 +10926,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>100000</v>
+        <v>25464500</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
+          <t>BDCC 3X3 CÓRREGO CAVALO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10992,7 +10992,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>24000000</v>
+        <v>100000</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
@@ -11032,7 +11032,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
+          <t>COMPLEMENTAÇÃO DA CONSTRUÇÃO DA PONTE SOBRE O RIO SÃO FRANCISCO, PINTÓPOLIS</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>252000</v>
+        <v>24000000</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
@@ -11098,7 +11098,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE CÓRREGO SÃO BARTOLOMEU E ENCABEÇAMENTO CÓRREGO BARBADINHO, TRECHO CANABRAVA (JOÃO PINHEIRO) - ENTR. MG-181, NA LMG-698</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>319200</v>
+        <v>252000</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
@@ -11164,7 +11164,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO AMENDOIM, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>495600</v>
+        <v>319200</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE CÓRREGO BOI PRETO, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>679000</v>
+        <v>495600</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
@@ -11296,7 +11296,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O CÓRREGO DAS LAJES, TRECHO ENTR. MGC-479 (SERRA DAS ARARAS) - ENTR. MG-402, NA LMG-622</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440000</v>
+        <v>679000</v>
       </c>
       <c r="R161" t="n">
         <v>0</v>
@@ -11362,7 +11362,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SANTO INÁCIO, TRECHO ENTR. MG-188 (COROMANDEL) - DISTRITO DE VEREDA, NA LMG-747</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>14920000</v>
+        <v>440000</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
@@ -11428,7 +11428,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SÃO JOÃO, TRECHO IGARATINGA - ENTR. MG-252, NA MG-430 (SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -11454,7 +11454,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>8798400</v>
+        <v>14920000</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
+          <t>ENCABEÇAMENTO E PONTE SOBRE O RIO SERRA BRANCA, TRECHO PAI PEDRO - CATUTI, NA MGC-122</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -11520,7 +11520,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>369600</v>
+        <v>8798400</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
@@ -11560,7 +11560,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
+          <t>ENCABEÇAMENTOS E PONTES SOBRE CÓRREGO VEREDINHA E RIBEIRÃO MARQUES, NO TRECHO RIACHINHO - GUARAPUAVA (UNAÍ), NA LMG-638</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11586,7 +11586,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>1000000</v>
+        <v>369600</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
@@ -11626,7 +11626,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
+          <t>LMG-722 (ROCHINHA A LAGAMAR, PONTE SOBRE O RIO PARANAÍBA)</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11652,7 +11652,7 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>1203643</v>
+        <v>1000000</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
@@ -11692,7 +11692,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
+          <t>MGC-267 (CORDISLÂNDIA A CARVALHÓPOLIS, PONTE SOBRE O RIO SAPUCAÍ -  LOTE 01)</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11718,7 +11718,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>730000</v>
+        <v>1203643</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
@@ -11758,7 +11758,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
+          <t>OLHOS D´AGUA DO OESTE A SANTA LUZIA DA SERRA - CÓRREGO SÃO BARTOLOMEU</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>66619</v>
+        <v>730000</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
+          <t>PASSARELA MG-010 (CIDADE ADMINISTRATIVA)</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>901000</v>
+        <v>66619</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
@@ -11890,7 +11890,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
+          <t>PONTE CÓRREGO PERUAÇU, TRECHO CÔNEGO MARINHO - MIRAVÂNIA (RESERVA XACRIABÁ)</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11916,7 +11916,7 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>100000</v>
+        <v>901000</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
@@ -11956,7 +11956,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE CÓRREGO RIBEIRÃO, TRECHO ENTR. BR-040 - PORTO DIAMANTE</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>170000</v>
+        <v>100000</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
@@ -12022,7 +12022,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
+          <t>PONTE SOBRE O EXTRAVASOR DA CEMIG, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -12048,7 +12048,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>2940000</v>
+        <v>170000</v>
       </c>
       <c r="R172" t="n">
         <v>0</v>
@@ -12088,7 +12088,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
+          <t>PONTE SOBRE O RIBEIRÃO MATA BOI NA RODOVIA MG-414, TRECHO ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>810000</v>
+        <v>2940000</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
@@ -12154,7 +12154,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
+          <t>PONTE SOBRE O RIBEIRÃO PANDEIROS, TRECHO JANUÁRIA - RIO PARDO - PANDEIROS, NA MGC-479</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>542000</v>
+        <v>810000</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
@@ -12220,7 +12220,7 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
+          <t>PONTE SOBRE O RIO ARAGUARI (TROCA DOS APARELHOS DE DO 1º E 5º VÃOS), TRECHO ENTR. MG-190 - ZELÂNDIA (USINA SANTA JULIANA), DIMENSÕES 130,00X12,20M, RODOVIA AMG-0730</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -12246,7 +12246,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>2163814</v>
+        <v>542000</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
@@ -12286,7 +12286,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
+          <t>PONTE SOBRE O RIO CORRENTE -  MG-460, NO TRECHO DE MUNHOZ - TOLEDO ( E SEMI-INTEGRADA)</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -12312,7 +12312,7 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>25000000</v>
+        <v>2163814</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
@@ -12352,7 +12352,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
+          <t>PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC-135 (MANGA) ¿ PORTO DE MATIAS CARDOSO, NA RODOVIA MG-401</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>500000</v>
+        <v>25000000</v>
       </c>
       <c r="R177" t="n">
         <v>0</v>
@@ -12418,7 +12418,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
+          <t>PONTES SOBRE OS RIOS SUAÇUI PEQUENO I E II, TRECHO PEÇANHA - COROACI, NA MG-314</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -12444,7 +12444,7 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>1382535</v>
+        <v>500000</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
@@ -12484,7 +12484,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>RECUPERAÇÃO DA PONTE S/ O RIO JEQUITINHONHA- DIAMANTINA - COUTO MAGALHÃES.</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -12510,7 +12510,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>1000000</v>
+        <v>1382535</v>
       </c>
       <c r="R179" t="n">
         <v>0</v>
@@ -12550,7 +12550,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -12576,7 +12576,7 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="R180" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
+          <t>RECUPERAÇÃO ESTRUTURAL DA PONTE SOBRE O RIO PARACATU, TRECHO JOÃO PINHEIRO (ENTR. MG-408) - BRASÍLÂNDIA DE MINAS, NA MG-181</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>168000</v>
+        <v>900000</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
@@ -12682,7 +12682,7 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO DAS ARARAS I, TRECHO GUANHÃES - SÃO PEDRO DO SUAÇUÍ, NA CMG-120</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>249000</v>
+        <v>168000</v>
       </c>
       <c r="R182" t="n">
         <v>0</v>
@@ -12748,7 +12748,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
+          <t>REFORÇO DA FUNDAÇÃO DA PONTE SOBRE O RIBEIRÃO MACAÚBAS, TRECHO SANTA LUZIA - JABOTICATUBAS, MG-020</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12774,7 +12774,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>705000</v>
+        <v>249000</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
@@ -12814,7 +12814,7 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
+          <t>REFORÇO DA FUNDAÇÃO DO VIADUTO II NA PISTA DIREITA DA INTERSEÇÃO 3 (ACESSO AO INHOTIM, ESTACA 138)</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12840,7 +12840,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>58800</v>
+        <v>705000</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
+          <t>REFORÇO DE FUNDAÇÃO CÓRREGO DOIDOS, TRECHO SÃO FRANCISCO DE PAULA - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>725000</v>
+        <v>58800</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
@@ -12932,7 +12932,7 @@
         <v>81</v>
       </c>
       <c r="E186" t="n">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="F186" t="n">
         <v>1</v>
@@ -12946,7 +12946,7 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
+          <t>REFORÇO NA FUNDAÇÃO DA PONTE SOBRE O RIO VERMELHO, TRECHO SANTA BÁRBARA - CATAS ALTAS, NA MG-129</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12972,10 +12972,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>725000</v>
       </c>
       <c r="R186" t="n">
-        <v>82286728</v>
+        <v>0</v>
       </c>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
@@ -13012,7 +13012,7 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
+          <t>PAVIMENTAÇÃO MG-326 (PONTE NOVA A BARRA LONGA)</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -13041,7 +13041,7 @@
         <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>22137718</v>
+        <v>82286728</v>
       </c>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
@@ -13078,7 +13078,7 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
+          <t>PAVIMENTAÇÃO DA MG-314 (ENTR. MG-416 (PEÇANHA) A LMG-744 (COROACI) ENTR. VIRGOLÂNDIA)</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -13107,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>21757581</v>
+        <v>22137718</v>
       </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
@@ -13144,7 +13144,7 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
+          <t>PAVIMENTAÇÃO DA RODOVIA MUNICIPAL (SANTA RITA DO ITUETO A ENTR. BR-259 (RESPLENDOR))</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -13173,7 +13173,7 @@
         <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>8036364</v>
+        <v>21757581</v>
       </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
@@ -13210,7 +13210,7 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
+          <t>RODOVIA MG-010, TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 21,80 KM</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -13239,7 +13239,7 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>14063636</v>
+        <v>8036364</v>
       </c>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
@@ -13276,7 +13276,7 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
+          <t>TRECHO ENTRº LMG-690 (PARACATU) - ENTRº ENTRE RIBEIROS (DISTRITO) - ENTRº MG-181 (ESTACA 1250 A 2000)</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -13305,7 +13305,7 @@
         <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>8100000</v>
+        <v>14063636</v>
       </c>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
@@ -13342,7 +13342,7 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
+          <t>RODOVIA MG-10 - TRECHO CONCEIÇÃO DO MATO DENTRO - SERRO (DISTRITO DE MATO GROSSO), COM EXTENSÃO DE 22,50 KM</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -13371,7 +13371,7 @@
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>4804860</v>
+        <v>8100000</v>
       </c>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
@@ -13408,7 +13408,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DO CONTORNO DE ANDRADAS</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -13437,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>6000001</v>
+        <v>4804860</v>
       </c>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
@@ -13474,7 +13474,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
+          <t>EMPREENDIMENTO EM DEFINIÇÃO JUNTO AO BANCO DO BRASIL - CONTRATO DE FINANCIAMENTO Nº 20/00020-0 (PDMG)</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>11326937</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>6000001</v>
       </c>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
@@ -13540,7 +13540,7 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - (LOTE 1), SEGMENTO 1 (0 A 835), 16,70 KM E SEGMENTO 2 (835 A 1250), 8,30 KM</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>19000000</v>
+        <v>11326937</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
@@ -13606,7 +13606,7 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
+          <t>COMPLEMENTAÇÃO LMG-680, TRECHO PARACATU (ENTR. LMG-690) - ENTR. ENTRE RIBEIROS - ENTR. MG-181 - ESTACA 2550 A 3281</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>74941120</v>
+        <v>19000000</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
@@ -13672,7 +13672,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
+          <t>COMPLEMENTO S JANUÁRIA - PANDEIROS, NA RODOVIA MGC-479</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13698,7 +13698,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>38460000</v>
+        <v>74941120</v>
       </c>
       <c r="R197" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
+          <t>CONTORNO DE ANDRADAS (COMPLEMENTAÇÃO) - LOTE 01</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13764,7 +13764,7 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>1000000</v>
+        <v>38460000</v>
       </c>
       <c r="R198" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
+          <t>ENTR. MG-181 (BRASILÂNDIA DE MINAS) - ENTR. BR-365 (BURITIZEIRO), NA MG-408 - LOTE 01</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
@@ -13870,7 +13870,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
+          <t>IBERTIOGA - PIEDADE DO RIO GRANDE, NA RODOVIA MG-338</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13896,7 +13896,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
@@ -13936,7 +13936,7 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
+          <t>INTERSEÇÃO DE ACESSO A COUTO DE MAGALHÃES DE MINAS, NA MGC-367</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13962,7 +13962,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>6121131</v>
+        <v>1000000</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
@@ -14002,7 +14002,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
+          <t>ITAPAGIPE - ENTR. BR-364 (CAMPINA VERDE), RODOVIA MGC-154</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>1000000</v>
+        <v>6121131</v>
       </c>
       <c r="R202" t="n">
         <v>0</v>
@@ -14068,7 +14068,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
+          <t>MG-631 - SÃO JOÃO DA PONTE A CAPITÃO ENÉAS</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -14134,7 +14134,7 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DA RODOVIA LMG-706, SEGMENTO 01: ENTR. BR-040 - VARIANTE (PONTE RIO ESCURO); SEGMENTO 02: VAZAMOR - VAZANTE; SEGMENTO 03: CONTORNO DE VAZANTE - ENTR. BR-354</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -14200,7 +14200,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
+          <t>ACESSO AO PRESÍDIO DE ITURAMA</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -14266,7 +14266,7 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
+          <t>MONTE CARMELO (ENTR. MG-190) - ENTR. LMG-742 (CHAPADA DE MINAS P/ GRUPIARA), NA LMG-746 - LOTE 01 9,50 KM</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -14332,7 +14332,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
+          <t>MONTE CARMELO A CHAPADA DE MINAS - LOTE 2</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -14398,7 +14398,7 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
+          <t>NATALÂNDIA - ENTR. BR-251, NA LMG-622</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>431808</v>
+        <v>1000000</v>
       </c>
       <c r="R208" t="n">
         <v>0</v>
@@ -14464,7 +14464,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
+          <t>PEÇANHA (ENTR. MG-416) - LMG-744 (COROACI), NA MG-314</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>1000000</v>
+        <v>431808</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
@@ -14530,7 +14530,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
+          <t>PEDRA AZUL (ENTR. MG-105) - DISTRITO DE PEDRA GRANDE - ALMENARA, MG-251/MG-406, LOTE 01 35 KM</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14596,7 +14596,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
+          <t>PEDRA BONITA - ENTR. BR-116 E INTERSEÇÃO ENTR. BR-116 (COMPLEMENTAÇÃO), RODOVIA LMG-840</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14662,7 +14662,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
+          <t>PRESIDENTE OLEGÁRIO - GALENA, NA LMG-726</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>14356788</v>
+        <v>1000000</v>
       </c>
       <c r="R212" t="n">
         <v>0</v>
@@ -14728,7 +14728,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
+          <t>SANTA RITA DO ITUETO - ENTR. BR-259 (RESPLENDOR) (COMPLEMENTAÇÃO), MUNICIPAL AMG-2320</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14754,7 +14754,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>100000</v>
+        <v>14356788</v>
       </c>
       <c r="R213" t="n">
         <v>0</v>
@@ -14794,7 +14794,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
+          <t>SÃO DOMINGOS DO PRATA - DOM SILVÉRIO, NA MGC-120</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="R214" t="n">
         <v>0</v>
@@ -14860,7 +14860,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
+          <t>UNAÍ (ENTR. BR-251) - PARACATU (ENTR. BR-040) (ESTRADA DO MUNDO NOVO), NA LMG-658 - LOTE 01</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>35359852</v>
+        <v>1000000</v>
       </c>
       <c r="R215" t="n">
         <v>0</v>
@@ -14926,7 +14926,7 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
+          <t>ARAÇAÍ - SETE LAGOAS, RODOVIA MUNICIPAL</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14952,7 +14952,7 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>29030000</v>
+        <v>35359852</v>
       </c>
       <c r="R216" t="n">
         <v>0</v>
@@ -14992,7 +14992,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
+          <t>ARAGUARI (DISTRITO DE AMANHECE) - DIVISA MG/GO, NA MG-414</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -15018,7 +15018,7 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>1000000</v>
+        <v>29030000</v>
       </c>
       <c r="R217" t="n">
         <v>0</v>
@@ -15058,7 +15058,7 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
+          <t>CAMPO VERDE (DISTRITO E NOVORIZONTE) - FRUTA DE LEITE, NA LMG-626 (LOTE 01 TSD)</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>3541727</v>
+        <v>1000000</v>
       </c>
       <c r="R218" t="n">
         <v>0</v>
@@ -15124,7 +15124,7 @@
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
+          <t>JABOTICATUBAS - LAGOA SANTA, RODOVIA MUNICIPAL - LOTE 01</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -15150,7 +15150,7 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>31280000</v>
+        <v>3541727</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
@@ -15176,7 +15176,7 @@
         <v>81</v>
       </c>
       <c r="E220" t="n">
-        <v>4287</v>
+        <v>4275</v>
       </c>
       <c r="F220" t="n">
         <v>1</v>
@@ -15190,7 +15190,7 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
+          <t xml:space="preserve">LMG-629 (RIO PARDO DE MINAS A ENTRº LMG-635) - LOTE 2 </t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -15216,7 +15216,7 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>1000</v>
+        <v>31280000</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
@@ -15242,7 +15242,7 @@
         <v>81</v>
       </c>
       <c r="E221" t="n">
-        <v>4289</v>
+        <v>4287</v>
       </c>
       <c r="F221" t="n">
         <v>1</v>
@@ -15256,7 +15256,7 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
+          <t>Empreendimentos do Acordo Judicial do Rio Doce</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -15308,7 +15308,7 @@
         <v>81</v>
       </c>
       <c r="E222" t="n">
-        <v>4293</v>
+        <v>4289</v>
       </c>
       <c r="F222" t="n">
         <v>1</v>
@@ -15322,7 +15322,7 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
+          <t>Empreendimentos do Acordo Judicial de Brumadinho</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -15348,7 +15348,7 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>10000000</v>
+        <v>1000</v>
       </c>
       <c r="R222" t="n">
         <v>0</v>
@@ -15388,7 +15388,7 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
+          <t>PROGRAMA DE MICRORREVESTIMENTO ASFÁLTICO</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -15414,7 +15414,7 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>1406178</v>
+        <v>10000000</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>04ª URG BARBACENA</t>
+          <t>REALINHAMENTO DE PREÇOS DO FORNECIMENTO DO MATERIAL BETUMINOSO</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>0</v>
+        <v>1406178</v>
       </c>
       <c r="R224" t="n">
-        <v>12870000</v>
+        <v>0</v>
       </c>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr"/>
@@ -15520,7 +15520,7 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>20ª URG FORMIGA</t>
+          <t>04ª URG BARBACENA</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -15586,7 +15586,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>28ª URG TEÓFILO OTONI</t>
+          <t>20ª URG FORMIGA</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -15615,7 +15615,7 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>9575065</v>
+        <v>12870000</v>
       </c>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr"/>
@@ -15652,7 +15652,7 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>30ª URG JUIZ DE FORA</t>
+          <t>28ª URG TEÓFILO OTONI</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -15681,7 +15681,7 @@
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>12375000</v>
+        <v>9575065</v>
       </c>
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
@@ -15718,7 +15718,7 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - SUL</t>
+          <t>30ª URG JUIZ DE FORA</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -15747,7 +15747,7 @@
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>14850000</v>
+        <v>12375000</v>
       </c>
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr"/>
@@ -15784,7 +15784,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>01ª URG BELO HORIZONTE - NORTE</t>
+          <t>01ª URG BELO HORIZONTE - SUL</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15850,7 +15850,7 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>31ª URG ITUIUTABA</t>
+          <t>01ª URG BELO HORIZONTE - NORTE</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -15879,7 +15879,7 @@
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>9900000</v>
+        <v>14850000</v>
       </c>
       <c r="S230" t="inlineStr"/>
       <c r="T230" t="inlineStr"/>
@@ -15916,7 +15916,7 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
+          <t>31ª URG ITUIUTABA</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -15942,10 +15942,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>654124898</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>9900000</v>
       </c>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr"/>
@@ -15982,7 +15982,7 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
+          <t>CONSERVAÇÃO DA MALHA VIÁRIA DAS 40ª URG`S</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -16008,7 +16008,7 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>30767861</v>
+        <v>654124898</v>
       </c>
       <c r="R232" t="n">
         <v>0</v>
@@ -16048,7 +16048,7 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA EXECUÇÃO DE SERVIÇOS DE NATUREZA CONTÍNUA DE SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, EM REGIME DE EMPREITADA POR PREÇO UNITÁRIO, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -16074,7 +16074,7 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>19976964</v>
+        <v>30767861</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
@@ -16114,7 +16114,7 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
+          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO CIDADE ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>12895888</v>
+        <v>19976964</v>
       </c>
       <c r="R234" t="n">
         <v>0</v>
@@ -16180,7 +16180,7 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 1</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -16206,7 +16206,7 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>11846334</v>
+        <v>12895888</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
@@ -16246,7 +16246,7 @@
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 2</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>15201174</v>
+        <v>11846334</v>
       </c>
       <c r="R236" t="n">
         <v>0</v>
@@ -16312,7 +16312,7 @@
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
-          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 3</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>12921920</v>
+        <v>15201174</v>
       </c>
       <c r="R237" t="n">
         <v>0</v>
@@ -16364,7 +16364,7 @@
         <v>81</v>
       </c>
       <c r="E238" t="n">
-        <v>4385</v>
+        <v>4293</v>
       </c>
       <c r="F238" t="n">
         <v>1</v>
@@ -16378,7 +16378,7 @@
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
+          <t>SINALIZAÇÃO VIÁRIA VERTICAL, HORIZONTAL E DISPOSITIVOS AUXILIARES, COM FORNECIMENTO DE MATERIAIS, UTILIZAÇÃO DE EQUIPAMENTOS E MÃO-DE-OBRA ESPECIALIZADA - LOTE 4</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -16404,7 +16404,7 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>6382601</v>
+        <v>12921920</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
@@ -16444,7 +16444,7 @@
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
+          <t>RECUPERAÇÃO FUNCIONAL MG-232 (BRAÚNAS (DIV. 40ª/ 2ª) - IPATINGA)</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -16470,7 +16470,7 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>30000000</v>
+        <v>6382601</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
@@ -16510,7 +16510,7 @@
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-259 ( SABINÓPOLIS - SERRO, GUANHÃES - SABINÓPOLIS E ALVORADA MINAS - SERRO) *</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>4000000</v>
+        <v>30000000</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
@@ -16559,10 +16559,10 @@
         <v>782</v>
       </c>
       <c r="D241" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E241" t="n">
-        <v>4280</v>
+        <v>4385</v>
       </c>
       <c r="F241" t="n">
         <v>1</v>
@@ -16576,7 +16576,7 @@
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
+          <t>RECUPERAÇÃO FUNCIONAL MGC-455 (PIRAJUBA - ENTRº BR-364 (PLANURA)</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -16642,7 +16642,7 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
+          <t>PONTO CRÍTICO: ENTRº BR-040 (BARREIRA DOTRIUNFO) - ENTRº MG-353 (GOIANÁ)</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -16668,7 +16668,7 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>470000</v>
+        <v>4000000</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
@@ -16708,7 +16708,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
+          <t>PONTO CRÍTICO: ENTRº MGC-265 (RIO POMBA) - PONTE RIO POMBA</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>4000000</v>
+        <v>470000</v>
       </c>
       <c r="R243" t="n">
         <v>0</v>
@@ -16774,7 +16774,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
+          <t>PONTO CRÍTICO: ENTRº P/ MARIA DA FÉ - INÍCIO DO PERÍMETRO URBANO DE ITAJUBÁ (2  PONTOS)</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
@@ -16840,7 +16840,7 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
+          <t>PONTO CRÍTICO: PALMÓPOLIS - RIO DO PRADO (6 PONTOS)/ PONTE SOBRE O RIBEIRÃO JOSÉ FERREIRA (1 PONTO)</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -16866,7 +16866,7 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>420000</v>
+        <v>1000000</v>
       </c>
       <c r="R245" t="n">
         <v>0</v>
@@ -16906,7 +16906,7 @@
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
-          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
+          <t>PONTO CRÍTICO: RODEIRO - ENTRº MG-285</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -16932,7 +16932,7 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>790000</v>
+        <v>420000</v>
       </c>
       <c r="R246" t="n">
         <v>0</v>
@@ -16946,19 +16946,19 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="B247" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C247" t="n">
-        <v>363</v>
+        <v>782</v>
       </c>
       <c r="D247" t="n">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="E247" t="n">
-        <v>4006</v>
+        <v>4280</v>
       </c>
       <c r="F247" t="n">
         <v>1</v>
@@ -16972,39 +16972,33 @@
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
+          <t>PONTO CRÍTICO: SABARÁ-CAETÉ (3 PONTOS)</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>PARALISADO</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>METRO QUADRADO</t>
-        </is>
-      </c>
-      <c r="M247" t="n">
-        <v>5000</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>UNAÍ</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>5000000</v>
+        <v>790000</v>
       </c>
       <c r="R247" t="n">
         <v>0</v>
@@ -17018,19 +17012,19 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2321</v>
+        <v>2311</v>
       </c>
       <c r="B248" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C248" t="n">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="D248" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="E248" t="n">
-        <v>4222</v>
+        <v>4006</v>
       </c>
       <c r="F248" t="n">
         <v>1</v>
@@ -17044,33 +17038,39 @@
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projetos em unidade diversas </t>
+          <t>Construção da escola do Brasil Profissionalizado no município de Unaí-MG</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
+          <t>PARALISADO</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>METRO QUADRADO</t>
+        </is>
+      </c>
+      <c r="M248" t="n">
+        <v>5000</v>
+      </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>UNAÍ</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>800291</v>
+        <v>5000000</v>
       </c>
       <c r="R248" t="n">
         <v>0</v>
@@ -17132,11 +17132,11 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>174673</v>
+        <v>800291</v>
       </c>
       <c r="R249" t="n">
         <v>0</v>
@@ -17173,17 +17173,15 @@
       <c r="H250" t="n">
         <v>249</v>
       </c>
-      <c r="I250" t="n">
-        <v>11877</v>
-      </c>
+      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Contrato a obra de reforma e ampliação</t>
+          <t xml:space="preserve">Projetos em unidade diversas </t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L250" t="inlineStr"/>
@@ -17195,16 +17193,16 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Região Intermediária de Barbacena</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DEL REI</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>1088908</v>
+        <v>174673</v>
       </c>
       <c r="R250" t="n">
         <v>0</v>
@@ -17218,19 +17216,19 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2361</v>
+        <v>2321</v>
       </c>
       <c r="B251" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C251" t="n">
-        <v>846</v>
+        <v>302</v>
       </c>
       <c r="D251" t="n">
-        <v>705</v>
+        <v>87</v>
       </c>
       <c r="E251" t="n">
-        <v>7004</v>
+        <v>4222</v>
       </c>
       <c r="F251" t="n">
         <v>1</v>
@@ -17241,10 +17239,12 @@
       <c r="H251" t="n">
         <v>250</v>
       </c>
-      <c r="I251" t="inlineStr"/>
+      <c r="I251" t="n">
+        <v>11877</v>
+      </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Possível adequação da sede</t>
+          <t>Contrato a obra de reforma e ampliação</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -17259,10 +17259,22 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="inlineStr"/>
-      <c r="R251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Região Intermediária de Barbacena</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>SÃO JOÃO DEL REI</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>1088908</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0</v>
+      </c>
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr"/>
       <c r="U251" t="inlineStr"/>
@@ -17275,16 +17287,16 @@
         <v>2361</v>
       </c>
       <c r="B252" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C252" t="n">
-        <v>274</v>
+        <v>846</v>
       </c>
       <c r="D252" t="n">
-        <v>766</v>
+        <v>705</v>
       </c>
       <c r="E252" t="n">
-        <v>2113</v>
+        <v>7004</v>
       </c>
       <c r="F252" t="n">
         <v>1</v>
@@ -17335,10 +17347,10 @@
         <v>274</v>
       </c>
       <c r="D253" t="n">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E253" t="n">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
@@ -17352,7 +17364,7 @@
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Possível obras de adequação da sede.</t>
+          <t>Possível adequação da sede</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -17367,22 +17379,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>Região Intermediária de Belo Horizonte</t>
-        </is>
-      </c>
-      <c r="P253" t="inlineStr">
-        <is>
-          <t>BELO HORIZONTE</t>
-        </is>
-      </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
-      <c r="R253" t="n">
-        <v>2754406</v>
-      </c>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr"/>
       <c r="U253" t="inlineStr"/>
@@ -17392,19 +17392,19 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>2371</v>
+        <v>2361</v>
       </c>
       <c r="B254" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C254" t="n">
-        <v>609</v>
+        <v>274</v>
       </c>
       <c r="D254" t="n">
-        <v>78</v>
+        <v>767</v>
       </c>
       <c r="E254" t="n">
-        <v>4238</v>
+        <v>2114</v>
       </c>
       <c r="F254" t="n">
         <v>1</v>
@@ -17418,7 +17418,7 @@
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
+          <t>Possível obras de adequação da sede.</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -17444,10 +17444,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>8311374</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>2754406</v>
       </c>
       <c r="S254" t="inlineStr"/>
       <c r="T254" t="inlineStr"/>
@@ -17458,19 +17458,19 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2421</v>
+        <v>2371</v>
       </c>
       <c r="B255" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C255" t="n">
-        <v>544</v>
+        <v>609</v>
       </c>
       <c r="D255" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="E255" t="n">
-        <v>1016</v>
+        <v>4238</v>
       </c>
       <c r="F255" t="n">
         <v>1</v>
@@ -17484,7 +17484,7 @@
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
+          <t>Reestruturação física e ampliação do Laboratório de Química Agropecuária do Instituto Mineiro de Agropecuária - IMA</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -17501,16 +17501,16 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>MONTES CLAROS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>477508</v>
+        <v>8311374</v>
       </c>
       <c r="R255" t="n">
         <v>0</v>
@@ -17524,19 +17524,19 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>3051</v>
+        <v>2421</v>
       </c>
       <c r="B256" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C256" t="n">
-        <v>364</v>
+        <v>544</v>
       </c>
       <c r="D256" t="n">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="E256" t="n">
-        <v>4016</v>
+        <v>1016</v>
       </c>
       <c r="F256" t="n">
         <v>1</v>
@@ -17550,7 +17550,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
+          <t>Perfuração de Sistemas de Abastecimento de Agua conforme demanda dos municípios atendidos pelo IDENE</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -17567,16 +17567,16 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>4825656</v>
+        <v>477508</v>
       </c>
       <c r="R256" t="n">
         <v>0</v>
@@ -17616,7 +17616,7 @@
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
+          <t>Instalações do curso de Agropecuária de Precisão, com 1.070 m² de área total, além de 5 unidades de tratamento de águas residuárias.</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -17642,7 +17642,7 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>12649000</v>
+        <v>4825656</v>
       </c>
       <c r="R257" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
+          <t>Construção de novas instalações no Instituto Tecnológico de Agropecuária de Pitangui - ITAP, totalizando 3.214 m², para salas de aula, plantas-piloto de produção e laboratórios de apoio.</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>3715000</v>
+        <v>12649000</v>
       </c>
       <c r="R258" t="n">
         <v>0</v>
@@ -17725,16 +17725,16 @@
         <v>3051</v>
       </c>
       <c r="B259" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C259" t="n">
-        <v>571</v>
+        <v>364</v>
       </c>
       <c r="D259" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E259" t="n">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -17748,7 +17748,7 @@
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
+          <t xml:space="preserve">Reforma do edifício histórico do Instituto de Laticínios Cândido Tostes, localizado no município dde juiz de Fora. </t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -17774,10 +17774,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>0</v>
+        <v>3715000</v>
       </c>
       <c r="R259" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr"/>
@@ -17788,19 +17788,19 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>4031</v>
+        <v>3051</v>
       </c>
       <c r="B260" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C260" t="n">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="D260" t="n">
-        <v>706</v>
+        <v>16</v>
       </c>
       <c r="E260" t="n">
-        <v>2091</v>
+        <v>4018</v>
       </c>
       <c r="F260" t="n">
         <v>1</v>
@@ -17811,47 +17811,39 @@
       <c r="H260" t="n">
         <v>259</v>
       </c>
-      <c r="I260" t="n">
-        <v>12054</v>
-      </c>
+      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
+          <t>Melhoria na infraestrutura das unidades de pesquisa.</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>UNIDADE</t>
-        </is>
-      </c>
-      <c r="M260" t="n">
-        <v>1</v>
-      </c>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>BETIM</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>11016496</v>
+        <v>250000</v>
       </c>
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr"/>
@@ -17886,11 +17878,11 @@
         <v>260</v>
       </c>
       <c r="I261" t="n">
-        <v>12806</v>
+        <v>12054</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
+          <t xml:space="preserve"> Construção do novo prédio do Fórum da Comarca de Betim/MG</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17913,19 +17905,19 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>CAMPO BELO</t>
+          <t>BETIM</t>
         </is>
       </c>
       <c r="Q261" t="n">
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>19994210</v>
+        <v>11016496</v>
       </c>
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr"/>
@@ -17960,11 +17952,11 @@
         <v>261</v>
       </c>
       <c r="I262" t="n">
-        <v>12638</v>
+        <v>12806</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
+          <t>Campo Belo/MG - Construção do novo Fórum da Comarca de Campo Belo</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -17987,19 +17979,19 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>CARANGOLA</t>
+          <t>CAMPO BELO</t>
         </is>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>12843388</v>
+        <v>19994210</v>
       </c>
       <c r="S262" t="inlineStr"/>
       <c r="T262" t="inlineStr"/>
@@ -18034,11 +18026,11 @@
         <v>262</v>
       </c>
       <c r="I263" t="n">
-        <v>12400</v>
+        <v>12638</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Carangola.</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -18061,19 +18053,19 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>IPATINGA</t>
+          <t>CARANGOLA</t>
         </is>
       </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>18849069</v>
+        <v>12843388</v>
       </c>
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr"/>
@@ -18108,11 +18100,11 @@
         <v>263</v>
       </c>
       <c r="I264" t="n">
-        <v>12288</v>
+        <v>12400</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
+          <t xml:space="preserve"> Contrato a execução da obra de reforma e ampliação do Fórum da Comarca de Ipatinga/MG</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -18135,19 +18127,19 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>MONTE BELO</t>
+          <t>IPATINGA</t>
         </is>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>1950000</v>
+        <v>18849069</v>
       </c>
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr"/>
@@ -18182,11 +18174,11 @@
         <v>264</v>
       </c>
       <c r="I265" t="n">
-        <v>12816</v>
+        <v>12288</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
+          <t xml:space="preserve"> Reforma e Ampliação do Fórum da Comarca de Monte Belo/MG</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -18209,19 +18201,19 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>PIRAPORA</t>
+          <t>MONTE BELO</t>
         </is>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>22776109</v>
+        <v>1950000</v>
       </c>
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr"/>
@@ -18256,11 +18248,11 @@
         <v>265</v>
       </c>
       <c r="I266" t="n">
-        <v>12781</v>
+        <v>12816</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Pirapora/MG</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -18283,19 +18275,19 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO SAPUCAÍ</t>
+          <t>PIRAPORA</t>
         </is>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>14670005</v>
+        <v>22776109</v>
       </c>
       <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr"/>
@@ -18330,11 +18322,11 @@
         <v>266</v>
       </c>
       <c r="I267" t="n">
-        <v>12799</v>
+        <v>12781</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
+          <t>Construção do novo fórum da Comarca de São Gonçalo do Sapucaí/MG</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -18357,19 +18349,19 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>TIMÓTEO</t>
+          <t>SÃO GONÇALO DO SAPUCAÍ</t>
         </is>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>19506288</v>
+        <v>14670005</v>
       </c>
       <c r="S267" t="inlineStr"/>
       <c r="T267" t="inlineStr"/>
@@ -18404,16 +18396,16 @@
         <v>267</v>
       </c>
       <c r="I268" t="n">
-        <v>12833</v>
+        <v>12799</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
+          <t xml:space="preserve">Construção do novo Fórum da Comarca de Timóteo/MG </t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -18431,19 +18423,19 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>RIO NOVO</t>
+          <t>TIMÓTEO</t>
         </is>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>4976096</v>
+        <v>19506288</v>
       </c>
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr"/>
@@ -18478,11 +18470,11 @@
         <v>268</v>
       </c>
       <c r="I269" t="n">
-        <v>12629</v>
+        <v>12833</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Rio Novo.</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -18505,19 +18497,19 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>Região Intermediária de Divinópolis</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>RIO NOVO</t>
         </is>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>7654409</v>
+        <v>4976096</v>
       </c>
       <c r="S269" t="inlineStr"/>
       <c r="T269" t="inlineStr"/>
@@ -18552,16 +18544,16 @@
         <v>269</v>
       </c>
       <c r="I270" t="n">
-        <v>12607</v>
+        <v>12629</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
+          <t>Obra de construção do novo Fórum da Comarca de Luz.</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -18579,19 +18571,19 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Divinópolis</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>32235085</v>
+        <v>7654409</v>
       </c>
       <c r="S270" t="inlineStr"/>
       <c r="T270" t="inlineStr"/>
@@ -18626,11 +18618,11 @@
         <v>270</v>
       </c>
       <c r="I271" t="n">
-        <v>12639</v>
+        <v>12607</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
+          <t>Reforma e ampliação do Fórum da Comarca de Sete Lagoas/MG.</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -18653,19 +18645,19 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Região Intermediária de Varginha</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>TRÊS PONTAS</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="Q271" t="n">
         <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>9489687</v>
+        <v>32235085</v>
       </c>
       <c r="S271" t="inlineStr"/>
       <c r="T271" t="inlineStr"/>
@@ -18700,16 +18692,16 @@
         <v>271</v>
       </c>
       <c r="I272" t="n">
-        <v>11547</v>
+        <v>12639</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
+          <t>Obra de construção do novo Fórum da Comarca de Três Pontas</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -18727,19 +18719,19 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Região Intermediária de Pouso Alegre</t>
+          <t>Região Intermediária de Varginha</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>ITAJUBÁ</t>
+          <t>TRÊS PONTAS</t>
         </is>
       </c>
       <c r="Q272" t="n">
         <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>9366263</v>
+        <v>9489687</v>
       </c>
       <c r="S272" t="inlineStr"/>
       <c r="T272" t="inlineStr"/>
@@ -18774,11 +18766,11 @@
         <v>272</v>
       </c>
       <c r="I273" t="n">
-        <v>12856</v>
+        <v>11547</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
+          <t>RETOMADA DA OBRA DE CONSTRUÇÃO DO NOVO PRÉDIO DO FÓRUM DA COMARCA DE ITAJUBÁ/MG</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -18806,14 +18798,14 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>POÇOS DE CALDAS</t>
+          <t>ITAJUBÁ</t>
         </is>
       </c>
       <c r="Q273" t="n">
         <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>11009635</v>
+        <v>9366263</v>
       </c>
       <c r="S273" t="inlineStr"/>
       <c r="T273" t="inlineStr"/>
@@ -18848,11 +18840,11 @@
         <v>273</v>
       </c>
       <c r="I274" t="n">
-        <v>12344</v>
+        <v>12856</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
+          <t>Retomada da obra de construção do novo Fórum da Comarca de Poços de Caldas.</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -18880,14 +18872,14 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>CAMANDUCAIA</t>
+          <t>POÇOS DE CALDAS</t>
         </is>
       </c>
       <c r="Q274" t="n">
         <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>4627222</v>
+        <v>11009635</v>
       </c>
       <c r="S274" t="inlineStr"/>
       <c r="T274" t="inlineStr"/>
@@ -18921,10 +18913,12 @@
       <c r="H275" t="n">
         <v>274</v>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="n">
+        <v>12344</v>
+      </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
+          <t>Construção do novo prédio do Fórum da Comarca de Camanducaia/MG</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -18947,19 +18941,19 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Pouso Alegre</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>SÃO JOÃO DO PARAÍSO</t>
+          <t>CAMANDUCAIA</t>
         </is>
       </c>
       <c r="Q275" t="n">
         <v>0</v>
       </c>
       <c r="R275" t="n">
-        <v>7290196</v>
+        <v>4627222</v>
       </c>
       <c r="S275" t="inlineStr"/>
       <c r="T275" t="inlineStr"/>
@@ -18996,7 +18990,7 @@
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
+          <t>Obra de construção do novo Fórum da Comarca de São João do Paraíso</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -19019,19 +19013,19 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>Região Intermediária de Patos de Minas</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>BRASILÂNDIA DE MINAS</t>
+          <t>SÃO JOÃO DO PARAÍSO</t>
         </is>
       </c>
       <c r="Q276" t="n">
         <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>1373680</v>
+        <v>7290196</v>
       </c>
       <c r="S276" t="inlineStr"/>
       <c r="T276" t="inlineStr"/>
@@ -19068,7 +19062,7 @@
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
+          <t>Implantação do Fórum Digital no município de Brasilândia de Minas</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -19096,7 +19090,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO DO ABAETÉ</t>
+          <t>BRASILÂNDIA DE MINAS</t>
         </is>
       </c>
       <c r="Q277" t="n">
@@ -19140,7 +19134,7 @@
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
+          <t>Implantação do Fórum Digital no município de São Gonçalo do Abaeté</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -19163,19 +19157,19 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Patos de Minas</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>PONTO CHIQUE</t>
+          <t>SÃO GONÇALO DO ABAETÉ</t>
         </is>
       </c>
       <c r="Q278" t="n">
         <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>1760000</v>
+        <v>1373680</v>
       </c>
       <c r="S278" t="inlineStr"/>
       <c r="T278" t="inlineStr"/>
@@ -19209,17 +19203,15 @@
       <c r="H279" t="n">
         <v>278</v>
       </c>
-      <c r="I279" t="n">
-        <v>12627</v>
-      </c>
+      <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
+          <t>Implantação do Fórum Digital no município de Ponto Chique</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -19237,19 +19229,19 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>PONTO CHIQUE</t>
         </is>
       </c>
       <c r="Q279" t="n">
         <v>0</v>
       </c>
       <c r="R279" t="n">
-        <v>38084213</v>
+        <v>1760000</v>
       </c>
       <c r="S279" t="inlineStr"/>
       <c r="T279" t="inlineStr"/>
@@ -19284,11 +19276,11 @@
         <v>279</v>
       </c>
       <c r="I280" t="n">
-        <v>12146</v>
+        <v>12627</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
+          <t>Execução da 4ª (quarta) parcela da reforma parcial do Edifício-Sede do TRIBUNAL.</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -19323,7 +19315,7 @@
         <v>0</v>
       </c>
       <c r="R280" t="n">
-        <v>135013067</v>
+        <v>38084213</v>
       </c>
       <c r="S280" t="inlineStr"/>
       <c r="T280" t="inlineStr"/>
@@ -19358,11 +19350,11 @@
         <v>280</v>
       </c>
       <c r="I281" t="n">
-        <v>12703</v>
+        <v>12146</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
+          <t>Reforma geral do Fórum Lafayette, em Belo Horizonte/MG</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -19397,7 +19389,7 @@
         <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>1052449</v>
+        <v>135013067</v>
       </c>
       <c r="S281" t="inlineStr"/>
       <c r="T281" t="inlineStr"/>
@@ -19431,15 +19423,17 @@
       <c r="H282" t="n">
         <v>281</v>
       </c>
-      <c r="I282" t="inlineStr"/>
+      <c r="I282" t="n">
+        <v>12703</v>
+      </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
+          <t>Cincão - Reforma parcial para adequações da estrutura física dos Armazéns 6, 7 e 8, Galpão 2, Arquivo Central e Permanente</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -19457,19 +19451,19 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>MONTE ALEGRE DE MINAS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q282" t="n">
         <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>6139672</v>
+        <v>1052449</v>
       </c>
       <c r="S282" t="inlineStr"/>
       <c r="T282" t="inlineStr"/>
@@ -19480,19 +19474,19 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>5011</v>
+        <v>4031</v>
       </c>
       <c r="B283" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C283" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="D283" t="n">
-        <v>133</v>
+        <v>706</v>
       </c>
       <c r="E283" t="n">
-        <v>3017</v>
+        <v>2091</v>
       </c>
       <c r="F283" t="n">
         <v>1</v>
@@ -19506,7 +19500,7 @@
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
-          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
+          <t>Obra de construção do novo Fórum da Comarca de Monte Alegre de Minas</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -19514,28 +19508,34 @@
           <t>INICIANDO</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
+        <v>1</v>
+      </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>MONTE ALEGRE DE MINAS</t>
         </is>
       </c>
       <c r="Q283" t="n">
         <v>0</v>
       </c>
       <c r="R283" t="n">
-        <v>800000</v>
+        <v>6139672</v>
       </c>
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="inlineStr"/>
@@ -19546,19 +19546,19 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>5031</v>
+        <v>5011</v>
       </c>
       <c r="B284" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C284" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="D284" t="n">
         <v>133</v>
       </c>
       <c r="E284" t="n">
-        <v>3015</v>
+        <v>3017</v>
       </c>
       <c r="F284" t="n">
         <v>1</v>
@@ -19572,7 +19572,7 @@
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
-          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
+          <t>CENTRO DE CULTURA PRESIDENTE ITAMAR FRANCO</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -19601,7 +19601,7 @@
         <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>4782988</v>
+        <v>800000</v>
       </c>
       <c r="S284" t="inlineStr"/>
       <c r="T284" t="inlineStr"/>
@@ -19612,19 +19612,19 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>5141</v>
+        <v>5031</v>
       </c>
       <c r="B285" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C285" t="n">
-        <v>126</v>
+        <v>572</v>
       </c>
       <c r="D285" t="n">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="E285" t="n">
-        <v>6006</v>
+        <v>3015</v>
       </c>
       <c r="F285" t="n">
         <v>1</v>
@@ -19638,7 +19638,7 @@
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
-          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
+          <t>BALNEÁRIO ÁGUAS SANTAS - TIRADENTES/MG | BARREIO DE ARAXÁ</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -19667,7 +19667,7 @@
         <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>16317109</v>
+        <v>4782988</v>
       </c>
       <c r="S285" t="inlineStr"/>
       <c r="T285" t="inlineStr"/>
@@ -19678,19 +19678,19 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>5251</v>
+        <v>5141</v>
       </c>
       <c r="B286" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C286" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D286" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E286" t="n">
-        <v>3018</v>
+        <v>6006</v>
       </c>
       <c r="F286" t="n">
         <v>1</v>
@@ -19704,12 +19704,12 @@
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Projeto de Expansão</t>
+          <t>ELABORAÇÃO E EXECUÇÃO DE PROJETOS RELACIONADOS À REFORMA, MODERNIZAÇÃO E ADEQUAÇÃO DAS INSTALAÇÕES PREDIAIS DA COMPANHIA.</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>EXECUÇÃO</t>
+          <t>INICIANDO</t>
         </is>
       </c>
       <c r="L286" t="inlineStr"/>
@@ -19721,19 +19721,19 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q286" t="n">
         <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>457766318</v>
+        <v>16317109</v>
       </c>
       <c r="S286" t="inlineStr"/>
       <c r="T286" t="inlineStr"/>
@@ -19744,19 +19744,19 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>5391</v>
+        <v>5251</v>
       </c>
       <c r="B287" t="n">
         <v>25</v>
       </c>
       <c r="C287" t="n">
-        <v>752</v>
+        <v>121</v>
       </c>
       <c r="D287" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="E287" t="n">
-        <v>3004</v>
+        <v>3018</v>
       </c>
       <c r="F287" t="n">
         <v>1</v>
@@ -19770,12 +19770,12 @@
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
+          <t>Projeto de Expansão</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>INICIANDO</t>
+          <t>EXECUÇÃO</t>
         </is>
       </c>
       <c r="L287" t="inlineStr"/>
@@ -19792,14 +19792,14 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q287" t="n">
         <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>92004926</v>
+        <v>457766318</v>
       </c>
       <c r="S287" t="inlineStr"/>
       <c r="T287" t="inlineStr"/>
@@ -19853,19 +19853,19 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q288" t="n">
         <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>10705994</v>
+        <v>92004926</v>
       </c>
       <c r="S288" t="inlineStr"/>
       <c r="T288" t="inlineStr"/>
@@ -19919,19 +19919,19 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q289" t="n">
         <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>10464844</v>
+        <v>10705994</v>
       </c>
       <c r="S289" t="inlineStr"/>
       <c r="T289" t="inlineStr"/>
@@ -19985,19 +19985,19 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q290" t="n">
         <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>2098278</v>
+        <v>10464844</v>
       </c>
       <c r="S290" t="inlineStr"/>
       <c r="T290" t="inlineStr"/>
@@ -20051,19 +20051,19 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q291" t="n">
         <v>0</v>
       </c>
       <c r="R291" t="n">
-        <v>96721858</v>
+        <v>2098278</v>
       </c>
       <c r="S291" t="inlineStr"/>
       <c r="T291" t="inlineStr"/>
@@ -20117,19 +20117,19 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q292" t="n">
         <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>16415074</v>
+        <v>96721858</v>
       </c>
       <c r="S292" t="inlineStr"/>
       <c r="T292" t="inlineStr"/>
@@ -20183,19 +20183,19 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q293" t="n">
         <v>0</v>
       </c>
       <c r="R293" t="n">
-        <v>1</v>
+        <v>16415074</v>
       </c>
       <c r="S293" t="inlineStr"/>
       <c r="T293" t="inlineStr"/>
@@ -20218,7 +20218,7 @@
         <v>92</v>
       </c>
       <c r="E294" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F294" t="n">
         <v>1</v>
@@ -20232,7 +20232,7 @@
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Reformas de Subestações e Linhas de Transmissão</t>
+          <t xml:space="preserve">Expansão e Aquisição do Sistema de Transmissão </t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -20249,19 +20249,19 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>Região Intermediária de Belo Horizonte</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q294" t="n">
         <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>126817302</v>
+        <v>1</v>
       </c>
       <c r="S294" t="inlineStr"/>
       <c r="T294" t="inlineStr"/>
@@ -20315,19 +20315,19 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>Região Intermediária de Montes Claros</t>
+          <t>Região Intermediária de Belo Horizonte</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE BELO HORIZONTE</t>
         </is>
       </c>
       <c r="Q295" t="n">
         <v>0</v>
       </c>
       <c r="R295" t="n">
-        <v>16058991</v>
+        <v>126817302</v>
       </c>
       <c r="S295" t="inlineStr"/>
       <c r="T295" t="inlineStr"/>
@@ -20381,19 +20381,19 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>Região Intermediária de Juíz de Fora</t>
+          <t>Região Intermediária de Montes Claros</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="Q296" t="n">
         <v>0</v>
       </c>
       <c r="R296" t="n">
-        <v>65795530</v>
+        <v>16058991</v>
       </c>
       <c r="S296" t="inlineStr"/>
       <c r="T296" t="inlineStr"/>
@@ -20447,19 +20447,19 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberlândia</t>
+          <t>Região Intermediária de Juíz de Fora</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE JUÍZ DE FORA</t>
         </is>
       </c>
       <c r="Q297" t="n">
         <v>0</v>
       </c>
       <c r="R297" t="n">
-        <v>44156794</v>
+        <v>65795530</v>
       </c>
       <c r="S297" t="inlineStr"/>
       <c r="T297" t="inlineStr"/>
@@ -20513,19 +20513,19 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberlândia</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERLÂNDIA</t>
         </is>
       </c>
       <c r="Q298" t="n">
         <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>140716908</v>
+        <v>44156794</v>
       </c>
       <c r="S298" t="inlineStr"/>
       <c r="T298" t="inlineStr"/>
@@ -20579,19 +20579,19 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>Região Intermediária de Ipatinga</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
         </is>
       </c>
       <c r="Q299" t="n">
         <v>0</v>
       </c>
       <c r="R299" t="n">
-        <v>8715687</v>
+        <v>140716908</v>
       </c>
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="inlineStr"/>
@@ -20645,19 +20645,19 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>Região Intermediária de Uberaba</t>
+          <t>Região Intermediária de Ipatinga</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE IPATINGA</t>
         </is>
       </c>
       <c r="Q300" t="n">
         <v>0</v>
       </c>
       <c r="R300" t="n">
-        <v>24622611</v>
+        <v>8715687</v>
       </c>
       <c r="S300" t="inlineStr"/>
       <c r="T300" t="inlineStr"/>
@@ -20677,10 +20677,10 @@
         <v>752</v>
       </c>
       <c r="D301" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E301" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="F301" t="n">
         <v>1</v>
@@ -20694,7 +20694,7 @@
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Expansão do Sistema de Geração</t>
+          <t>Reformas de Subestações e Linhas de Transmissão</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -20711,19 +20711,19 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Região Intermediária de Uberaba</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+          <t>DIVERSOS MUNICÍPIOS - REGIÃO INTERMEDIÁRIA DE UBERABA</t>
         </is>
       </c>
       <c r="Q301" t="n">
         <v>0</v>
       </c>
       <c r="R301" t="n">
-        <v>1</v>
+        <v>24622611</v>
       </c>
       <c r="S301" t="inlineStr"/>
       <c r="T301" t="inlineStr"/>
@@ -20732,6 +20732,72 @@
       <c r="W301" t="inlineStr"/>
       <c r="X301" t="inlineStr"/>
     </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B302" t="n">
+        <v>25</v>
+      </c>
+      <c r="C302" t="n">
+        <v>752</v>
+      </c>
+      <c r="D302" t="n">
+        <v>94</v>
+      </c>
+      <c r="E302" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="n">
+        <v>301</v>
+      </c>
+      <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Expansão do Sistema de Geração</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>INICIANDO</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>DIVERSOS MUNICÍPIOS - ESTADUAL</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>0</v>
+      </c>
+      <c r="R302" t="n">
+        <v>1</v>
+      </c>
+      <c r="S302" t="inlineStr"/>
+      <c r="T302" t="inlineStr"/>
+      <c r="U302" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
+      <c r="W302" t="inlineStr"/>
+      <c r="X302" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
